--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="398">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1569,7 +1569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP309"/>
+  <dimension ref="A1:BP311"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2730,7 +2730,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ6">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -4378,7 +4378,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ14">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -6435,7 +6435,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ24">
         <v>0.92</v>
@@ -8498,7 +8498,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ34">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR34">
         <v>1.56</v>
@@ -10555,7 +10555,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ44">
         <v>0.75</v>
@@ -11588,7 +11588,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ49">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR49">
         <v>1.17</v>
@@ -13027,7 +13027,7 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ56">
         <v>1.46</v>
@@ -14678,7 +14678,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ64">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR64">
         <v>1.36</v>
@@ -15502,7 +15502,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ68">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR68">
         <v>1.6</v>
@@ -16735,7 +16735,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ74">
         <v>0.31</v>
@@ -19828,7 +19828,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ89">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR89">
         <v>1.26</v>
@@ -21064,7 +21064,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ95">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR95">
         <v>0.98</v>
@@ -21888,7 +21888,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ99">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR99">
         <v>1.08</v>
@@ -22709,7 +22709,7 @@
         <v>0.75</v>
       </c>
       <c r="AP103">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ103">
         <v>1.33</v>
@@ -24566,7 +24566,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ112">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR112">
         <v>1.26</v>
@@ -27244,7 +27244,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ125">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR125">
         <v>1.76</v>
@@ -30334,7 +30334,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ140">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR140">
         <v>1.3</v>
@@ -30743,7 +30743,7 @@
         <v>0.4</v>
       </c>
       <c r="AP142">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ142">
         <v>0.67</v>
@@ -33218,7 +33218,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ154">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR154">
         <v>1.43</v>
@@ -34866,7 +34866,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ162">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR162">
         <v>1.39</v>
@@ -35069,7 +35069,7 @@
         <v>0.86</v>
       </c>
       <c r="AP163">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ163">
         <v>0.54</v>
@@ -36514,7 +36514,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ170">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR170">
         <v>1.45</v>
@@ -38983,10 +38983,10 @@
         <v>0.75</v>
       </c>
       <c r="AP182">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ182">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR182">
         <v>1.52</v>
@@ -41664,7 +41664,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ195">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR195">
         <v>1.46</v>
@@ -48665,7 +48665,7 @@
         <v>1.1</v>
       </c>
       <c r="AP229">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ229">
         <v>1.08</v>
@@ -49904,7 +49904,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ235">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR235">
         <v>1.35</v>
@@ -50110,7 +50110,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ236">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR236">
         <v>1.67</v>
@@ -54024,7 +54024,7 @@
         <v>2</v>
       </c>
       <c r="AQ255">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR255">
         <v>1.44</v>
@@ -54436,7 +54436,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ257">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR257">
         <v>1.86</v>
@@ -54845,7 +54845,7 @@
         <v>1.4</v>
       </c>
       <c r="AP259">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ259">
         <v>1.5</v>
@@ -60410,7 +60410,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ286">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR286">
         <v>1.65</v>
@@ -60613,7 +60613,7 @@
         <v>1.08</v>
       </c>
       <c r="AP287">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ287">
         <v>1.08</v>
@@ -60822,7 +60822,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ288">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR288">
         <v>1.32</v>
@@ -63706,7 +63706,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ302">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR302">
         <v>1.22</v>
@@ -65224,6 +65224,418 @@
       </c>
       <c r="BP309">
         <v>1.59</v>
+      </c>
+    </row>
+    <row r="310" spans="1:68">
+      <c r="A310" s="1">
+        <v>309</v>
+      </c>
+      <c r="B310">
+        <v>7478961</v>
+      </c>
+      <c r="C310" t="s">
+        <v>68</v>
+      </c>
+      <c r="D310" t="s">
+        <v>69</v>
+      </c>
+      <c r="E310" s="2">
+        <v>45671.69791666666</v>
+      </c>
+      <c r="F310">
+        <v>19</v>
+      </c>
+      <c r="G310" t="s">
+        <v>78</v>
+      </c>
+      <c r="H310" t="s">
+        <v>87</v>
+      </c>
+      <c r="I310">
+        <v>0</v>
+      </c>
+      <c r="J310">
+        <v>0</v>
+      </c>
+      <c r="K310">
+        <v>0</v>
+      </c>
+      <c r="L310">
+        <v>1</v>
+      </c>
+      <c r="M310">
+        <v>1</v>
+      </c>
+      <c r="N310">
+        <v>2</v>
+      </c>
+      <c r="O310" t="s">
+        <v>231</v>
+      </c>
+      <c r="P310" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q310">
+        <v>2.88</v>
+      </c>
+      <c r="R310">
+        <v>2.2</v>
+      </c>
+      <c r="S310">
+        <v>3.6</v>
+      </c>
+      <c r="T310">
+        <v>1.36</v>
+      </c>
+      <c r="U310">
+        <v>3</v>
+      </c>
+      <c r="V310">
+        <v>2.63</v>
+      </c>
+      <c r="W310">
+        <v>1.44</v>
+      </c>
+      <c r="X310">
+        <v>7</v>
+      </c>
+      <c r="Y310">
+        <v>1.1</v>
+      </c>
+      <c r="Z310">
+        <v>2.35</v>
+      </c>
+      <c r="AA310">
+        <v>3.6</v>
+      </c>
+      <c r="AB310">
+        <v>2.8</v>
+      </c>
+      <c r="AC310">
+        <v>1.05</v>
+      </c>
+      <c r="AD310">
+        <v>9.5</v>
+      </c>
+      <c r="AE310">
+        <v>1.25</v>
+      </c>
+      <c r="AF310">
+        <v>3.8</v>
+      </c>
+      <c r="AG310">
+        <v>1.71</v>
+      </c>
+      <c r="AH310">
+        <v>2</v>
+      </c>
+      <c r="AI310">
+        <v>1.62</v>
+      </c>
+      <c r="AJ310">
+        <v>2.2</v>
+      </c>
+      <c r="AK310">
+        <v>1.35</v>
+      </c>
+      <c r="AL310">
+        <v>1.25</v>
+      </c>
+      <c r="AM310">
+        <v>1.65</v>
+      </c>
+      <c r="AN310">
+        <v>1.08</v>
+      </c>
+      <c r="AO310">
+        <v>0.67</v>
+      </c>
+      <c r="AP310">
+        <v>1.08</v>
+      </c>
+      <c r="AQ310">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR310">
+        <v>1.52</v>
+      </c>
+      <c r="AS310">
+        <v>1.14</v>
+      </c>
+      <c r="AT310">
+        <v>2.66</v>
+      </c>
+      <c r="AU310">
+        <v>6</v>
+      </c>
+      <c r="AV310">
+        <v>3</v>
+      </c>
+      <c r="AW310">
+        <v>5</v>
+      </c>
+      <c r="AX310">
+        <v>3</v>
+      </c>
+      <c r="AY310">
+        <v>13</v>
+      </c>
+      <c r="AZ310">
+        <v>6</v>
+      </c>
+      <c r="BA310">
+        <v>7</v>
+      </c>
+      <c r="BB310">
+        <v>3</v>
+      </c>
+      <c r="BC310">
+        <v>10</v>
+      </c>
+      <c r="BD310">
+        <v>1.65</v>
+      </c>
+      <c r="BE310">
+        <v>6.75</v>
+      </c>
+      <c r="BF310">
+        <v>2.48</v>
+      </c>
+      <c r="BG310">
+        <v>1.21</v>
+      </c>
+      <c r="BH310">
+        <v>3.95</v>
+      </c>
+      <c r="BI310">
+        <v>1.43</v>
+      </c>
+      <c r="BJ310">
+        <v>2.73</v>
+      </c>
+      <c r="BK310">
+        <v>1.75</v>
+      </c>
+      <c r="BL310">
+        <v>2.08</v>
+      </c>
+      <c r="BM310">
+        <v>2.17</v>
+      </c>
+      <c r="BN310">
+        <v>1.68</v>
+      </c>
+      <c r="BO310">
+        <v>2.83</v>
+      </c>
+      <c r="BP310">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="311" spans="1:68">
+      <c r="A311" s="1">
+        <v>310</v>
+      </c>
+      <c r="B311">
+        <v>7478966</v>
+      </c>
+      <c r="C311" t="s">
+        <v>68</v>
+      </c>
+      <c r="D311" t="s">
+        <v>69</v>
+      </c>
+      <c r="E311" s="2">
+        <v>45671.69791666666</v>
+      </c>
+      <c r="F311">
+        <v>19</v>
+      </c>
+      <c r="G311" t="s">
+        <v>92</v>
+      </c>
+      <c r="H311" t="s">
+        <v>73</v>
+      </c>
+      <c r="I311">
+        <v>0</v>
+      </c>
+      <c r="J311">
+        <v>1</v>
+      </c>
+      <c r="K311">
+        <v>1</v>
+      </c>
+      <c r="L311">
+        <v>1</v>
+      </c>
+      <c r="M311">
+        <v>1</v>
+      </c>
+      <c r="N311">
+        <v>2</v>
+      </c>
+      <c r="O311" t="s">
+        <v>187</v>
+      </c>
+      <c r="P311" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q311">
+        <v>3.1</v>
+      </c>
+      <c r="R311">
+        <v>2.2</v>
+      </c>
+      <c r="S311">
+        <v>3.4</v>
+      </c>
+      <c r="T311">
+        <v>1.4</v>
+      </c>
+      <c r="U311">
+        <v>2.75</v>
+      </c>
+      <c r="V311">
+        <v>2.75</v>
+      </c>
+      <c r="W311">
+        <v>1.4</v>
+      </c>
+      <c r="X311">
+        <v>8</v>
+      </c>
+      <c r="Y311">
+        <v>1.08</v>
+      </c>
+      <c r="Z311">
+        <v>2.45</v>
+      </c>
+      <c r="AA311">
+        <v>3.5</v>
+      </c>
+      <c r="AB311">
+        <v>2.75</v>
+      </c>
+      <c r="AC311">
+        <v>1.05</v>
+      </c>
+      <c r="AD311">
+        <v>9</v>
+      </c>
+      <c r="AE311">
+        <v>1.3</v>
+      </c>
+      <c r="AF311">
+        <v>3.45</v>
+      </c>
+      <c r="AG311">
+        <v>1.82</v>
+      </c>
+      <c r="AH311">
+        <v>1.87</v>
+      </c>
+      <c r="AI311">
+        <v>1.67</v>
+      </c>
+      <c r="AJ311">
+        <v>2.1</v>
+      </c>
+      <c r="AK311">
+        <v>1.42</v>
+      </c>
+      <c r="AL311">
+        <v>1.25</v>
+      </c>
+      <c r="AM311">
+        <v>1.53</v>
+      </c>
+      <c r="AN311">
+        <v>1.55</v>
+      </c>
+      <c r="AO311">
+        <v>0.5</v>
+      </c>
+      <c r="AP311">
+        <v>1.5</v>
+      </c>
+      <c r="AQ311">
+        <v>0.54</v>
+      </c>
+      <c r="AR311">
+        <v>1.49</v>
+      </c>
+      <c r="AS311">
+        <v>0.96</v>
+      </c>
+      <c r="AT311">
+        <v>2.45</v>
+      </c>
+      <c r="AU311">
+        <v>3</v>
+      </c>
+      <c r="AV311">
+        <v>5</v>
+      </c>
+      <c r="AW311">
+        <v>7</v>
+      </c>
+      <c r="AX311">
+        <v>6</v>
+      </c>
+      <c r="AY311">
+        <v>12</v>
+      </c>
+      <c r="AZ311">
+        <v>12</v>
+      </c>
+      <c r="BA311">
+        <v>6</v>
+      </c>
+      <c r="BB311">
+        <v>3</v>
+      </c>
+      <c r="BC311">
+        <v>9</v>
+      </c>
+      <c r="BD311">
+        <v>1.49</v>
+      </c>
+      <c r="BE311">
+        <v>7</v>
+      </c>
+      <c r="BF311">
+        <v>2.8</v>
+      </c>
+      <c r="BG311">
+        <v>1.07</v>
+      </c>
+      <c r="BH311">
+        <v>6.27</v>
+      </c>
+      <c r="BI311">
+        <v>1.21</v>
+      </c>
+      <c r="BJ311">
+        <v>3.96</v>
+      </c>
+      <c r="BK311">
+        <v>1.41</v>
+      </c>
+      <c r="BL311">
+        <v>2.78</v>
+      </c>
+      <c r="BM311">
+        <v>1.71</v>
+      </c>
+      <c r="BN311">
+        <v>2.14</v>
+      </c>
+      <c r="BO311">
+        <v>2.09</v>
+      </c>
+      <c r="BP311">
+        <v>1.74</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1934" uniqueCount="399">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -907,6 +907,9 @@
     <t>['7']</t>
   </si>
   <si>
+    <t>['61', '71', '76']</t>
+  </si>
+  <si>
     <t>['67', '88']</t>
   </si>
   <si>
@@ -1569,7 +1572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP311"/>
+  <dimension ref="A1:BP312"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1825,7 +1828,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -1903,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ2">
         <v>0.5</v>
@@ -2031,7 +2034,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2237,7 +2240,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2649,7 +2652,7 @@
         <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -3061,7 +3064,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q8">
         <v>1.83</v>
@@ -3142,7 +3145,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ8">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3267,7 +3270,7 @@
         <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3473,7 +3476,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -4091,7 +4094,7 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4297,7 +4300,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -5121,7 +5124,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -5739,7 +5742,7 @@
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5945,7 +5948,7 @@
         <v>111</v>
       </c>
       <c r="P22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q22">
         <v>2.6</v>
@@ -6769,7 +6772,7 @@
         <v>95</v>
       </c>
       <c r="P26" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -7593,7 +7596,7 @@
         <v>117</v>
       </c>
       <c r="P30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -7674,7 +7677,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ30">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR30">
         <v>1.4</v>
@@ -8495,7 +8498,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ34">
         <v>0.54</v>
@@ -8623,7 +8626,7 @@
         <v>122</v>
       </c>
       <c r="P35" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8829,7 +8832,7 @@
         <v>123</v>
       </c>
       <c r="P36" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -9241,7 +9244,7 @@
         <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q38">
         <v>2.4</v>
@@ -9653,7 +9656,7 @@
         <v>95</v>
       </c>
       <c r="P40" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q40">
         <v>4.5</v>
@@ -9859,7 +9862,7 @@
         <v>95</v>
       </c>
       <c r="P41" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -10271,7 +10274,7 @@
         <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q43">
         <v>4.33</v>
@@ -11713,7 +11716,7 @@
         <v>95</v>
       </c>
       <c r="P50" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -12949,7 +12952,7 @@
         <v>135</v>
       </c>
       <c r="P56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q56">
         <v>4.5</v>
@@ -13645,7 +13648,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ59">
         <v>1.08</v>
@@ -13773,7 +13776,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13979,7 +13982,7 @@
         <v>95</v>
       </c>
       <c r="P61" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q61">
         <v>4.33</v>
@@ -14185,7 +14188,7 @@
         <v>139</v>
       </c>
       <c r="P62" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -15009,7 +15012,7 @@
         <v>95</v>
       </c>
       <c r="P66" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q66">
         <v>5.5</v>
@@ -15627,7 +15630,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q69">
         <v>2.05</v>
@@ -15708,7 +15711,7 @@
         <v>2</v>
       </c>
       <c r="AQ69">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR69">
         <v>1.36</v>
@@ -16039,7 +16042,7 @@
         <v>147</v>
       </c>
       <c r="P71" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -16657,7 +16660,7 @@
         <v>149</v>
       </c>
       <c r="P74" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q74">
         <v>3.9</v>
@@ -16941,7 +16944,7 @@
         <v>1.67</v>
       </c>
       <c r="AP75">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -17069,7 +17072,7 @@
         <v>151</v>
       </c>
       <c r="P76" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17275,7 +17278,7 @@
         <v>152</v>
       </c>
       <c r="P77" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q77">
         <v>3.75</v>
@@ -17687,7 +17690,7 @@
         <v>153</v>
       </c>
       <c r="P79" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -18099,7 +18102,7 @@
         <v>155</v>
       </c>
       <c r="P81" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q81">
         <v>2.63</v>
@@ -19747,7 +19750,7 @@
         <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q89">
         <v>2.1</v>
@@ -20365,7 +20368,7 @@
         <v>162</v>
       </c>
       <c r="P92" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q92">
         <v>2.85</v>
@@ -21270,7 +21273,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ96">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR96">
         <v>1.07</v>
@@ -21601,7 +21604,7 @@
         <v>165</v>
       </c>
       <c r="P98" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -22425,7 +22428,7 @@
         <v>119</v>
       </c>
       <c r="P102" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q102">
         <v>2.5</v>
@@ -22631,7 +22634,7 @@
         <v>168</v>
       </c>
       <c r="P103" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -25103,7 +25106,7 @@
         <v>95</v>
       </c>
       <c r="P115" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q115">
         <v>3.4</v>
@@ -25309,7 +25312,7 @@
         <v>178</v>
       </c>
       <c r="P116" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25390,7 +25393,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ116">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR116">
         <v>1.81</v>
@@ -25721,7 +25724,7 @@
         <v>95</v>
       </c>
       <c r="P118" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
@@ -26005,7 +26008,7 @@
         <v>0.75</v>
       </c>
       <c r="AP119">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ119">
         <v>1.08</v>
@@ -26751,7 +26754,7 @@
         <v>182</v>
       </c>
       <c r="P123" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -26957,7 +26960,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q124">
         <v>3</v>
@@ -27450,7 +27453,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ126">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR126">
         <v>1.35</v>
@@ -28271,7 +28274,7 @@
         <v>2</v>
       </c>
       <c r="AP130">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ130">
         <v>1.36</v>
@@ -28399,7 +28402,7 @@
         <v>187</v>
       </c>
       <c r="P131" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -29017,7 +29020,7 @@
         <v>162</v>
       </c>
       <c r="P134" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29429,7 +29432,7 @@
         <v>190</v>
       </c>
       <c r="P136" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -29841,7 +29844,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q138">
         <v>3.25</v>
@@ -30665,7 +30668,7 @@
         <v>194</v>
       </c>
       <c r="P142" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q142">
         <v>3.25</v>
@@ -31283,7 +31286,7 @@
         <v>196</v>
       </c>
       <c r="P145" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q145">
         <v>3.2</v>
@@ -31489,7 +31492,7 @@
         <v>197</v>
       </c>
       <c r="P146" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31695,7 +31698,7 @@
         <v>198</v>
       </c>
       <c r="P147" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q147">
         <v>3.4</v>
@@ -31901,7 +31904,7 @@
         <v>199</v>
       </c>
       <c r="P148" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q148">
         <v>2.88</v>
@@ -32107,7 +32110,7 @@
         <v>95</v>
       </c>
       <c r="P149" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32185,7 +32188,7 @@
         <v>1.33</v>
       </c>
       <c r="AP149">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ149">
         <v>1.79</v>
@@ -32313,7 +32316,7 @@
         <v>200</v>
       </c>
       <c r="P150" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q150">
         <v>2.25</v>
@@ -32394,7 +32397,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ150">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR150">
         <v>1.35</v>
@@ -32725,7 +32728,7 @@
         <v>132</v>
       </c>
       <c r="P152" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33137,7 +33140,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33549,7 +33552,7 @@
         <v>95</v>
       </c>
       <c r="P156" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q156">
         <v>2.25</v>
@@ -33961,7 +33964,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q158">
         <v>4.75</v>
@@ -34579,7 +34582,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q161">
         <v>3.75</v>
@@ -35072,7 +35075,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ163">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR163">
         <v>1.59</v>
@@ -35403,7 +35406,7 @@
         <v>95</v>
       </c>
       <c r="P165" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -35481,7 +35484,7 @@
         <v>0.67</v>
       </c>
       <c r="AP165">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ165">
         <v>0.75</v>
@@ -35609,7 +35612,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q166">
         <v>2.5</v>
@@ -36845,7 +36848,7 @@
         <v>197</v>
       </c>
       <c r="P172" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37051,7 +37054,7 @@
         <v>172</v>
       </c>
       <c r="P173" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37463,7 +37466,7 @@
         <v>214</v>
       </c>
       <c r="P175" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q175">
         <v>2.63</v>
@@ -37875,7 +37878,7 @@
         <v>216</v>
       </c>
       <c r="P177" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38493,7 +38496,7 @@
         <v>142</v>
       </c>
       <c r="P180" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q180">
         <v>3.75</v>
@@ -38905,7 +38908,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q182">
         <v>3.4</v>
@@ -39317,7 +39320,7 @@
         <v>220</v>
       </c>
       <c r="P184" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q184">
         <v>3.2</v>
@@ -40141,7 +40144,7 @@
         <v>223</v>
       </c>
       <c r="P188" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q188">
         <v>5.5</v>
@@ -40759,7 +40762,7 @@
         <v>225</v>
       </c>
       <c r="P191" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -40965,7 +40968,7 @@
         <v>226</v>
       </c>
       <c r="P192" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q192">
         <v>5</v>
@@ -41789,7 +41792,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q196">
         <v>3</v>
@@ -42819,7 +42822,7 @@
         <v>95</v>
       </c>
       <c r="P201" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q201">
         <v>2.6</v>
@@ -44055,7 +44058,7 @@
         <v>233</v>
       </c>
       <c r="P207" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q207">
         <v>2.05</v>
@@ -44339,7 +44342,7 @@
         <v>1.63</v>
       </c>
       <c r="AP208">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ208">
         <v>1.62</v>
@@ -44673,7 +44676,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44879,7 +44882,7 @@
         <v>235</v>
       </c>
       <c r="P211" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q211">
         <v>2.38</v>
@@ -45291,7 +45294,7 @@
         <v>237</v>
       </c>
       <c r="P213" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q213">
         <v>2.4</v>
@@ -45372,7 +45375,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ213">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR213">
         <v>1.34</v>
@@ -45497,7 +45500,7 @@
         <v>95</v>
       </c>
       <c r="P214" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45703,7 +45706,7 @@
         <v>178</v>
       </c>
       <c r="P215" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q215">
         <v>3.2</v>
@@ -47557,7 +47560,7 @@
         <v>244</v>
       </c>
       <c r="P224" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q224">
         <v>2.88</v>
@@ -47763,7 +47766,7 @@
         <v>245</v>
       </c>
       <c r="P225" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q225">
         <v>3.2</v>
@@ -48175,7 +48178,7 @@
         <v>95</v>
       </c>
       <c r="P227" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q227">
         <v>3</v>
@@ -48587,7 +48590,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -49411,7 +49414,7 @@
         <v>95</v>
       </c>
       <c r="P233" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49617,7 +49620,7 @@
         <v>95</v>
       </c>
       <c r="P234" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -50522,7 +50525,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ238">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR238">
         <v>1.39</v>
@@ -50853,7 +50856,7 @@
         <v>252</v>
       </c>
       <c r="P240" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q240">
         <v>2.5</v>
@@ -51471,7 +51474,7 @@
         <v>253</v>
       </c>
       <c r="P243" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q243">
         <v>3.1</v>
@@ -51677,7 +51680,7 @@
         <v>254</v>
       </c>
       <c r="P244" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -52089,7 +52092,7 @@
         <v>244</v>
       </c>
       <c r="P246" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52373,7 +52376,7 @@
         <v>0.44</v>
       </c>
       <c r="AP247">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ247">
         <v>0.31</v>
@@ -52707,7 +52710,7 @@
         <v>131</v>
       </c>
       <c r="P249" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -53325,7 +53328,7 @@
         <v>260</v>
       </c>
       <c r="P252" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q252">
         <v>3.2</v>
@@ -53737,7 +53740,7 @@
         <v>262</v>
       </c>
       <c r="P254" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -54767,7 +54770,7 @@
         <v>266</v>
       </c>
       <c r="P259" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q259">
         <v>5.5</v>
@@ -54973,7 +54976,7 @@
         <v>267</v>
       </c>
       <c r="P260" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
@@ -55385,7 +55388,7 @@
         <v>269</v>
       </c>
       <c r="P262" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q262">
         <v>3.5</v>
@@ -56003,7 +56006,7 @@
         <v>95</v>
       </c>
       <c r="P265" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56209,7 +56212,7 @@
         <v>271</v>
       </c>
       <c r="P266" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q266">
         <v>2.25</v>
@@ -56827,7 +56830,7 @@
         <v>274</v>
       </c>
       <c r="P269" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -56905,7 +56908,7 @@
         <v>1.64</v>
       </c>
       <c r="AP269">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ269">
         <v>1.46</v>
@@ -57114,7 +57117,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ270">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR270">
         <v>1.47</v>
@@ -57445,7 +57448,7 @@
         <v>277</v>
       </c>
       <c r="P272" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q272">
         <v>3.5</v>
@@ -57651,7 +57654,7 @@
         <v>95</v>
       </c>
       <c r="P273" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q273">
         <v>6</v>
@@ -58063,7 +58066,7 @@
         <v>278</v>
       </c>
       <c r="P275" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q275">
         <v>3.2</v>
@@ -58269,7 +58272,7 @@
         <v>279</v>
       </c>
       <c r="P276" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q276">
         <v>2.5</v>
@@ -58475,7 +58478,7 @@
         <v>280</v>
       </c>
       <c r="P277" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58681,7 +58684,7 @@
         <v>281</v>
       </c>
       <c r="P278" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q278">
         <v>2.6</v>
@@ -59377,7 +59380,7 @@
         <v>0.73</v>
       </c>
       <c r="AP281">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ281">
         <v>0.92</v>
@@ -59792,7 +59795,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ283">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR283">
         <v>1.45</v>
@@ -60535,7 +60538,7 @@
         <v>285</v>
       </c>
       <c r="P287" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q287">
         <v>3.75</v>
@@ -60947,7 +60950,7 @@
         <v>286</v>
       </c>
       <c r="P289" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q289">
         <v>2.38</v>
@@ -61153,7 +61156,7 @@
         <v>287</v>
       </c>
       <c r="P290" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61771,7 +61774,7 @@
         <v>198</v>
       </c>
       <c r="P293" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q293">
         <v>1.95</v>
@@ -61977,7 +61980,7 @@
         <v>289</v>
       </c>
       <c r="P294" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q294">
         <v>3.4</v>
@@ -62595,7 +62598,7 @@
         <v>290</v>
       </c>
       <c r="P297" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -63291,7 +63294,7 @@
         <v>1.92</v>
       </c>
       <c r="AP300">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ300">
         <v>2</v>
@@ -63419,7 +63422,7 @@
         <v>291</v>
       </c>
       <c r="P301" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q301">
         <v>3</v>
@@ -63625,7 +63628,7 @@
         <v>204</v>
       </c>
       <c r="P302" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -64037,7 +64040,7 @@
         <v>293</v>
       </c>
       <c r="P304" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q304">
         <v>3.75</v>
@@ -64243,7 +64246,7 @@
         <v>294</v>
       </c>
       <c r="P305" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q305">
         <v>6.5</v>
@@ -64655,7 +64658,7 @@
         <v>200</v>
       </c>
       <c r="P307" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q307">
         <v>2.2</v>
@@ -64942,7 +64945,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ308">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR308">
         <v>1.55</v>
@@ -65273,7 +65276,7 @@
         <v>231</v>
       </c>
       <c r="P310" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
@@ -65636,6 +65639,212 @@
       </c>
       <c r="BP311">
         <v>1.74</v>
+      </c>
+    </row>
+    <row r="312" spans="1:68">
+      <c r="A312" s="1">
+        <v>311</v>
+      </c>
+      <c r="B312">
+        <v>7478924</v>
+      </c>
+      <c r="C312" t="s">
+        <v>68</v>
+      </c>
+      <c r="D312" t="s">
+        <v>69</v>
+      </c>
+      <c r="E312" s="2">
+        <v>45672.69791666666</v>
+      </c>
+      <c r="F312">
+        <v>16</v>
+      </c>
+      <c r="G312" t="s">
+        <v>70</v>
+      </c>
+      <c r="H312" t="s">
+        <v>85</v>
+      </c>
+      <c r="I312">
+        <v>0</v>
+      </c>
+      <c r="J312">
+        <v>0</v>
+      </c>
+      <c r="K312">
+        <v>0</v>
+      </c>
+      <c r="L312">
+        <v>3</v>
+      </c>
+      <c r="M312">
+        <v>0</v>
+      </c>
+      <c r="N312">
+        <v>3</v>
+      </c>
+      <c r="O312" t="s">
+        <v>297</v>
+      </c>
+      <c r="P312" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q312">
+        <v>2.25</v>
+      </c>
+      <c r="R312">
+        <v>2.25</v>
+      </c>
+      <c r="S312">
+        <v>5</v>
+      </c>
+      <c r="T312">
+        <v>1.36</v>
+      </c>
+      <c r="U312">
+        <v>3</v>
+      </c>
+      <c r="V312">
+        <v>2.75</v>
+      </c>
+      <c r="W312">
+        <v>1.4</v>
+      </c>
+      <c r="X312">
+        <v>7</v>
+      </c>
+      <c r="Y312">
+        <v>1.1</v>
+      </c>
+      <c r="Z312">
+        <v>1.71</v>
+      </c>
+      <c r="AA312">
+        <v>3.46</v>
+      </c>
+      <c r="AB312">
+        <v>4.36</v>
+      </c>
+      <c r="AC312">
+        <v>1.04</v>
+      </c>
+      <c r="AD312">
+        <v>13</v>
+      </c>
+      <c r="AE312">
+        <v>1.28</v>
+      </c>
+      <c r="AF312">
+        <v>3.75</v>
+      </c>
+      <c r="AG312">
+        <v>2.01</v>
+      </c>
+      <c r="AH312">
+        <v>1.83</v>
+      </c>
+      <c r="AI312">
+        <v>1.8</v>
+      </c>
+      <c r="AJ312">
+        <v>1.91</v>
+      </c>
+      <c r="AK312">
+        <v>1.17</v>
+      </c>
+      <c r="AL312">
+        <v>1.22</v>
+      </c>
+      <c r="AM312">
+        <v>2.25</v>
+      </c>
+      <c r="AN312">
+        <v>1.77</v>
+      </c>
+      <c r="AO312">
+        <v>0.54</v>
+      </c>
+      <c r="AP312">
+        <v>1.86</v>
+      </c>
+      <c r="AQ312">
+        <v>0.5</v>
+      </c>
+      <c r="AR312">
+        <v>1.26</v>
+      </c>
+      <c r="AS312">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT312">
+        <v>2.2</v>
+      </c>
+      <c r="AU312">
+        <v>6</v>
+      </c>
+      <c r="AV312">
+        <v>3</v>
+      </c>
+      <c r="AW312">
+        <v>3</v>
+      </c>
+      <c r="AX312">
+        <v>4</v>
+      </c>
+      <c r="AY312">
+        <v>10</v>
+      </c>
+      <c r="AZ312">
+        <v>7</v>
+      </c>
+      <c r="BA312">
+        <v>5</v>
+      </c>
+      <c r="BB312">
+        <v>6</v>
+      </c>
+      <c r="BC312">
+        <v>11</v>
+      </c>
+      <c r="BD312">
+        <v>1.55</v>
+      </c>
+      <c r="BE312">
+        <v>6.75</v>
+      </c>
+      <c r="BF312">
+        <v>2.65</v>
+      </c>
+      <c r="BG312">
+        <v>1.18</v>
+      </c>
+      <c r="BH312">
+        <v>4.1</v>
+      </c>
+      <c r="BI312">
+        <v>1.34</v>
+      </c>
+      <c r="BJ312">
+        <v>2.9</v>
+      </c>
+      <c r="BK312">
+        <v>1.57</v>
+      </c>
+      <c r="BL312">
+        <v>2.23</v>
+      </c>
+      <c r="BM312">
+        <v>1.9</v>
+      </c>
+      <c r="BN312">
+        <v>1.79</v>
+      </c>
+      <c r="BO312">
+        <v>2.35</v>
+      </c>
+      <c r="BP312">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1934" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="403">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -910,6 +910,15 @@
     <t>['61', '71', '76']</t>
   </si>
   <si>
+    <t>['47', '51', '67']</t>
+  </si>
+  <si>
+    <t>['22', '59']</t>
+  </si>
+  <si>
+    <t>['54', '82']</t>
+  </si>
+  <si>
     <t>['67', '88']</t>
   </si>
   <si>
@@ -1211,6 +1220,9 @@
   </si>
   <si>
     <t>['46', '62', '72']</t>
+  </si>
+  <si>
+    <t>['4', '66']</t>
   </si>
 </sst>
 </file>
@@ -1572,7 +1584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP312"/>
+  <dimension ref="A1:BP323"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1828,7 +1840,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -2034,7 +2046,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2240,7 +2252,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2524,10 +2536,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ5">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2652,7 +2664,7 @@
         <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -2730,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ6">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3064,7 +3076,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q8">
         <v>1.83</v>
@@ -3270,7 +3282,7 @@
         <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3351,7 +3363,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ9">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3476,7 +3488,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -3554,10 +3566,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ10">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3763,7 +3775,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ11">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4094,7 +4106,7 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4172,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ13">
         <v>2</v>
@@ -4300,7 +4312,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -4378,7 +4390,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ14">
         <v>0.54</v>
@@ -4584,7 +4596,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ15">
         <v>1.62</v>
@@ -4790,10 +4802,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ16">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4996,7 +5008,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ17">
         <v>0.31</v>
@@ -5124,7 +5136,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -5202,10 +5214,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5411,7 +5423,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ19">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5617,7 +5629,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ20">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5742,7 +5754,7 @@
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5948,7 +5960,7 @@
         <v>111</v>
       </c>
       <c r="P22" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q22">
         <v>2.6</v>
@@ -6029,7 +6041,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ22">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6232,7 +6244,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ23">
         <v>0.77</v>
@@ -6438,10 +6450,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ24">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6772,7 +6784,7 @@
         <v>95</v>
       </c>
       <c r="P26" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -7596,7 +7608,7 @@
         <v>117</v>
       </c>
       <c r="P30" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -8626,7 +8638,7 @@
         <v>122</v>
       </c>
       <c r="P35" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8832,7 +8844,7 @@
         <v>123</v>
       </c>
       <c r="P36" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -9244,7 +9256,7 @@
         <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q38">
         <v>2.4</v>
@@ -9322,10 +9334,10 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR38">
         <v>1.01</v>
@@ -9528,10 +9540,10 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ39">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR39">
         <v>1.03</v>
@@ -9656,7 +9668,7 @@
         <v>95</v>
       </c>
       <c r="P40" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q40">
         <v>4.5</v>
@@ -9734,10 +9746,10 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ40">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR40">
         <v>1.28</v>
@@ -9862,7 +9874,7 @@
         <v>95</v>
       </c>
       <c r="P41" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9940,10 +9952,10 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR41">
         <v>2.58</v>
@@ -10146,10 +10158,10 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ42">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>0.8100000000000001</v>
@@ -10274,7 +10286,7 @@
         <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q43">
         <v>4.33</v>
@@ -10352,10 +10364,10 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ43">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR43">
         <v>1.59</v>
@@ -10558,10 +10570,10 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ44">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR44">
         <v>1.62</v>
@@ -10764,7 +10776,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ45">
         <v>1.42</v>
@@ -10973,7 +10985,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ46">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR46">
         <v>2.31</v>
@@ -11176,10 +11188,10 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ47">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR47">
         <v>0.68</v>
@@ -11382,10 +11394,10 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ48">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR48">
         <v>1.23</v>
@@ -11588,10 +11600,10 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ49">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR49">
         <v>1.17</v>
@@ -11716,7 +11728,7 @@
         <v>95</v>
       </c>
       <c r="P50" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -12206,7 +12218,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ52">
         <v>0.31</v>
@@ -12412,10 +12424,10 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ53">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR53">
         <v>1.18</v>
@@ -12618,7 +12630,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ54">
         <v>0.77</v>
@@ -12952,7 +12964,7 @@
         <v>135</v>
       </c>
       <c r="P56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q56">
         <v>4.5</v>
@@ -13030,10 +13042,10 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ56">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR56">
         <v>1.63</v>
@@ -13239,7 +13251,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR57">
         <v>1.82</v>
@@ -13445,7 +13457,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR58">
         <v>1.35</v>
@@ -13651,7 +13663,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ59">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR59">
         <v>1.55</v>
@@ -13776,7 +13788,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13857,7 +13869,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ60">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR60">
         <v>1.85</v>
@@ -13982,7 +13994,7 @@
         <v>95</v>
       </c>
       <c r="P61" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q61">
         <v>4.33</v>
@@ -14060,7 +14072,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ61">
         <v>1.36</v>
@@ -14188,7 +14200,7 @@
         <v>139</v>
       </c>
       <c r="P62" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14269,7 +14281,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ62">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR62">
         <v>0.99</v>
@@ -14475,7 +14487,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR63">
         <v>1.34</v>
@@ -14681,7 +14693,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ64">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR64">
         <v>1.36</v>
@@ -15012,7 +15024,7 @@
         <v>95</v>
       </c>
       <c r="P66" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q66">
         <v>5.5</v>
@@ -15090,7 +15102,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ66">
         <v>1.62</v>
@@ -15296,7 +15308,7 @@
         <v>0.5</v>
       </c>
       <c r="AP67">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ67">
         <v>0.21</v>
@@ -15630,7 +15642,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q69">
         <v>2.05</v>
@@ -15708,7 +15720,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ69">
         <v>0.5</v>
@@ -15914,7 +15926,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ70">
         <v>1.42</v>
@@ -16042,7 +16054,7 @@
         <v>147</v>
       </c>
       <c r="P71" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -16120,10 +16132,10 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ71">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR71">
         <v>2.05</v>
@@ -16326,7 +16338,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ72">
         <v>0.5</v>
@@ -16535,7 +16547,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ73">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR73">
         <v>0.68</v>
@@ -16660,7 +16672,7 @@
         <v>149</v>
       </c>
       <c r="P74" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q74">
         <v>3.9</v>
@@ -16738,7 +16750,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ74">
         <v>0.31</v>
@@ -16947,7 +16959,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ75">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR75">
         <v>1.35</v>
@@ -17072,7 +17084,7 @@
         <v>151</v>
       </c>
       <c r="P76" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17150,10 +17162,10 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ76">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR76">
         <v>1.2</v>
@@ -17278,7 +17290,7 @@
         <v>152</v>
       </c>
       <c r="P77" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q77">
         <v>3.75</v>
@@ -17562,7 +17574,7 @@
         <v>2</v>
       </c>
       <c r="AP78">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ78">
         <v>2</v>
@@ -17690,7 +17702,7 @@
         <v>153</v>
       </c>
       <c r="P79" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17771,7 +17783,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ79">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR79">
         <v>1.74</v>
@@ -17977,7 +17989,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ80">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR80">
         <v>1.8</v>
@@ -18102,7 +18114,7 @@
         <v>155</v>
       </c>
       <c r="P81" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q81">
         <v>2.63</v>
@@ -18180,10 +18192,10 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ81">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR81">
         <v>1.39</v>
@@ -18592,7 +18604,7 @@
         <v>2.33</v>
       </c>
       <c r="AP83">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ83">
         <v>1.79</v>
@@ -19007,7 +19019,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ85">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR85">
         <v>1.34</v>
@@ -19210,7 +19222,7 @@
         <v>0.33</v>
       </c>
       <c r="AP86">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ86">
         <v>0.21</v>
@@ -19416,7 +19428,7 @@
         <v>0.67</v>
       </c>
       <c r="AP87">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ87">
         <v>0.83</v>
@@ -19622,10 +19634,10 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ88">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR88">
         <v>2.03</v>
@@ -19750,7 +19762,7 @@
         <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q89">
         <v>2.1</v>
@@ -19828,7 +19840,7 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ89">
         <v>0.54</v>
@@ -20368,7 +20380,7 @@
         <v>162</v>
       </c>
       <c r="P92" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q92">
         <v>2.85</v>
@@ -20449,7 +20461,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ92">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR92">
         <v>1.63</v>
@@ -20652,10 +20664,10 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ93">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR93">
         <v>1.4</v>
@@ -20858,10 +20870,10 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ94">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR94">
         <v>1.56</v>
@@ -21067,7 +21079,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ95">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR95">
         <v>0.98</v>
@@ -21604,7 +21616,7 @@
         <v>165</v>
       </c>
       <c r="P98" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21888,7 +21900,7 @@
         <v>0.25</v>
       </c>
       <c r="AP99">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ99">
         <v>0.54</v>
@@ -22097,7 +22109,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ100">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR100">
         <v>1.37</v>
@@ -22300,10 +22312,10 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ101">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR101">
         <v>1.42</v>
@@ -22428,7 +22440,7 @@
         <v>119</v>
       </c>
       <c r="P102" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q102">
         <v>2.5</v>
@@ -22506,7 +22518,7 @@
         <v>0.25</v>
       </c>
       <c r="AP102">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ102">
         <v>1.42</v>
@@ -22634,7 +22646,7 @@
         <v>168</v>
       </c>
       <c r="P103" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22712,10 +22724,10 @@
         <v>0.75</v>
       </c>
       <c r="AP103">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ103">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR103">
         <v>1.59</v>
@@ -22918,7 +22930,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ104">
         <v>0.31</v>
@@ -23127,7 +23139,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ105">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR105">
         <v>1.25</v>
@@ -23333,7 +23345,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ106">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR106">
         <v>1.67</v>
@@ -23536,7 +23548,7 @@
         <v>0.5</v>
       </c>
       <c r="AP107">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ107">
         <v>0.83</v>
@@ -23742,10 +23754,10 @@
         <v>1.25</v>
       </c>
       <c r="AP108">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR108">
         <v>1.27</v>
@@ -24360,7 +24372,7 @@
         <v>0.25</v>
       </c>
       <c r="AP111">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ111">
         <v>0.21</v>
@@ -24566,10 +24578,10 @@
         <v>0.75</v>
       </c>
       <c r="AP112">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ112">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR112">
         <v>1.26</v>
@@ -24978,7 +24990,7 @@
         <v>2.25</v>
       </c>
       <c r="AP114">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ114">
         <v>1.36</v>
@@ -25106,7 +25118,7 @@
         <v>95</v>
       </c>
       <c r="P115" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q115">
         <v>3.4</v>
@@ -25312,7 +25324,7 @@
         <v>178</v>
       </c>
       <c r="P116" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25599,7 +25611,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ117">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR117">
         <v>1.44</v>
@@ -25724,7 +25736,7 @@
         <v>95</v>
       </c>
       <c r="P118" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
@@ -25805,7 +25817,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ118">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR118">
         <v>1.94</v>
@@ -26011,7 +26023,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ119">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR119">
         <v>1.51</v>
@@ -26214,7 +26226,7 @@
         <v>0</v>
       </c>
       <c r="AP120">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ120">
         <v>0.5</v>
@@ -26423,7 +26435,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ121">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR121">
         <v>1.53</v>
@@ -26629,7 +26641,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ122">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR122">
         <v>1.52</v>
@@ -26754,7 +26766,7 @@
         <v>182</v>
       </c>
       <c r="P123" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -26835,7 +26847,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ123">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -26960,7 +26972,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q124">
         <v>3</v>
@@ -27041,7 +27053,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ124">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR124">
         <v>1.42</v>
@@ -27247,7 +27259,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ125">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR125">
         <v>1.76</v>
@@ -27450,7 +27462,7 @@
         <v>1</v>
       </c>
       <c r="AP126">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ126">
         <v>0.5</v>
@@ -27656,7 +27668,7 @@
         <v>0.2</v>
       </c>
       <c r="AP127">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ127">
         <v>0.5</v>
@@ -28402,7 +28414,7 @@
         <v>187</v>
       </c>
       <c r="P131" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28480,10 +28492,10 @@
         <v>1.8</v>
       </c>
       <c r="AP131">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ131">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR131">
         <v>1.3</v>
@@ -28686,7 +28698,7 @@
         <v>0.2</v>
       </c>
       <c r="AP132">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ132">
         <v>0.21</v>
@@ -29020,7 +29032,7 @@
         <v>162</v>
       </c>
       <c r="P134" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29098,7 +29110,7 @@
         <v>0.8</v>
       </c>
       <c r="AP134">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ134">
         <v>1.42</v>
@@ -29432,7 +29444,7 @@
         <v>190</v>
       </c>
       <c r="P136" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -29510,7 +29522,7 @@
         <v>0.8</v>
       </c>
       <c r="AP136">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ136">
         <v>0.31</v>
@@ -29719,7 +29731,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ137">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR137">
         <v>1.56</v>
@@ -29844,7 +29856,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q138">
         <v>3.25</v>
@@ -30128,7 +30140,7 @@
         <v>0.4</v>
       </c>
       <c r="AP139">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ139">
         <v>0.77</v>
@@ -30540,10 +30552,10 @@
         <v>0.8</v>
       </c>
       <c r="AP141">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ141">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR141">
         <v>1.59</v>
@@ -30668,7 +30680,7 @@
         <v>194</v>
       </c>
       <c r="P142" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q142">
         <v>3.25</v>
@@ -30746,10 +30758,10 @@
         <v>0.4</v>
       </c>
       <c r="AP142">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ142">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR142">
         <v>1.64</v>
@@ -30952,10 +30964,10 @@
         <v>1.4</v>
       </c>
       <c r="AP143">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ143">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR143">
         <v>1.28</v>
@@ -31158,10 +31170,10 @@
         <v>1</v>
       </c>
       <c r="AP144">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ144">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR144">
         <v>1.29</v>
@@ -31286,7 +31298,7 @@
         <v>196</v>
       </c>
       <c r="P145" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q145">
         <v>3.2</v>
@@ -31367,7 +31379,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ145">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR145">
         <v>1.49</v>
@@ -31492,7 +31504,7 @@
         <v>197</v>
       </c>
       <c r="P146" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31570,7 +31582,7 @@
         <v>1.83</v>
       </c>
       <c r="AP146">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ146">
         <v>1.36</v>
@@ -31698,7 +31710,7 @@
         <v>198</v>
       </c>
       <c r="P147" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q147">
         <v>3.4</v>
@@ -31776,10 +31788,10 @@
         <v>0.67</v>
       </c>
       <c r="AP147">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ147">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR147">
         <v>1.08</v>
@@ -31904,7 +31916,7 @@
         <v>199</v>
       </c>
       <c r="P148" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q148">
         <v>2.88</v>
@@ -32110,7 +32122,7 @@
         <v>95</v>
       </c>
       <c r="P149" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32316,7 +32328,7 @@
         <v>200</v>
       </c>
       <c r="P150" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q150">
         <v>2.25</v>
@@ -32600,10 +32612,10 @@
         <v>1.33</v>
       </c>
       <c r="AP151">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ151">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR151">
         <v>1.54</v>
@@ -32728,7 +32740,7 @@
         <v>132</v>
       </c>
       <c r="P152" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32809,7 +32821,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ152">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR152">
         <v>1.21</v>
@@ -33015,7 +33027,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ153">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR153">
         <v>1.73</v>
@@ -33140,7 +33152,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33221,7 +33233,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ154">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR154">
         <v>1.43</v>
@@ -33552,7 +33564,7 @@
         <v>95</v>
       </c>
       <c r="P156" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q156">
         <v>2.25</v>
@@ -33836,7 +33848,7 @@
         <v>1.83</v>
       </c>
       <c r="AP157">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ157">
         <v>2</v>
@@ -33964,7 +33976,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q158">
         <v>4.75</v>
@@ -34045,7 +34057,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ158">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR158">
         <v>1.74</v>
@@ -34251,7 +34263,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ159">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR159">
         <v>1.46</v>
@@ -34454,10 +34466,10 @@
         <v>1.33</v>
       </c>
       <c r="AP160">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ160">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR160">
         <v>1.05</v>
@@ -34582,7 +34594,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q161">
         <v>3.75</v>
@@ -34869,7 +34881,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ162">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR162">
         <v>1.39</v>
@@ -35072,7 +35084,7 @@
         <v>0.86</v>
       </c>
       <c r="AP163">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ163">
         <v>0.5</v>
@@ -35278,7 +35290,7 @@
         <v>1.67</v>
       </c>
       <c r="AP164">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ164">
         <v>1.62</v>
@@ -35406,7 +35418,7 @@
         <v>95</v>
       </c>
       <c r="P165" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -35487,7 +35499,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ165">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR165">
         <v>1.23</v>
@@ -35612,7 +35624,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q166">
         <v>2.5</v>
@@ -35690,7 +35702,7 @@
         <v>0.29</v>
       </c>
       <c r="AP166">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ166">
         <v>0.5</v>
@@ -35896,7 +35908,7 @@
         <v>0.5</v>
       </c>
       <c r="AP167">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ167">
         <v>0.77</v>
@@ -36105,7 +36117,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ168">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR168">
         <v>1.18</v>
@@ -36308,7 +36320,7 @@
         <v>1.57</v>
       </c>
       <c r="AP169">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ169">
         <v>2</v>
@@ -36848,7 +36860,7 @@
         <v>197</v>
       </c>
       <c r="P172" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37054,7 +37066,7 @@
         <v>172</v>
       </c>
       <c r="P173" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37132,10 +37144,10 @@
         <v>0.5</v>
       </c>
       <c r="AP173">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ173">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR173">
         <v>1.5</v>
@@ -37341,7 +37353,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ174">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR174">
         <v>1.88</v>
@@ -37466,7 +37478,7 @@
         <v>214</v>
       </c>
       <c r="P175" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q175">
         <v>2.63</v>
@@ -37750,10 +37762,10 @@
         <v>0.5</v>
       </c>
       <c r="AP176">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ176">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR176">
         <v>1.24</v>
@@ -37878,7 +37890,7 @@
         <v>216</v>
       </c>
       <c r="P177" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -37956,7 +37968,7 @@
         <v>0.14</v>
       </c>
       <c r="AP177">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ177">
         <v>0.21</v>
@@ -38165,7 +38177,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ178">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR178">
         <v>1.46</v>
@@ -38368,7 +38380,7 @@
         <v>1.17</v>
       </c>
       <c r="AP179">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ179">
         <v>1.42</v>
@@ -38496,7 +38508,7 @@
         <v>142</v>
       </c>
       <c r="P180" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q180">
         <v>3.75</v>
@@ -38780,10 +38792,10 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ181">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR181">
         <v>1.38</v>
@@ -38908,7 +38920,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q182">
         <v>3.4</v>
@@ -38986,10 +38998,10 @@
         <v>0.75</v>
       </c>
       <c r="AP182">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ182">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR182">
         <v>1.52</v>
@@ -39320,7 +39332,7 @@
         <v>220</v>
       </c>
       <c r="P184" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q184">
         <v>3.2</v>
@@ -39398,7 +39410,7 @@
         <v>1.75</v>
       </c>
       <c r="AP184">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ184">
         <v>1.79</v>
@@ -39810,10 +39822,10 @@
         <v>1.14</v>
       </c>
       <c r="AP186">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ186">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR186">
         <v>1.39</v>
@@ -40016,10 +40028,10 @@
         <v>1.75</v>
       </c>
       <c r="AP187">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ187">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR187">
         <v>1.36</v>
@@ -40144,7 +40156,7 @@
         <v>223</v>
       </c>
       <c r="P188" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q188">
         <v>5.5</v>
@@ -40222,10 +40234,10 @@
         <v>1.43</v>
       </c>
       <c r="AP188">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ188">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR188">
         <v>1.01</v>
@@ -40637,7 +40649,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ190">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR190">
         <v>1.68</v>
@@ -40762,7 +40774,7 @@
         <v>225</v>
       </c>
       <c r="P191" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -40840,10 +40852,10 @@
         <v>1</v>
       </c>
       <c r="AP191">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ191">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR191">
         <v>1.32</v>
@@ -40968,7 +40980,7 @@
         <v>226</v>
       </c>
       <c r="P192" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q192">
         <v>5</v>
@@ -41255,7 +41267,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ193">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR193">
         <v>1.53</v>
@@ -41461,7 +41473,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ194">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR194">
         <v>1.32</v>
@@ -41664,7 +41676,7 @@
         <v>0.29</v>
       </c>
       <c r="AP195">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ195">
         <v>0.54</v>
@@ -41792,7 +41804,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q196">
         <v>3</v>
@@ -42076,7 +42088,7 @@
         <v>0.88</v>
       </c>
       <c r="AP197">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ197">
         <v>0.79</v>
@@ -42822,7 +42834,7 @@
         <v>95</v>
       </c>
       <c r="P201" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q201">
         <v>2.6</v>
@@ -42900,10 +42912,10 @@
         <v>0.86</v>
       </c>
       <c r="AP201">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ201">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR201">
         <v>1.58</v>
@@ -43109,7 +43121,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ202">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR202">
         <v>1.65</v>
@@ -43312,10 +43324,10 @@
         <v>0.88</v>
       </c>
       <c r="AP203">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ203">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR203">
         <v>1.33</v>
@@ -43518,10 +43530,10 @@
         <v>1.67</v>
       </c>
       <c r="AP204">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ204">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR204">
         <v>1.53</v>
@@ -43727,7 +43739,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ205">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR205">
         <v>1.43</v>
@@ -43930,7 +43942,7 @@
         <v>1</v>
       </c>
       <c r="AP206">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ206">
         <v>0.83</v>
@@ -44058,7 +44070,7 @@
         <v>233</v>
       </c>
       <c r="P207" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q207">
         <v>2.05</v>
@@ -44139,7 +44151,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ207">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR207">
         <v>1.61</v>
@@ -44676,7 +44688,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44882,7 +44894,7 @@
         <v>235</v>
       </c>
       <c r="P211" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q211">
         <v>2.38</v>
@@ -44960,7 +44972,7 @@
         <v>0.5</v>
       </c>
       <c r="AP211">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ211">
         <v>0.77</v>
@@ -45294,7 +45306,7 @@
         <v>237</v>
       </c>
       <c r="P213" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q213">
         <v>2.4</v>
@@ -45500,7 +45512,7 @@
         <v>95</v>
       </c>
       <c r="P214" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45706,7 +45718,7 @@
         <v>178</v>
       </c>
       <c r="P215" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q215">
         <v>3.2</v>
@@ -45784,7 +45796,7 @@
         <v>1.25</v>
       </c>
       <c r="AP215">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ215">
         <v>1.42</v>
@@ -45990,10 +46002,10 @@
         <v>1.63</v>
       </c>
       <c r="AP216">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ216">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR216">
         <v>1.41</v>
@@ -46405,7 +46417,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ218">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR218">
         <v>1.44</v>
@@ -46611,7 +46623,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ219">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR219">
         <v>1.4</v>
@@ -46817,7 +46829,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ220">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR220">
         <v>1.32</v>
@@ -47020,7 +47032,7 @@
         <v>0.78</v>
       </c>
       <c r="AP221">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ221">
         <v>0.79</v>
@@ -47226,10 +47238,10 @@
         <v>1.33</v>
       </c>
       <c r="AP222">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ222">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR222">
         <v>1.32</v>
@@ -47435,7 +47447,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ223">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR223">
         <v>1.71</v>
@@ -47560,7 +47572,7 @@
         <v>244</v>
       </c>
       <c r="P224" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q224">
         <v>2.88</v>
@@ -47638,10 +47650,10 @@
         <v>1.11</v>
       </c>
       <c r="AP224">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ224">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR224">
         <v>1.39</v>
@@ -47766,7 +47778,7 @@
         <v>245</v>
       </c>
       <c r="P225" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q225">
         <v>3.2</v>
@@ -47844,7 +47856,7 @@
         <v>1.67</v>
       </c>
       <c r="AP225">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ225">
         <v>1.79</v>
@@ -48053,7 +48065,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ226">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR226">
         <v>1.51</v>
@@ -48178,7 +48190,7 @@
         <v>95</v>
       </c>
       <c r="P227" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q227">
         <v>3</v>
@@ -48259,7 +48271,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ227">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR227">
         <v>1.42</v>
@@ -48462,10 +48474,10 @@
         <v>0.9</v>
       </c>
       <c r="AP228">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ228">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR228">
         <v>1.37</v>
@@ -48590,7 +48602,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48668,10 +48680,10 @@
         <v>1.1</v>
       </c>
       <c r="AP229">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ229">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR229">
         <v>1.48</v>
@@ -48874,10 +48886,10 @@
         <v>0.89</v>
       </c>
       <c r="AP230">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ230">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR230">
         <v>1.35</v>
@@ -49080,7 +49092,7 @@
         <v>0.6</v>
       </c>
       <c r="AP231">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ231">
         <v>0.5</v>
@@ -49289,7 +49301,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ232">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR232">
         <v>1.9</v>
@@ -49414,7 +49426,7 @@
         <v>95</v>
       </c>
       <c r="P233" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49492,7 +49504,7 @@
         <v>1.6</v>
       </c>
       <c r="AP233">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ233">
         <v>1.79</v>
@@ -49620,7 +49632,7 @@
         <v>95</v>
       </c>
       <c r="P234" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -49698,10 +49710,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP234">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ234">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR234">
         <v>1.65</v>
@@ -49907,7 +49919,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ235">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR235">
         <v>1.35</v>
@@ -50316,7 +50328,7 @@
         <v>1</v>
       </c>
       <c r="AP237">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ237">
         <v>0.79</v>
@@ -50522,7 +50534,7 @@
         <v>0.78</v>
       </c>
       <c r="AP238">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ238">
         <v>0.5</v>
@@ -50856,7 +50868,7 @@
         <v>252</v>
       </c>
       <c r="P240" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q240">
         <v>2.5</v>
@@ -50934,10 +50946,10 @@
         <v>0.89</v>
       </c>
       <c r="AP240">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ240">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR240">
         <v>1.9</v>
@@ -51143,7 +51155,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ241">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR241">
         <v>1.43</v>
@@ -51474,7 +51486,7 @@
         <v>253</v>
       </c>
       <c r="P243" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q243">
         <v>3.1</v>
@@ -51680,7 +51692,7 @@
         <v>254</v>
       </c>
       <c r="P244" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -51761,7 +51773,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ244">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR244">
         <v>1.43</v>
@@ -51964,7 +51976,7 @@
         <v>0.2</v>
       </c>
       <c r="AP245">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ245">
         <v>0.21</v>
@@ -52092,7 +52104,7 @@
         <v>244</v>
       </c>
       <c r="P246" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52170,7 +52182,7 @@
         <v>1.44</v>
       </c>
       <c r="AP246">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ246">
         <v>1.42</v>
@@ -52710,7 +52722,7 @@
         <v>131</v>
       </c>
       <c r="P249" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -52994,7 +53006,7 @@
         <v>0.64</v>
       </c>
       <c r="AP250">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ250">
         <v>0.5</v>
@@ -53203,7 +53215,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ251">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR251">
         <v>1.45</v>
@@ -53328,7 +53340,7 @@
         <v>260</v>
       </c>
       <c r="P252" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q252">
         <v>3.2</v>
@@ -53409,7 +53421,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ252">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR252">
         <v>1.34</v>
@@ -53612,7 +53624,7 @@
         <v>0.91</v>
       </c>
       <c r="AP253">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ253">
         <v>0.79</v>
@@ -53740,7 +53752,7 @@
         <v>262</v>
       </c>
       <c r="P254" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -53821,7 +53833,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ254">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR254">
         <v>1.59</v>
@@ -54024,10 +54036,10 @@
         <v>0.8</v>
       </c>
       <c r="AP255">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ255">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR255">
         <v>1.44</v>
@@ -54230,7 +54242,7 @@
         <v>1.73</v>
       </c>
       <c r="AP256">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ256">
         <v>1.79</v>
@@ -54642,10 +54654,10 @@
         <v>1.5</v>
       </c>
       <c r="AP258">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ258">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR258">
         <v>1.31</v>
@@ -54770,7 +54782,7 @@
         <v>266</v>
       </c>
       <c r="P259" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q259">
         <v>5.5</v>
@@ -54848,10 +54860,10 @@
         <v>1.4</v>
       </c>
       <c r="AP259">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ259">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR259">
         <v>1.48</v>
@@ -54976,7 +54988,7 @@
         <v>267</v>
       </c>
       <c r="P260" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
@@ -55057,7 +55069,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ260">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR260">
         <v>1.65</v>
@@ -55260,10 +55272,10 @@
         <v>1.18</v>
       </c>
       <c r="AP261">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ261">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR261">
         <v>1.34</v>
@@ -55388,7 +55400,7 @@
         <v>269</v>
       </c>
       <c r="P262" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q262">
         <v>3.5</v>
@@ -55466,7 +55478,7 @@
         <v>0.6</v>
       </c>
       <c r="AP262">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ262">
         <v>0.77</v>
@@ -55675,7 +55687,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ263">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR263">
         <v>1.21</v>
@@ -56006,7 +56018,7 @@
         <v>95</v>
       </c>
       <c r="P265" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56084,7 +56096,7 @@
         <v>1.91</v>
       </c>
       <c r="AP265">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ265">
         <v>2</v>
@@ -56212,7 +56224,7 @@
         <v>271</v>
       </c>
       <c r="P266" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q266">
         <v>2.25</v>
@@ -56499,7 +56511,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ267">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR267">
         <v>1.39</v>
@@ -56830,7 +56842,7 @@
         <v>274</v>
       </c>
       <c r="P269" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -56911,7 +56923,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ269">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR269">
         <v>1.31</v>
@@ -57320,7 +57332,7 @@
         <v>0.18</v>
       </c>
       <c r="AP271">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ271">
         <v>0.21</v>
@@ -57448,7 +57460,7 @@
         <v>277</v>
       </c>
       <c r="P272" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q272">
         <v>3.5</v>
@@ -57526,7 +57538,7 @@
         <v>1.55</v>
       </c>
       <c r="AP272">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ272">
         <v>1.36</v>
@@ -57654,7 +57666,7 @@
         <v>95</v>
       </c>
       <c r="P273" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q273">
         <v>6</v>
@@ -57938,7 +57950,7 @@
         <v>1.42</v>
       </c>
       <c r="AP274">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ274">
         <v>1.36</v>
@@ -58066,7 +58078,7 @@
         <v>278</v>
       </c>
       <c r="P275" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q275">
         <v>3.2</v>
@@ -58272,7 +58284,7 @@
         <v>279</v>
       </c>
       <c r="P276" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q276">
         <v>2.5</v>
@@ -58353,7 +58365,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ276">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR276">
         <v>1.44</v>
@@ -58478,7 +58490,7 @@
         <v>280</v>
       </c>
       <c r="P277" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58684,7 +58696,7 @@
         <v>281</v>
       </c>
       <c r="P278" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q278">
         <v>2.6</v>
@@ -58971,7 +58983,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ279">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR279">
         <v>1.22</v>
@@ -59174,7 +59186,7 @@
         <v>0.17</v>
       </c>
       <c r="AP280">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ280">
         <v>0.21</v>
@@ -59383,7 +59395,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ281">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR281">
         <v>1.28</v>
@@ -59586,7 +59598,7 @@
         <v>0.8</v>
       </c>
       <c r="AP282">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ282">
         <v>0.83</v>
@@ -59998,7 +60010,7 @@
         <v>1.55</v>
       </c>
       <c r="AP284">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ284">
         <v>1.62</v>
@@ -60413,7 +60425,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ286">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR286">
         <v>1.65</v>
@@ -60538,7 +60550,7 @@
         <v>285</v>
       </c>
       <c r="P287" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Q287">
         <v>3.75</v>
@@ -60616,10 +60628,10 @@
         <v>1.08</v>
       </c>
       <c r="AP287">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ287">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR287">
         <v>1.48</v>
@@ -60822,7 +60834,7 @@
         <v>0.2</v>
       </c>
       <c r="AP288">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ288">
         <v>0.54</v>
@@ -60950,7 +60962,7 @@
         <v>286</v>
       </c>
       <c r="P289" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q289">
         <v>2.38</v>
@@ -61028,10 +61040,10 @@
         <v>0.73</v>
       </c>
       <c r="AP289">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ289">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR289">
         <v>1.34</v>
@@ -61156,7 +61168,7 @@
         <v>287</v>
       </c>
       <c r="P290" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61440,10 +61452,10 @@
         <v>1.17</v>
       </c>
       <c r="AP291">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ291">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR291">
         <v>1.38</v>
@@ -61646,10 +61658,10 @@
         <v>0.83</v>
       </c>
       <c r="AP292">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ292">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR292">
         <v>1.41</v>
@@ -61774,7 +61786,7 @@
         <v>198</v>
       </c>
       <c r="P293" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q293">
         <v>1.95</v>
@@ -61855,7 +61867,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ293">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR293">
         <v>1.93</v>
@@ -61980,7 +61992,7 @@
         <v>289</v>
       </c>
       <c r="P294" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q294">
         <v>3.4</v>
@@ -62058,7 +62070,7 @@
         <v>0.83</v>
       </c>
       <c r="AP294">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ294">
         <v>0.79</v>
@@ -62264,10 +62276,10 @@
         <v>0.73</v>
       </c>
       <c r="AP295">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ295">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR295">
         <v>1.45</v>
@@ -62473,7 +62485,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ296">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR296">
         <v>1.35</v>
@@ -62598,7 +62610,7 @@
         <v>290</v>
       </c>
       <c r="P297" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -63422,7 +63434,7 @@
         <v>291</v>
       </c>
       <c r="P301" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q301">
         <v>3</v>
@@ -63628,7 +63640,7 @@
         <v>204</v>
       </c>
       <c r="P302" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -64040,7 +64052,7 @@
         <v>293</v>
       </c>
       <c r="P304" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Q304">
         <v>3.75</v>
@@ -64246,7 +64258,7 @@
         <v>294</v>
       </c>
       <c r="P305" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q305">
         <v>6.5</v>
@@ -64658,7 +64670,7 @@
         <v>200</v>
       </c>
       <c r="P307" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q307">
         <v>2.2</v>
@@ -65276,7 +65288,7 @@
         <v>231</v>
       </c>
       <c r="P310" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
@@ -65354,10 +65366,10 @@
         <v>0.67</v>
       </c>
       <c r="AP310">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ310">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR310">
         <v>1.52</v>
@@ -65560,7 +65572,7 @@
         <v>0.5</v>
       </c>
       <c r="AP311">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ311">
         <v>0.54</v>
@@ -65781,22 +65793,22 @@
         <v>2.2</v>
       </c>
       <c r="AU312">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV312">
         <v>3</v>
       </c>
       <c r="AW312">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX312">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY312">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ312">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BA312">
         <v>5</v>
@@ -65845,6 +65857,2272 @@
       </c>
       <c r="BP312">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="313" spans="1:68">
+      <c r="A313" s="1">
+        <v>312</v>
+      </c>
+      <c r="B313">
+        <v>7479056</v>
+      </c>
+      <c r="C313" t="s">
+        <v>68</v>
+      </c>
+      <c r="D313" t="s">
+        <v>69</v>
+      </c>
+      <c r="E313" s="2">
+        <v>45674.70833333334</v>
+      </c>
+      <c r="F313">
+        <v>27</v>
+      </c>
+      <c r="G313" t="s">
+        <v>91</v>
+      </c>
+      <c r="H313" t="s">
+        <v>93</v>
+      </c>
+      <c r="I313">
+        <v>0</v>
+      </c>
+      <c r="J313">
+        <v>0</v>
+      </c>
+      <c r="K313">
+        <v>0</v>
+      </c>
+      <c r="L313">
+        <v>0</v>
+      </c>
+      <c r="M313">
+        <v>0</v>
+      </c>
+      <c r="N313">
+        <v>0</v>
+      </c>
+      <c r="O313" t="s">
+        <v>95</v>
+      </c>
+      <c r="P313" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q313">
+        <v>3</v>
+      </c>
+      <c r="R313">
+        <v>1.95</v>
+      </c>
+      <c r="S313">
+        <v>4.33</v>
+      </c>
+      <c r="T313">
+        <v>1.53</v>
+      </c>
+      <c r="U313">
+        <v>2.38</v>
+      </c>
+      <c r="V313">
+        <v>3.75</v>
+      </c>
+      <c r="W313">
+        <v>1.25</v>
+      </c>
+      <c r="X313">
+        <v>11</v>
+      </c>
+      <c r="Y313">
+        <v>1.05</v>
+      </c>
+      <c r="Z313">
+        <v>2.17</v>
+      </c>
+      <c r="AA313">
+        <v>3.25</v>
+      </c>
+      <c r="AB313">
+        <v>3.45</v>
+      </c>
+      <c r="AC313">
+        <v>1.1</v>
+      </c>
+      <c r="AD313">
+        <v>7.5</v>
+      </c>
+      <c r="AE313">
+        <v>1.5</v>
+      </c>
+      <c r="AF313">
+        <v>2.4</v>
+      </c>
+      <c r="AG313">
+        <v>2.4</v>
+      </c>
+      <c r="AH313">
+        <v>1.5</v>
+      </c>
+      <c r="AI313">
+        <v>2.1</v>
+      </c>
+      <c r="AJ313">
+        <v>1.67</v>
+      </c>
+      <c r="AK313">
+        <v>1.29</v>
+      </c>
+      <c r="AL313">
+        <v>1.34</v>
+      </c>
+      <c r="AM313">
+        <v>1.65</v>
+      </c>
+      <c r="AN313">
+        <v>2</v>
+      </c>
+      <c r="AO313">
+        <v>1.46</v>
+      </c>
+      <c r="AP313">
+        <v>1.92</v>
+      </c>
+      <c r="AQ313">
+        <v>1.43</v>
+      </c>
+      <c r="AR313">
+        <v>1.47</v>
+      </c>
+      <c r="AS313">
+        <v>1.34</v>
+      </c>
+      <c r="AT313">
+        <v>2.81</v>
+      </c>
+      <c r="AU313">
+        <v>5</v>
+      </c>
+      <c r="AV313">
+        <v>4</v>
+      </c>
+      <c r="AW313">
+        <v>5</v>
+      </c>
+      <c r="AX313">
+        <v>10</v>
+      </c>
+      <c r="AY313">
+        <v>12</v>
+      </c>
+      <c r="AZ313">
+        <v>19</v>
+      </c>
+      <c r="BA313">
+        <v>5</v>
+      </c>
+      <c r="BB313">
+        <v>4</v>
+      </c>
+      <c r="BC313">
+        <v>9</v>
+      </c>
+      <c r="BD313">
+        <v>1.48</v>
+      </c>
+      <c r="BE313">
+        <v>6.75</v>
+      </c>
+      <c r="BF313">
+        <v>2.95</v>
+      </c>
+      <c r="BG313">
+        <v>1.33</v>
+      </c>
+      <c r="BH313">
+        <v>2.95</v>
+      </c>
+      <c r="BI313">
+        <v>1.56</v>
+      </c>
+      <c r="BJ313">
+        <v>2.23</v>
+      </c>
+      <c r="BK313">
+        <v>1.9</v>
+      </c>
+      <c r="BL313">
+        <v>1.78</v>
+      </c>
+      <c r="BM313">
+        <v>2.4</v>
+      </c>
+      <c r="BN313">
+        <v>1.49</v>
+      </c>
+      <c r="BO313">
+        <v>3.15</v>
+      </c>
+      <c r="BP313">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="314" spans="1:68">
+      <c r="A314" s="1">
+        <v>313</v>
+      </c>
+      <c r="B314">
+        <v>7479057</v>
+      </c>
+      <c r="C314" t="s">
+        <v>68</v>
+      </c>
+      <c r="D314" t="s">
+        <v>69</v>
+      </c>
+      <c r="E314" s="2">
+        <v>45675.39583333334</v>
+      </c>
+      <c r="F314">
+        <v>27</v>
+      </c>
+      <c r="G314" t="s">
+        <v>78</v>
+      </c>
+      <c r="H314" t="s">
+        <v>88</v>
+      </c>
+      <c r="I314">
+        <v>0</v>
+      </c>
+      <c r="J314">
+        <v>0</v>
+      </c>
+      <c r="K314">
+        <v>0</v>
+      </c>
+      <c r="L314">
+        <v>3</v>
+      </c>
+      <c r="M314">
+        <v>0</v>
+      </c>
+      <c r="N314">
+        <v>3</v>
+      </c>
+      <c r="O314" t="s">
+        <v>298</v>
+      </c>
+      <c r="P314" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q314">
+        <v>3.4</v>
+      </c>
+      <c r="R314">
+        <v>2.05</v>
+      </c>
+      <c r="S314">
+        <v>3.4</v>
+      </c>
+      <c r="T314">
+        <v>1.44</v>
+      </c>
+      <c r="U314">
+        <v>2.63</v>
+      </c>
+      <c r="V314">
+        <v>3.25</v>
+      </c>
+      <c r="W314">
+        <v>1.33</v>
+      </c>
+      <c r="X314">
+        <v>9</v>
+      </c>
+      <c r="Y314">
+        <v>1.07</v>
+      </c>
+      <c r="Z314">
+        <v>2.55</v>
+      </c>
+      <c r="AA314">
+        <v>3.09</v>
+      </c>
+      <c r="AB314">
+        <v>2.6</v>
+      </c>
+      <c r="AC314">
+        <v>1.06</v>
+      </c>
+      <c r="AD314">
+        <v>10</v>
+      </c>
+      <c r="AE314">
+        <v>1.36</v>
+      </c>
+      <c r="AF314">
+        <v>3.2</v>
+      </c>
+      <c r="AG314">
+        <v>1.99</v>
+      </c>
+      <c r="AH314">
+        <v>1.73</v>
+      </c>
+      <c r="AI314">
+        <v>1.83</v>
+      </c>
+      <c r="AJ314">
+        <v>1.83</v>
+      </c>
+      <c r="AK314">
+        <v>1.43</v>
+      </c>
+      <c r="AL314">
+        <v>1.32</v>
+      </c>
+      <c r="AM314">
+        <v>1.5</v>
+      </c>
+      <c r="AN314">
+        <v>1.08</v>
+      </c>
+      <c r="AO314">
+        <v>1.08</v>
+      </c>
+      <c r="AP314">
+        <v>1.21</v>
+      </c>
+      <c r="AQ314">
+        <v>1</v>
+      </c>
+      <c r="AR314">
+        <v>1.51</v>
+      </c>
+      <c r="AS314">
+        <v>1.11</v>
+      </c>
+      <c r="AT314">
+        <v>2.62</v>
+      </c>
+      <c r="AU314">
+        <v>7</v>
+      </c>
+      <c r="AV314">
+        <v>3</v>
+      </c>
+      <c r="AW314">
+        <v>5</v>
+      </c>
+      <c r="AX314">
+        <v>4</v>
+      </c>
+      <c r="AY314">
+        <v>14</v>
+      </c>
+      <c r="AZ314">
+        <v>8</v>
+      </c>
+      <c r="BA314">
+        <v>3</v>
+      </c>
+      <c r="BB314">
+        <v>6</v>
+      </c>
+      <c r="BC314">
+        <v>9</v>
+      </c>
+      <c r="BD314">
+        <v>1.68</v>
+      </c>
+      <c r="BE314">
+        <v>6.75</v>
+      </c>
+      <c r="BF314">
+        <v>2.43</v>
+      </c>
+      <c r="BG314">
+        <v>1.25</v>
+      </c>
+      <c r="BH314">
+        <v>3.4</v>
+      </c>
+      <c r="BI314">
+        <v>1.44</v>
+      </c>
+      <c r="BJ314">
+        <v>2.55</v>
+      </c>
+      <c r="BK314">
+        <v>1.72</v>
+      </c>
+      <c r="BL314">
+        <v>1.98</v>
+      </c>
+      <c r="BM314">
+        <v>2.12</v>
+      </c>
+      <c r="BN314">
+        <v>1.63</v>
+      </c>
+      <c r="BO314">
+        <v>2.7</v>
+      </c>
+      <c r="BP314">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="315" spans="1:68">
+      <c r="A315" s="1">
+        <v>314</v>
+      </c>
+      <c r="B315">
+        <v>7479064</v>
+      </c>
+      <c r="C315" t="s">
+        <v>68</v>
+      </c>
+      <c r="D315" t="s">
+        <v>69</v>
+      </c>
+      <c r="E315" s="2">
+        <v>45675.39583333334</v>
+      </c>
+      <c r="F315">
+        <v>27</v>
+      </c>
+      <c r="G315" t="s">
+        <v>92</v>
+      </c>
+      <c r="H315" t="s">
+        <v>72</v>
+      </c>
+      <c r="I315">
+        <v>0</v>
+      </c>
+      <c r="J315">
+        <v>0</v>
+      </c>
+      <c r="K315">
+        <v>0</v>
+      </c>
+      <c r="L315">
+        <v>0</v>
+      </c>
+      <c r="M315">
+        <v>1</v>
+      </c>
+      <c r="N315">
+        <v>1</v>
+      </c>
+      <c r="O315" t="s">
+        <v>95</v>
+      </c>
+      <c r="P315" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q315">
+        <v>4</v>
+      </c>
+      <c r="R315">
+        <v>2.05</v>
+      </c>
+      <c r="S315">
+        <v>3</v>
+      </c>
+      <c r="T315">
+        <v>1.44</v>
+      </c>
+      <c r="U315">
+        <v>2.63</v>
+      </c>
+      <c r="V315">
+        <v>3.25</v>
+      </c>
+      <c r="W315">
+        <v>1.33</v>
+      </c>
+      <c r="X315">
+        <v>9</v>
+      </c>
+      <c r="Y315">
+        <v>1.07</v>
+      </c>
+      <c r="Z315">
+        <v>3.08</v>
+      </c>
+      <c r="AA315">
+        <v>3.15</v>
+      </c>
+      <c r="AB315">
+        <v>2.17</v>
+      </c>
+      <c r="AC315">
+        <v>1.07</v>
+      </c>
+      <c r="AD315">
+        <v>10</v>
+      </c>
+      <c r="AE315">
+        <v>1.36</v>
+      </c>
+      <c r="AF315">
+        <v>3.2</v>
+      </c>
+      <c r="AG315">
+        <v>1.98</v>
+      </c>
+      <c r="AH315">
+        <v>1.77</v>
+      </c>
+      <c r="AI315">
+        <v>1.83</v>
+      </c>
+      <c r="AJ315">
+        <v>1.83</v>
+      </c>
+      <c r="AK315">
+        <v>1.7</v>
+      </c>
+      <c r="AL315">
+        <v>1.31</v>
+      </c>
+      <c r="AM315">
+        <v>1.29</v>
+      </c>
+      <c r="AN315">
+        <v>1.5</v>
+      </c>
+      <c r="AO315">
+        <v>1</v>
+      </c>
+      <c r="AP315">
+        <v>1.38</v>
+      </c>
+      <c r="AQ315">
+        <v>1.15</v>
+      </c>
+      <c r="AR315">
+        <v>1.45</v>
+      </c>
+      <c r="AS315">
+        <v>0.77</v>
+      </c>
+      <c r="AT315">
+        <v>2.22</v>
+      </c>
+      <c r="AU315">
+        <v>2</v>
+      </c>
+      <c r="AV315">
+        <v>7</v>
+      </c>
+      <c r="AW315">
+        <v>2</v>
+      </c>
+      <c r="AX315">
+        <v>8</v>
+      </c>
+      <c r="AY315">
+        <v>5</v>
+      </c>
+      <c r="AZ315">
+        <v>18</v>
+      </c>
+      <c r="BA315">
+        <v>8</v>
+      </c>
+      <c r="BB315">
+        <v>6</v>
+      </c>
+      <c r="BC315">
+        <v>14</v>
+      </c>
+      <c r="BD315">
+        <v>2.02</v>
+      </c>
+      <c r="BE315">
+        <v>7</v>
+      </c>
+      <c r="BF315">
+        <v>1.93</v>
+      </c>
+      <c r="BG315">
+        <v>1.11</v>
+      </c>
+      <c r="BH315">
+        <v>5.3</v>
+      </c>
+      <c r="BI315">
+        <v>1.22</v>
+      </c>
+      <c r="BJ315">
+        <v>3.7</v>
+      </c>
+      <c r="BK315">
+        <v>1.38</v>
+      </c>
+      <c r="BL315">
+        <v>2.75</v>
+      </c>
+      <c r="BM315">
+        <v>1.6</v>
+      </c>
+      <c r="BN315">
+        <v>2.17</v>
+      </c>
+      <c r="BO315">
+        <v>1.93</v>
+      </c>
+      <c r="BP315">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="316" spans="1:68">
+      <c r="A316" s="1">
+        <v>315</v>
+      </c>
+      <c r="B316">
+        <v>7479062</v>
+      </c>
+      <c r="C316" t="s">
+        <v>68</v>
+      </c>
+      <c r="D316" t="s">
+        <v>69</v>
+      </c>
+      <c r="E316" s="2">
+        <v>45675.39583333334</v>
+      </c>
+      <c r="F316">
+        <v>27</v>
+      </c>
+      <c r="G316" t="s">
+        <v>74</v>
+      </c>
+      <c r="H316" t="s">
+        <v>77</v>
+      </c>
+      <c r="I316">
+        <v>0</v>
+      </c>
+      <c r="J316">
+        <v>0</v>
+      </c>
+      <c r="K316">
+        <v>0</v>
+      </c>
+      <c r="L316">
+        <v>0</v>
+      </c>
+      <c r="M316">
+        <v>1</v>
+      </c>
+      <c r="N316">
+        <v>1</v>
+      </c>
+      <c r="O316" t="s">
+        <v>95</v>
+      </c>
+      <c r="P316" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q316">
+        <v>2.88</v>
+      </c>
+      <c r="R316">
+        <v>1.95</v>
+      </c>
+      <c r="S316">
+        <v>4.5</v>
+      </c>
+      <c r="T316">
+        <v>1.57</v>
+      </c>
+      <c r="U316">
+        <v>2.25</v>
+      </c>
+      <c r="V316">
+        <v>3.75</v>
+      </c>
+      <c r="W316">
+        <v>1.25</v>
+      </c>
+      <c r="X316">
+        <v>11</v>
+      </c>
+      <c r="Y316">
+        <v>1.05</v>
+      </c>
+      <c r="Z316">
+        <v>2.17</v>
+      </c>
+      <c r="AA316">
+        <v>2.92</v>
+      </c>
+      <c r="AB316">
+        <v>3.34</v>
+      </c>
+      <c r="AC316">
+        <v>1.1</v>
+      </c>
+      <c r="AD316">
+        <v>7.5</v>
+      </c>
+      <c r="AE316">
+        <v>1.48</v>
+      </c>
+      <c r="AF316">
+        <v>2.75</v>
+      </c>
+      <c r="AG316">
+        <v>2.48</v>
+      </c>
+      <c r="AH316">
+        <v>1.5</v>
+      </c>
+      <c r="AI316">
+        <v>2.1</v>
+      </c>
+      <c r="AJ316">
+        <v>1.67</v>
+      </c>
+      <c r="AK316">
+        <v>1.26</v>
+      </c>
+      <c r="AL316">
+        <v>1.34</v>
+      </c>
+      <c r="AM316">
+        <v>1.71</v>
+      </c>
+      <c r="AN316">
+        <v>1.54</v>
+      </c>
+      <c r="AO316">
+        <v>0.92</v>
+      </c>
+      <c r="AP316">
+        <v>1.43</v>
+      </c>
+      <c r="AQ316">
+        <v>1.08</v>
+      </c>
+      <c r="AR316">
+        <v>1.34</v>
+      </c>
+      <c r="AS316">
+        <v>1.29</v>
+      </c>
+      <c r="AT316">
+        <v>2.63</v>
+      </c>
+      <c r="AU316">
+        <v>2</v>
+      </c>
+      <c r="AV316">
+        <v>4</v>
+      </c>
+      <c r="AW316">
+        <v>11</v>
+      </c>
+      <c r="AX316">
+        <v>5</v>
+      </c>
+      <c r="AY316">
+        <v>17</v>
+      </c>
+      <c r="AZ316">
+        <v>11</v>
+      </c>
+      <c r="BA316">
+        <v>1</v>
+      </c>
+      <c r="BB316">
+        <v>3</v>
+      </c>
+      <c r="BC316">
+        <v>4</v>
+      </c>
+      <c r="BD316">
+        <v>1.75</v>
+      </c>
+      <c r="BE316">
+        <v>6.75</v>
+      </c>
+      <c r="BF316">
+        <v>2.23</v>
+      </c>
+      <c r="BG316">
+        <v>1.19</v>
+      </c>
+      <c r="BH316">
+        <v>4.1</v>
+      </c>
+      <c r="BI316">
+        <v>1.33</v>
+      </c>
+      <c r="BJ316">
+        <v>2.95</v>
+      </c>
+      <c r="BK316">
+        <v>1.55</v>
+      </c>
+      <c r="BL316">
+        <v>2.25</v>
+      </c>
+      <c r="BM316">
+        <v>1.88</v>
+      </c>
+      <c r="BN316">
+        <v>1.81</v>
+      </c>
+      <c r="BO316">
+        <v>2.32</v>
+      </c>
+      <c r="BP316">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="317" spans="1:68">
+      <c r="A317" s="1">
+        <v>316</v>
+      </c>
+      <c r="B317">
+        <v>7479067</v>
+      </c>
+      <c r="C317" t="s">
+        <v>68</v>
+      </c>
+      <c r="D317" t="s">
+        <v>69</v>
+      </c>
+      <c r="E317" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F317">
+        <v>27</v>
+      </c>
+      <c r="G317" t="s">
+        <v>83</v>
+      </c>
+      <c r="H317" t="s">
+        <v>75</v>
+      </c>
+      <c r="I317">
+        <v>0</v>
+      </c>
+      <c r="J317">
+        <v>1</v>
+      </c>
+      <c r="K317">
+        <v>1</v>
+      </c>
+      <c r="L317">
+        <v>1</v>
+      </c>
+      <c r="M317">
+        <v>1</v>
+      </c>
+      <c r="N317">
+        <v>2</v>
+      </c>
+      <c r="O317" t="s">
+        <v>191</v>
+      </c>
+      <c r="P317" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q317">
+        <v>2.38</v>
+      </c>
+      <c r="R317">
+        <v>2.1</v>
+      </c>
+      <c r="S317">
+        <v>5.5</v>
+      </c>
+      <c r="T317">
+        <v>1.44</v>
+      </c>
+      <c r="U317">
+        <v>2.63</v>
+      </c>
+      <c r="V317">
+        <v>3</v>
+      </c>
+      <c r="W317">
+        <v>1.36</v>
+      </c>
+      <c r="X317">
+        <v>9</v>
+      </c>
+      <c r="Y317">
+        <v>1.07</v>
+      </c>
+      <c r="Z317">
+        <v>1.76</v>
+      </c>
+      <c r="AA317">
+        <v>3.32</v>
+      </c>
+      <c r="AB317">
+        <v>4.32</v>
+      </c>
+      <c r="AC317">
+        <v>1.06</v>
+      </c>
+      <c r="AD317">
+        <v>11</v>
+      </c>
+      <c r="AE317">
+        <v>1.33</v>
+      </c>
+      <c r="AF317">
+        <v>3.4</v>
+      </c>
+      <c r="AG317">
+        <v>1.97</v>
+      </c>
+      <c r="AH317">
+        <v>1.78</v>
+      </c>
+      <c r="AI317">
+        <v>2</v>
+      </c>
+      <c r="AJ317">
+        <v>1.73</v>
+      </c>
+      <c r="AK317">
+        <v>1.18</v>
+      </c>
+      <c r="AL317">
+        <v>1.28</v>
+      </c>
+      <c r="AM317">
+        <v>2.05</v>
+      </c>
+      <c r="AN317">
+        <v>1.75</v>
+      </c>
+      <c r="AO317">
+        <v>0.75</v>
+      </c>
+      <c r="AP317">
+        <v>1.69</v>
+      </c>
+      <c r="AQ317">
+        <v>0.77</v>
+      </c>
+      <c r="AR317">
+        <v>1.35</v>
+      </c>
+      <c r="AS317">
+        <v>1.17</v>
+      </c>
+      <c r="AT317">
+        <v>2.52</v>
+      </c>
+      <c r="AU317">
+        <v>5</v>
+      </c>
+      <c r="AV317">
+        <v>3</v>
+      </c>
+      <c r="AW317">
+        <v>18</v>
+      </c>
+      <c r="AX317">
+        <v>1</v>
+      </c>
+      <c r="AY317">
+        <v>27</v>
+      </c>
+      <c r="AZ317">
+        <v>5</v>
+      </c>
+      <c r="BA317">
+        <v>12</v>
+      </c>
+      <c r="BB317">
+        <v>0</v>
+      </c>
+      <c r="BC317">
+        <v>12</v>
+      </c>
+      <c r="BD317">
+        <v>1.54</v>
+      </c>
+      <c r="BE317">
+        <v>7</v>
+      </c>
+      <c r="BF317">
+        <v>2.65</v>
+      </c>
+      <c r="BG317">
+        <v>1.11</v>
+      </c>
+      <c r="BH317">
+        <v>5.1</v>
+      </c>
+      <c r="BI317">
+        <v>1.24</v>
+      </c>
+      <c r="BJ317">
+        <v>3.55</v>
+      </c>
+      <c r="BK317">
+        <v>1.41</v>
+      </c>
+      <c r="BL317">
+        <v>2.65</v>
+      </c>
+      <c r="BM317">
+        <v>1.64</v>
+      </c>
+      <c r="BN317">
+        <v>2.1</v>
+      </c>
+      <c r="BO317">
+        <v>1.96</v>
+      </c>
+      <c r="BP317">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="318" spans="1:68">
+      <c r="A318" s="1">
+        <v>317</v>
+      </c>
+      <c r="B318">
+        <v>7479063</v>
+      </c>
+      <c r="C318" t="s">
+        <v>68</v>
+      </c>
+      <c r="D318" t="s">
+        <v>69</v>
+      </c>
+      <c r="E318" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F318">
+        <v>27</v>
+      </c>
+      <c r="G318" t="s">
+        <v>73</v>
+      </c>
+      <c r="H318" t="s">
+        <v>70</v>
+      </c>
+      <c r="I318">
+        <v>0</v>
+      </c>
+      <c r="J318">
+        <v>0</v>
+      </c>
+      <c r="K318">
+        <v>0</v>
+      </c>
+      <c r="L318">
+        <v>1</v>
+      </c>
+      <c r="M318">
+        <v>0</v>
+      </c>
+      <c r="N318">
+        <v>1</v>
+      </c>
+      <c r="O318" t="s">
+        <v>134</v>
+      </c>
+      <c r="P318" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q318">
+        <v>3.5</v>
+      </c>
+      <c r="R318">
+        <v>2.05</v>
+      </c>
+      <c r="S318">
+        <v>3.4</v>
+      </c>
+      <c r="T318">
+        <v>1.5</v>
+      </c>
+      <c r="U318">
+        <v>2.5</v>
+      </c>
+      <c r="V318">
+        <v>3.4</v>
+      </c>
+      <c r="W318">
+        <v>1.3</v>
+      </c>
+      <c r="X318">
+        <v>10</v>
+      </c>
+      <c r="Y318">
+        <v>1.06</v>
+      </c>
+      <c r="Z318">
+        <v>2.77</v>
+      </c>
+      <c r="AA318">
+        <v>3.05</v>
+      </c>
+      <c r="AB318">
+        <v>2.42</v>
+      </c>
+      <c r="AC318">
+        <v>1.07</v>
+      </c>
+      <c r="AD318">
+        <v>9</v>
+      </c>
+      <c r="AE318">
+        <v>1.4</v>
+      </c>
+      <c r="AF318">
+        <v>3</v>
+      </c>
+      <c r="AG318">
+        <v>2.12</v>
+      </c>
+      <c r="AH318">
+        <v>1.67</v>
+      </c>
+      <c r="AI318">
+        <v>1.83</v>
+      </c>
+      <c r="AJ318">
+        <v>1.83</v>
+      </c>
+      <c r="AK318">
+        <v>1.49</v>
+      </c>
+      <c r="AL318">
+        <v>1.33</v>
+      </c>
+      <c r="AM318">
+        <v>1.43</v>
+      </c>
+      <c r="AN318">
+        <v>1.69</v>
+      </c>
+      <c r="AO318">
+        <v>1.33</v>
+      </c>
+      <c r="AP318">
+        <v>1.79</v>
+      </c>
+      <c r="AQ318">
+        <v>1.23</v>
+      </c>
+      <c r="AR318">
+        <v>1.1</v>
+      </c>
+      <c r="AS318">
+        <v>0.93</v>
+      </c>
+      <c r="AT318">
+        <v>2.03</v>
+      </c>
+      <c r="AU318">
+        <v>7</v>
+      </c>
+      <c r="AV318">
+        <v>5</v>
+      </c>
+      <c r="AW318">
+        <v>10</v>
+      </c>
+      <c r="AX318">
+        <v>9</v>
+      </c>
+      <c r="AY318">
+        <v>21</v>
+      </c>
+      <c r="AZ318">
+        <v>19</v>
+      </c>
+      <c r="BA318">
+        <v>4</v>
+      </c>
+      <c r="BB318">
+        <v>3</v>
+      </c>
+      <c r="BC318">
+        <v>7</v>
+      </c>
+      <c r="BD318">
+        <v>1.95</v>
+      </c>
+      <c r="BE318">
+        <v>6.4</v>
+      </c>
+      <c r="BF318">
+        <v>2.05</v>
+      </c>
+      <c r="BG318">
+        <v>1.26</v>
+      </c>
+      <c r="BH318">
+        <v>3.4</v>
+      </c>
+      <c r="BI318">
+        <v>1.47</v>
+      </c>
+      <c r="BJ318">
+        <v>2.48</v>
+      </c>
+      <c r="BK318">
+        <v>1.73</v>
+      </c>
+      <c r="BL318">
+        <v>1.96</v>
+      </c>
+      <c r="BM318">
+        <v>2.17</v>
+      </c>
+      <c r="BN318">
+        <v>1.6</v>
+      </c>
+      <c r="BO318">
+        <v>2.7</v>
+      </c>
+      <c r="BP318">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="319" spans="1:68">
+      <c r="A319" s="1">
+        <v>318</v>
+      </c>
+      <c r="B319">
+        <v>7479066</v>
+      </c>
+      <c r="C319" t="s">
+        <v>68</v>
+      </c>
+      <c r="D319" t="s">
+        <v>69</v>
+      </c>
+      <c r="E319" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F319">
+        <v>27</v>
+      </c>
+      <c r="G319" t="s">
+        <v>86</v>
+      </c>
+      <c r="H319" t="s">
+        <v>90</v>
+      </c>
+      <c r="I319">
+        <v>1</v>
+      </c>
+      <c r="J319">
+        <v>0</v>
+      </c>
+      <c r="K319">
+        <v>1</v>
+      </c>
+      <c r="L319">
+        <v>2</v>
+      </c>
+      <c r="M319">
+        <v>0</v>
+      </c>
+      <c r="N319">
+        <v>2</v>
+      </c>
+      <c r="O319" t="s">
+        <v>299</v>
+      </c>
+      <c r="P319" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q319">
+        <v>2.88</v>
+      </c>
+      <c r="R319">
+        <v>2.1</v>
+      </c>
+      <c r="S319">
+        <v>4</v>
+      </c>
+      <c r="T319">
+        <v>1.44</v>
+      </c>
+      <c r="U319">
+        <v>2.63</v>
+      </c>
+      <c r="V319">
+        <v>3.25</v>
+      </c>
+      <c r="W319">
+        <v>1.33</v>
+      </c>
+      <c r="X319">
+        <v>9</v>
+      </c>
+      <c r="Y319">
+        <v>1.07</v>
+      </c>
+      <c r="Z319">
+        <v>2.2</v>
+      </c>
+      <c r="AA319">
+        <v>3.09</v>
+      </c>
+      <c r="AB319">
+        <v>3.08</v>
+      </c>
+      <c r="AC319">
+        <v>1.07</v>
+      </c>
+      <c r="AD319">
+        <v>10</v>
+      </c>
+      <c r="AE319">
+        <v>1.36</v>
+      </c>
+      <c r="AF319">
+        <v>3.2</v>
+      </c>
+      <c r="AG319">
+        <v>2.05</v>
+      </c>
+      <c r="AH319">
+        <v>1.72</v>
+      </c>
+      <c r="AI319">
+        <v>1.83</v>
+      </c>
+      <c r="AJ319">
+        <v>1.83</v>
+      </c>
+      <c r="AK319">
+        <v>1.29</v>
+      </c>
+      <c r="AL319">
+        <v>1.3</v>
+      </c>
+      <c r="AM319">
+        <v>1.72</v>
+      </c>
+      <c r="AN319">
+        <v>2.42</v>
+      </c>
+      <c r="AO319">
+        <v>1</v>
+      </c>
+      <c r="AP319">
+        <v>2.46</v>
+      </c>
+      <c r="AQ319">
+        <v>0.93</v>
+      </c>
+      <c r="AR319">
+        <v>1.41</v>
+      </c>
+      <c r="AS319">
+        <v>1.02</v>
+      </c>
+      <c r="AT319">
+        <v>2.43</v>
+      </c>
+      <c r="AU319">
+        <v>7</v>
+      </c>
+      <c r="AV319">
+        <v>0</v>
+      </c>
+      <c r="AW319">
+        <v>17</v>
+      </c>
+      <c r="AX319">
+        <v>12</v>
+      </c>
+      <c r="AY319">
+        <v>35</v>
+      </c>
+      <c r="AZ319">
+        <v>16</v>
+      </c>
+      <c r="BA319">
+        <v>7</v>
+      </c>
+      <c r="BB319">
+        <v>6</v>
+      </c>
+      <c r="BC319">
+        <v>13</v>
+      </c>
+      <c r="BD319">
+        <v>1.83</v>
+      </c>
+      <c r="BE319">
+        <v>6.75</v>
+      </c>
+      <c r="BF319">
+        <v>2.15</v>
+      </c>
+      <c r="BG319">
+        <v>1.19</v>
+      </c>
+      <c r="BH319">
+        <v>4</v>
+      </c>
+      <c r="BI319">
+        <v>1.34</v>
+      </c>
+      <c r="BJ319">
+        <v>2.9</v>
+      </c>
+      <c r="BK319">
+        <v>1.57</v>
+      </c>
+      <c r="BL319">
+        <v>2.23</v>
+      </c>
+      <c r="BM319">
+        <v>1.9</v>
+      </c>
+      <c r="BN319">
+        <v>1.79</v>
+      </c>
+      <c r="BO319">
+        <v>2.35</v>
+      </c>
+      <c r="BP319">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="320" spans="1:68">
+      <c r="A320" s="1">
+        <v>319</v>
+      </c>
+      <c r="B320">
+        <v>7479059</v>
+      </c>
+      <c r="C320" t="s">
+        <v>68</v>
+      </c>
+      <c r="D320" t="s">
+        <v>69</v>
+      </c>
+      <c r="E320" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F320">
+        <v>27</v>
+      </c>
+      <c r="G320" t="s">
+        <v>84</v>
+      </c>
+      <c r="H320" t="s">
+        <v>87</v>
+      </c>
+      <c r="I320">
+        <v>0</v>
+      </c>
+      <c r="J320">
+        <v>1</v>
+      </c>
+      <c r="K320">
+        <v>1</v>
+      </c>
+      <c r="L320">
+        <v>0</v>
+      </c>
+      <c r="M320">
+        <v>2</v>
+      </c>
+      <c r="N320">
+        <v>2</v>
+      </c>
+      <c r="O320" t="s">
+        <v>95</v>
+      </c>
+      <c r="P320" t="s">
+        <v>402</v>
+      </c>
+      <c r="Q320">
+        <v>3.1</v>
+      </c>
+      <c r="R320">
+        <v>2.05</v>
+      </c>
+      <c r="S320">
+        <v>3.6</v>
+      </c>
+      <c r="T320">
+        <v>1.44</v>
+      </c>
+      <c r="U320">
+        <v>2.63</v>
+      </c>
+      <c r="V320">
+        <v>3.25</v>
+      </c>
+      <c r="W320">
+        <v>1.33</v>
+      </c>
+      <c r="X320">
+        <v>9</v>
+      </c>
+      <c r="Y320">
+        <v>1.07</v>
+      </c>
+      <c r="Z320">
+        <v>2.36</v>
+      </c>
+      <c r="AA320">
+        <v>3.11</v>
+      </c>
+      <c r="AB320">
+        <v>2.81</v>
+      </c>
+      <c r="AC320">
+        <v>1.05</v>
+      </c>
+      <c r="AD320">
+        <v>11</v>
+      </c>
+      <c r="AE320">
+        <v>1.32</v>
+      </c>
+      <c r="AF320">
+        <v>3.4</v>
+      </c>
+      <c r="AG320">
+        <v>2.08</v>
+      </c>
+      <c r="AH320">
+        <v>1.7</v>
+      </c>
+      <c r="AI320">
+        <v>1.83</v>
+      </c>
+      <c r="AJ320">
+        <v>1.83</v>
+      </c>
+      <c r="AK320">
+        <v>1.41</v>
+      </c>
+      <c r="AL320">
+        <v>1.31</v>
+      </c>
+      <c r="AM320">
+        <v>1.53</v>
+      </c>
+      <c r="AN320">
+        <v>1.67</v>
+      </c>
+      <c r="AO320">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP320">
+        <v>1.54</v>
+      </c>
+      <c r="AQ320">
+        <v>0.86</v>
+      </c>
+      <c r="AR320">
+        <v>1.35</v>
+      </c>
+      <c r="AS320">
+        <v>1.11</v>
+      </c>
+      <c r="AT320">
+        <v>2.46</v>
+      </c>
+      <c r="AU320">
+        <v>5</v>
+      </c>
+      <c r="AV320">
+        <v>8</v>
+      </c>
+      <c r="AW320">
+        <v>11</v>
+      </c>
+      <c r="AX320">
+        <v>10</v>
+      </c>
+      <c r="AY320">
+        <v>21</v>
+      </c>
+      <c r="AZ320">
+        <v>25</v>
+      </c>
+      <c r="BA320">
+        <v>4</v>
+      </c>
+      <c r="BB320">
+        <v>8</v>
+      </c>
+      <c r="BC320">
+        <v>12</v>
+      </c>
+      <c r="BD320">
+        <v>1.6</v>
+      </c>
+      <c r="BE320">
+        <v>6.75</v>
+      </c>
+      <c r="BF320">
+        <v>2.55</v>
+      </c>
+      <c r="BG320">
+        <v>1.15</v>
+      </c>
+      <c r="BH320">
+        <v>4.4</v>
+      </c>
+      <c r="BI320">
+        <v>1.3</v>
+      </c>
+      <c r="BJ320">
+        <v>3.15</v>
+      </c>
+      <c r="BK320">
+        <v>1.5</v>
+      </c>
+      <c r="BL320">
+        <v>2.4</v>
+      </c>
+      <c r="BM320">
+        <v>1.79</v>
+      </c>
+      <c r="BN320">
+        <v>1.9</v>
+      </c>
+      <c r="BO320">
+        <v>2.2</v>
+      </c>
+      <c r="BP320">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="321" spans="1:68">
+      <c r="A321" s="1">
+        <v>320</v>
+      </c>
+      <c r="B321">
+        <v>7479058</v>
+      </c>
+      <c r="C321" t="s">
+        <v>68</v>
+      </c>
+      <c r="D321" t="s">
+        <v>69</v>
+      </c>
+      <c r="E321" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F321">
+        <v>27</v>
+      </c>
+      <c r="G321" t="s">
+        <v>82</v>
+      </c>
+      <c r="H321" t="s">
+        <v>89</v>
+      </c>
+      <c r="I321">
+        <v>0</v>
+      </c>
+      <c r="J321">
+        <v>0</v>
+      </c>
+      <c r="K321">
+        <v>0</v>
+      </c>
+      <c r="L321">
+        <v>1</v>
+      </c>
+      <c r="M321">
+        <v>0</v>
+      </c>
+      <c r="N321">
+        <v>1</v>
+      </c>
+      <c r="O321" t="s">
+        <v>143</v>
+      </c>
+      <c r="P321" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q321">
+        <v>2.75</v>
+      </c>
+      <c r="R321">
+        <v>2.1</v>
+      </c>
+      <c r="S321">
+        <v>4</v>
+      </c>
+      <c r="T321">
+        <v>1.4</v>
+      </c>
+      <c r="U321">
+        <v>2.75</v>
+      </c>
+      <c r="V321">
+        <v>3</v>
+      </c>
+      <c r="W321">
+        <v>1.36</v>
+      </c>
+      <c r="X321">
+        <v>8</v>
+      </c>
+      <c r="Y321">
+        <v>1.08</v>
+      </c>
+      <c r="Z321">
+        <v>2.2</v>
+      </c>
+      <c r="AA321">
+        <v>3.09</v>
+      </c>
+      <c r="AB321">
+        <v>3.09</v>
+      </c>
+      <c r="AC321">
+        <v>1.05</v>
+      </c>
+      <c r="AD321">
+        <v>11</v>
+      </c>
+      <c r="AE321">
+        <v>1.33</v>
+      </c>
+      <c r="AF321">
+        <v>3.4</v>
+      </c>
+      <c r="AG321">
+        <v>2.03</v>
+      </c>
+      <c r="AH321">
+        <v>1.85</v>
+      </c>
+      <c r="AI321">
+        <v>1.73</v>
+      </c>
+      <c r="AJ321">
+        <v>2</v>
+      </c>
+      <c r="AK321">
+        <v>1.31</v>
+      </c>
+      <c r="AL321">
+        <v>1.3</v>
+      </c>
+      <c r="AM321">
+        <v>1.68</v>
+      </c>
+      <c r="AN321">
+        <v>1.5</v>
+      </c>
+      <c r="AO321">
+        <v>1.08</v>
+      </c>
+      <c r="AP321">
+        <v>1.62</v>
+      </c>
+      <c r="AQ321">
+        <v>1</v>
+      </c>
+      <c r="AR321">
+        <v>1.84</v>
+      </c>
+      <c r="AS321">
+        <v>1.26</v>
+      </c>
+      <c r="AT321">
+        <v>3.1</v>
+      </c>
+      <c r="AU321">
+        <v>7</v>
+      </c>
+      <c r="AV321">
+        <v>3</v>
+      </c>
+      <c r="AW321">
+        <v>11</v>
+      </c>
+      <c r="AX321">
+        <v>6</v>
+      </c>
+      <c r="AY321">
+        <v>20</v>
+      </c>
+      <c r="AZ321">
+        <v>9</v>
+      </c>
+      <c r="BA321">
+        <v>3</v>
+      </c>
+      <c r="BB321">
+        <v>5</v>
+      </c>
+      <c r="BC321">
+        <v>8</v>
+      </c>
+      <c r="BD321">
+        <v>1.68</v>
+      </c>
+      <c r="BE321">
+        <v>7</v>
+      </c>
+      <c r="BF321">
+        <v>2.38</v>
+      </c>
+      <c r="BG321">
+        <v>1.18</v>
+      </c>
+      <c r="BH321">
+        <v>4.1</v>
+      </c>
+      <c r="BI321">
+        <v>1.3</v>
+      </c>
+      <c r="BJ321">
+        <v>3.05</v>
+      </c>
+      <c r="BK321">
+        <v>1.53</v>
+      </c>
+      <c r="BL321">
+        <v>2.32</v>
+      </c>
+      <c r="BM321">
+        <v>1.82</v>
+      </c>
+      <c r="BN321">
+        <v>1.86</v>
+      </c>
+      <c r="BO321">
+        <v>2.28</v>
+      </c>
+      <c r="BP321">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="322" spans="1:68">
+      <c r="A322" s="1">
+        <v>321</v>
+      </c>
+      <c r="B322">
+        <v>7479061</v>
+      </c>
+      <c r="C322" t="s">
+        <v>68</v>
+      </c>
+      <c r="D322" t="s">
+        <v>69</v>
+      </c>
+      <c r="E322" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F322">
+        <v>27</v>
+      </c>
+      <c r="G322" t="s">
+        <v>81</v>
+      </c>
+      <c r="H322" t="s">
+        <v>71</v>
+      </c>
+      <c r="I322">
+        <v>0</v>
+      </c>
+      <c r="J322">
+        <v>0</v>
+      </c>
+      <c r="K322">
+        <v>0</v>
+      </c>
+      <c r="L322">
+        <v>0</v>
+      </c>
+      <c r="M322">
+        <v>0</v>
+      </c>
+      <c r="N322">
+        <v>0</v>
+      </c>
+      <c r="O322" t="s">
+        <v>95</v>
+      </c>
+      <c r="P322" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q322">
+        <v>2.88</v>
+      </c>
+      <c r="R322">
+        <v>2.05</v>
+      </c>
+      <c r="S322">
+        <v>4</v>
+      </c>
+      <c r="T322">
+        <v>1.44</v>
+      </c>
+      <c r="U322">
+        <v>2.63</v>
+      </c>
+      <c r="V322">
+        <v>3.4</v>
+      </c>
+      <c r="W322">
+        <v>1.3</v>
+      </c>
+      <c r="X322">
+        <v>10</v>
+      </c>
+      <c r="Y322">
+        <v>1.06</v>
+      </c>
+      <c r="Z322">
+        <v>2.25</v>
+      </c>
+      <c r="AA322">
+        <v>2.99</v>
+      </c>
+      <c r="AB322">
+        <v>3.1</v>
+      </c>
+      <c r="AC322">
+        <v>1.08</v>
+      </c>
+      <c r="AD322">
+        <v>9</v>
+      </c>
+      <c r="AE322">
+        <v>1.4</v>
+      </c>
+      <c r="AF322">
+        <v>3</v>
+      </c>
+      <c r="AG322">
+        <v>2.12</v>
+      </c>
+      <c r="AH322">
+        <v>1.67</v>
+      </c>
+      <c r="AI322">
+        <v>1.83</v>
+      </c>
+      <c r="AJ322">
+        <v>1.83</v>
+      </c>
+      <c r="AK322">
+        <v>1.31</v>
+      </c>
+      <c r="AL322">
+        <v>1.32</v>
+      </c>
+      <c r="AM322">
+        <v>1.65</v>
+      </c>
+      <c r="AN322">
+        <v>1.62</v>
+      </c>
+      <c r="AO322">
+        <v>0.67</v>
+      </c>
+      <c r="AP322">
+        <v>1.57</v>
+      </c>
+      <c r="AQ322">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR322">
+        <v>1.41</v>
+      </c>
+      <c r="AS322">
+        <v>1.08</v>
+      </c>
+      <c r="AT322">
+        <v>2.49</v>
+      </c>
+      <c r="AU322">
+        <v>5</v>
+      </c>
+      <c r="AV322">
+        <v>2</v>
+      </c>
+      <c r="AW322">
+        <v>5</v>
+      </c>
+      <c r="AX322">
+        <v>2</v>
+      </c>
+      <c r="AY322">
+        <v>14</v>
+      </c>
+      <c r="AZ322">
+        <v>4</v>
+      </c>
+      <c r="BA322">
+        <v>3</v>
+      </c>
+      <c r="BB322">
+        <v>1</v>
+      </c>
+      <c r="BC322">
+        <v>4</v>
+      </c>
+      <c r="BD322">
+        <v>1.53</v>
+      </c>
+      <c r="BE322">
+        <v>6.75</v>
+      </c>
+      <c r="BF322">
+        <v>2.8</v>
+      </c>
+      <c r="BG322">
+        <v>1.21</v>
+      </c>
+      <c r="BH322">
+        <v>3.8</v>
+      </c>
+      <c r="BI322">
+        <v>1.38</v>
+      </c>
+      <c r="BJ322">
+        <v>2.7</v>
+      </c>
+      <c r="BK322">
+        <v>1.64</v>
+      </c>
+      <c r="BL322">
+        <v>2.1</v>
+      </c>
+      <c r="BM322">
+        <v>2</v>
+      </c>
+      <c r="BN322">
+        <v>1.71</v>
+      </c>
+      <c r="BO322">
+        <v>2.5</v>
+      </c>
+      <c r="BP322">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="323" spans="1:68">
+      <c r="A323" s="1">
+        <v>322</v>
+      </c>
+      <c r="B323">
+        <v>7479065</v>
+      </c>
+      <c r="C323" t="s">
+        <v>68</v>
+      </c>
+      <c r="D323" t="s">
+        <v>69</v>
+      </c>
+      <c r="E323" s="2">
+        <v>45675.52430555555</v>
+      </c>
+      <c r="F323">
+        <v>27</v>
+      </c>
+      <c r="G323" t="s">
+        <v>85</v>
+      </c>
+      <c r="H323" t="s">
+        <v>79</v>
+      </c>
+      <c r="I323">
+        <v>0</v>
+      </c>
+      <c r="J323">
+        <v>1</v>
+      </c>
+      <c r="K323">
+        <v>1</v>
+      </c>
+      <c r="L323">
+        <v>2</v>
+      </c>
+      <c r="M323">
+        <v>1</v>
+      </c>
+      <c r="N323">
+        <v>3</v>
+      </c>
+      <c r="O323" t="s">
+        <v>300</v>
+      </c>
+      <c r="P323" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q323">
+        <v>4.5</v>
+      </c>
+      <c r="R323">
+        <v>2.38</v>
+      </c>
+      <c r="S323">
+        <v>2.3</v>
+      </c>
+      <c r="T323">
+        <v>1.33</v>
+      </c>
+      <c r="U323">
+        <v>3.25</v>
+      </c>
+      <c r="V323">
+        <v>2.5</v>
+      </c>
+      <c r="W323">
+        <v>1.5</v>
+      </c>
+      <c r="X323">
+        <v>6</v>
+      </c>
+      <c r="Y323">
+        <v>1.13</v>
+      </c>
+      <c r="Z323">
+        <v>3.95</v>
+      </c>
+      <c r="AA323">
+        <v>3.64</v>
+      </c>
+      <c r="AB323">
+        <v>1.74</v>
+      </c>
+      <c r="AC323">
+        <v>1.03</v>
+      </c>
+      <c r="AD323">
+        <v>15</v>
+      </c>
+      <c r="AE323">
+        <v>1.22</v>
+      </c>
+      <c r="AF323">
+        <v>4.33</v>
+      </c>
+      <c r="AG323">
+        <v>1.64</v>
+      </c>
+      <c r="AH323">
+        <v>2.18</v>
+      </c>
+      <c r="AI323">
+        <v>1.62</v>
+      </c>
+      <c r="AJ323">
+        <v>2.2</v>
+      </c>
+      <c r="AK323">
+        <v>2.15</v>
+      </c>
+      <c r="AL323">
+        <v>1.22</v>
+      </c>
+      <c r="AM323">
+        <v>1.22</v>
+      </c>
+      <c r="AN323">
+        <v>1.45</v>
+      </c>
+      <c r="AO323">
+        <v>1.5</v>
+      </c>
+      <c r="AP323">
+        <v>1.58</v>
+      </c>
+      <c r="AQ323">
+        <v>1.38</v>
+      </c>
+      <c r="AR323">
+        <v>1.4</v>
+      </c>
+      <c r="AS323">
+        <v>1.57</v>
+      </c>
+      <c r="AT323">
+        <v>2.97</v>
+      </c>
+      <c r="AU323">
+        <v>6</v>
+      </c>
+      <c r="AV323">
+        <v>5</v>
+      </c>
+      <c r="AW323">
+        <v>8</v>
+      </c>
+      <c r="AX323">
+        <v>8</v>
+      </c>
+      <c r="AY323">
+        <v>17</v>
+      </c>
+      <c r="AZ323">
+        <v>16</v>
+      </c>
+      <c r="BA323">
+        <v>7</v>
+      </c>
+      <c r="BB323">
+        <v>4</v>
+      </c>
+      <c r="BC323">
+        <v>11</v>
+      </c>
+      <c r="BD323">
+        <v>2.15</v>
+      </c>
+      <c r="BE323">
+        <v>7</v>
+      </c>
+      <c r="BF323">
+        <v>1.8</v>
+      </c>
+      <c r="BG323">
+        <v>1.1</v>
+      </c>
+      <c r="BH323">
+        <v>5.4</v>
+      </c>
+      <c r="BI323">
+        <v>1.2</v>
+      </c>
+      <c r="BJ323">
+        <v>3.9</v>
+      </c>
+      <c r="BK323">
+        <v>1.35</v>
+      </c>
+      <c r="BL323">
+        <v>2.9</v>
+      </c>
+      <c r="BM323">
+        <v>1.56</v>
+      </c>
+      <c r="BN323">
+        <v>2.25</v>
+      </c>
+      <c r="BO323">
+        <v>1.86</v>
+      </c>
+      <c r="BP323">
+        <v>1.82</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="404">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -919,6 +919,9 @@
     <t>['54', '82']</t>
   </si>
   <si>
+    <t>['3', '88', '90+6']</t>
+  </si>
+  <si>
     <t>['67', '88']</t>
   </si>
   <si>
@@ -1584,7 +1587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP323"/>
+  <dimension ref="A1:BP324"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1840,7 +1843,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -2046,7 +2049,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2252,7 +2255,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2664,7 +2667,7 @@
         <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -3076,7 +3079,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q8">
         <v>1.83</v>
@@ -3154,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ8">
         <v>0.5</v>
@@ -3282,7 +3285,7 @@
         <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3488,7 +3491,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -4106,7 +4109,7 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4312,7 +4315,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -5136,7 +5139,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -5754,7 +5757,7 @@
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5960,7 +5963,7 @@
         <v>111</v>
       </c>
       <c r="P22" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q22">
         <v>2.6</v>
@@ -6659,7 +6662,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ25">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6784,7 +6787,7 @@
         <v>95</v>
       </c>
       <c r="P26" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -7608,7 +7611,7 @@
         <v>117</v>
       </c>
       <c r="P30" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -8638,7 +8641,7 @@
         <v>122</v>
       </c>
       <c r="P35" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8844,7 +8847,7 @@
         <v>123</v>
       </c>
       <c r="P36" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -9256,7 +9259,7 @@
         <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q38">
         <v>2.4</v>
@@ -9668,7 +9671,7 @@
         <v>95</v>
       </c>
       <c r="P40" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q40">
         <v>4.5</v>
@@ -9874,7 +9877,7 @@
         <v>95</v>
       </c>
       <c r="P41" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -10286,7 +10289,7 @@
         <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q43">
         <v>4.33</v>
@@ -10779,7 +10782,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ45">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR45">
         <v>1.47</v>
@@ -10982,7 +10985,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ46">
         <v>1.08</v>
@@ -11728,7 +11731,7 @@
         <v>95</v>
       </c>
       <c r="P50" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -12012,7 +12015,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ51">
         <v>2</v>
@@ -12964,7 +12967,7 @@
         <v>135</v>
       </c>
       <c r="P56" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q56">
         <v>4.5</v>
@@ -13788,7 +13791,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13994,7 +13997,7 @@
         <v>95</v>
       </c>
       <c r="P61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q61">
         <v>4.33</v>
@@ -14200,7 +14203,7 @@
         <v>139</v>
       </c>
       <c r="P62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -15024,7 +15027,7 @@
         <v>95</v>
       </c>
       <c r="P66" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q66">
         <v>5.5</v>
@@ -15642,7 +15645,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q69">
         <v>2.05</v>
@@ -15929,7 +15932,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ70">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR70">
         <v>1.2</v>
@@ -16054,7 +16057,7 @@
         <v>147</v>
       </c>
       <c r="P71" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -16672,7 +16675,7 @@
         <v>149</v>
       </c>
       <c r="P74" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q74">
         <v>3.9</v>
@@ -17084,7 +17087,7 @@
         <v>151</v>
       </c>
       <c r="P76" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17290,7 +17293,7 @@
         <v>152</v>
       </c>
       <c r="P77" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q77">
         <v>3.75</v>
@@ -17702,7 +17705,7 @@
         <v>153</v>
       </c>
       <c r="P79" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -18114,7 +18117,7 @@
         <v>155</v>
       </c>
       <c r="P81" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q81">
         <v>2.63</v>
@@ -18810,7 +18813,7 @@
         <v>0.67</v>
       </c>
       <c r="AP84">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ84">
         <v>0.79</v>
@@ -19762,7 +19765,7 @@
         <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q89">
         <v>2.1</v>
@@ -20380,7 +20383,7 @@
         <v>162</v>
       </c>
       <c r="P92" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q92">
         <v>2.85</v>
@@ -21491,7 +21494,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ97">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR97">
         <v>1.65</v>
@@ -21616,7 +21619,7 @@
         <v>165</v>
       </c>
       <c r="P98" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -22440,7 +22443,7 @@
         <v>119</v>
       </c>
       <c r="P102" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q102">
         <v>2.5</v>
@@ -22521,7 +22524,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ102">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR102">
         <v>2.01</v>
@@ -22646,7 +22649,7 @@
         <v>168</v>
       </c>
       <c r="P103" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -24166,7 +24169,7 @@
         <v>2</v>
       </c>
       <c r="AP110">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ110">
         <v>1.79</v>
@@ -25118,7 +25121,7 @@
         <v>95</v>
       </c>
       <c r="P115" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q115">
         <v>3.4</v>
@@ -25324,7 +25327,7 @@
         <v>178</v>
       </c>
       <c r="P116" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25736,7 +25739,7 @@
         <v>95</v>
       </c>
       <c r="P118" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
@@ -26766,7 +26769,7 @@
         <v>182</v>
       </c>
       <c r="P123" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -26972,7 +26975,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q124">
         <v>3</v>
@@ -27256,7 +27259,7 @@
         <v>0.6</v>
       </c>
       <c r="AP125">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ125">
         <v>0.86</v>
@@ -28414,7 +28417,7 @@
         <v>187</v>
       </c>
       <c r="P131" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -29032,7 +29035,7 @@
         <v>162</v>
       </c>
       <c r="P134" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29113,7 +29116,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ134">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR134">
         <v>1.28</v>
@@ -29444,7 +29447,7 @@
         <v>190</v>
       </c>
       <c r="P136" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -29856,7 +29859,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q138">
         <v>3.25</v>
@@ -30680,7 +30683,7 @@
         <v>194</v>
       </c>
       <c r="P142" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q142">
         <v>3.25</v>
@@ -31298,7 +31301,7 @@
         <v>196</v>
       </c>
       <c r="P145" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q145">
         <v>3.2</v>
@@ -31504,7 +31507,7 @@
         <v>197</v>
       </c>
       <c r="P146" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31710,7 +31713,7 @@
         <v>198</v>
       </c>
       <c r="P147" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q147">
         <v>3.4</v>
@@ -31916,7 +31919,7 @@
         <v>199</v>
       </c>
       <c r="P148" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q148">
         <v>2.88</v>
@@ -32122,7 +32125,7 @@
         <v>95</v>
       </c>
       <c r="P149" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32328,7 +32331,7 @@
         <v>200</v>
       </c>
       <c r="P150" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q150">
         <v>2.25</v>
@@ -32740,7 +32743,7 @@
         <v>132</v>
       </c>
       <c r="P152" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33152,7 +33155,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33436,7 +33439,7 @@
         <v>0.17</v>
       </c>
       <c r="AP155">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ155">
         <v>0.21</v>
@@ -33564,7 +33567,7 @@
         <v>95</v>
       </c>
       <c r="P156" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q156">
         <v>2.25</v>
@@ -33976,7 +33979,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q158">
         <v>4.75</v>
@@ -34594,7 +34597,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q161">
         <v>3.75</v>
@@ -35418,7 +35421,7 @@
         <v>95</v>
       </c>
       <c r="P165" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -35624,7 +35627,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q166">
         <v>2.5</v>
@@ -36860,7 +36863,7 @@
         <v>197</v>
       </c>
       <c r="P172" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37066,7 +37069,7 @@
         <v>172</v>
       </c>
       <c r="P173" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37350,7 +37353,7 @@
         <v>1</v>
       </c>
       <c r="AP174">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ174">
         <v>1.15</v>
@@ -37478,7 +37481,7 @@
         <v>214</v>
       </c>
       <c r="P175" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q175">
         <v>2.63</v>
@@ -37890,7 +37893,7 @@
         <v>216</v>
       </c>
       <c r="P177" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38383,7 +38386,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ179">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR179">
         <v>1.59</v>
@@ -38508,7 +38511,7 @@
         <v>142</v>
       </c>
       <c r="P180" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q180">
         <v>3.75</v>
@@ -38920,7 +38923,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q182">
         <v>3.4</v>
@@ -39332,7 +39335,7 @@
         <v>220</v>
       </c>
       <c r="P184" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q184">
         <v>3.2</v>
@@ -40156,7 +40159,7 @@
         <v>223</v>
       </c>
       <c r="P188" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q188">
         <v>5.5</v>
@@ -40774,7 +40777,7 @@
         <v>225</v>
       </c>
       <c r="P191" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -40980,7 +40983,7 @@
         <v>226</v>
       </c>
       <c r="P192" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q192">
         <v>5</v>
@@ -41804,7 +41807,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q196">
         <v>3</v>
@@ -41885,7 +41888,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ196">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR196">
         <v>1.31</v>
@@ -42706,7 +42709,7 @@
         <v>0.57</v>
       </c>
       <c r="AP200">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ200">
         <v>0.31</v>
@@ -42834,7 +42837,7 @@
         <v>95</v>
       </c>
       <c r="P201" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q201">
         <v>2.6</v>
@@ -44070,7 +44073,7 @@
         <v>233</v>
       </c>
       <c r="P207" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q207">
         <v>2.05</v>
@@ -44688,7 +44691,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44894,7 +44897,7 @@
         <v>235</v>
       </c>
       <c r="P211" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q211">
         <v>2.38</v>
@@ -45306,7 +45309,7 @@
         <v>237</v>
       </c>
       <c r="P213" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q213">
         <v>2.4</v>
@@ -45512,7 +45515,7 @@
         <v>95</v>
       </c>
       <c r="P214" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45718,7 +45721,7 @@
         <v>178</v>
       </c>
       <c r="P215" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q215">
         <v>3.2</v>
@@ -45799,7 +45802,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ215">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR215">
         <v>1.4</v>
@@ -46208,7 +46211,7 @@
         <v>0.67</v>
       </c>
       <c r="AP217">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ217">
         <v>0.5</v>
@@ -47572,7 +47575,7 @@
         <v>244</v>
       </c>
       <c r="P224" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q224">
         <v>2.88</v>
@@ -47778,7 +47781,7 @@
         <v>245</v>
       </c>
       <c r="P225" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q225">
         <v>3.2</v>
@@ -48190,7 +48193,7 @@
         <v>95</v>
       </c>
       <c r="P227" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q227">
         <v>3</v>
@@ -48602,7 +48605,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -49298,7 +49301,7 @@
         <v>1.56</v>
       </c>
       <c r="AP232">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ232">
         <v>1.38</v>
@@ -49426,7 +49429,7 @@
         <v>95</v>
       </c>
       <c r="P233" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49632,7 +49635,7 @@
         <v>95</v>
       </c>
       <c r="P234" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -50868,7 +50871,7 @@
         <v>252</v>
       </c>
       <c r="P240" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q240">
         <v>2.5</v>
@@ -51486,7 +51489,7 @@
         <v>253</v>
       </c>
       <c r="P243" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q243">
         <v>3.1</v>
@@ -51692,7 +51695,7 @@
         <v>254</v>
       </c>
       <c r="P244" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -52104,7 +52107,7 @@
         <v>244</v>
       </c>
       <c r="P246" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52185,7 +52188,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ246">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR246">
         <v>1.05</v>
@@ -52722,7 +52725,7 @@
         <v>131</v>
       </c>
       <c r="P249" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -53340,7 +53343,7 @@
         <v>260</v>
       </c>
       <c r="P252" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q252">
         <v>3.2</v>
@@ -53752,7 +53755,7 @@
         <v>262</v>
       </c>
       <c r="P254" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -54448,7 +54451,7 @@
         <v>0.22</v>
       </c>
       <c r="AP257">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ257">
         <v>0.54</v>
@@ -54782,7 +54785,7 @@
         <v>266</v>
       </c>
       <c r="P259" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q259">
         <v>5.5</v>
@@ -54988,7 +54991,7 @@
         <v>267</v>
       </c>
       <c r="P260" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
@@ -55400,7 +55403,7 @@
         <v>269</v>
       </c>
       <c r="P262" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q262">
         <v>3.5</v>
@@ -56018,7 +56021,7 @@
         <v>95</v>
       </c>
       <c r="P265" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56224,7 +56227,7 @@
         <v>271</v>
       </c>
       <c r="P266" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q266">
         <v>2.25</v>
@@ -56305,7 +56308,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ266">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR266">
         <v>1.6</v>
@@ -56842,7 +56845,7 @@
         <v>274</v>
       </c>
       <c r="P269" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57460,7 +57463,7 @@
         <v>277</v>
       </c>
       <c r="P272" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q272">
         <v>3.5</v>
@@ -57666,7 +57669,7 @@
         <v>95</v>
       </c>
       <c r="P273" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q273">
         <v>6</v>
@@ -58078,7 +58081,7 @@
         <v>278</v>
       </c>
       <c r="P275" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q275">
         <v>3.2</v>
@@ -58159,7 +58162,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ275">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR275">
         <v>1.19</v>
@@ -58284,7 +58287,7 @@
         <v>279</v>
       </c>
       <c r="P276" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q276">
         <v>2.5</v>
@@ -58490,7 +58493,7 @@
         <v>280</v>
       </c>
       <c r="P277" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58696,7 +58699,7 @@
         <v>281</v>
       </c>
       <c r="P278" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q278">
         <v>2.6</v>
@@ -60550,7 +60553,7 @@
         <v>285</v>
       </c>
       <c r="P287" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q287">
         <v>3.75</v>
@@ -60962,7 +60965,7 @@
         <v>286</v>
       </c>
       <c r="P289" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q289">
         <v>2.38</v>
@@ -61168,7 +61171,7 @@
         <v>287</v>
       </c>
       <c r="P290" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61786,7 +61789,7 @@
         <v>198</v>
       </c>
       <c r="P293" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q293">
         <v>1.95</v>
@@ -61864,7 +61867,7 @@
         <v>1.36</v>
       </c>
       <c r="AP293">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ293">
         <v>1.23</v>
@@ -61992,7 +61995,7 @@
         <v>289</v>
       </c>
       <c r="P294" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q294">
         <v>3.4</v>
@@ -62610,7 +62613,7 @@
         <v>290</v>
       </c>
       <c r="P297" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -63434,7 +63437,7 @@
         <v>291</v>
       </c>
       <c r="P301" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q301">
         <v>3</v>
@@ -63640,7 +63643,7 @@
         <v>204</v>
       </c>
       <c r="P302" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -64052,7 +64055,7 @@
         <v>293</v>
       </c>
       <c r="P304" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q304">
         <v>3.75</v>
@@ -64258,7 +64261,7 @@
         <v>294</v>
       </c>
       <c r="P305" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q305">
         <v>6.5</v>
@@ -64670,7 +64673,7 @@
         <v>200</v>
       </c>
       <c r="P307" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q307">
         <v>2.2</v>
@@ -65288,7 +65291,7 @@
         <v>231</v>
       </c>
       <c r="P310" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
@@ -67348,7 +67351,7 @@
         <v>95</v>
       </c>
       <c r="P320" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q320">
         <v>3.1</v>
@@ -68123,6 +68126,212 @@
       </c>
       <c r="BP323">
         <v>1.82</v>
+      </c>
+    </row>
+    <row r="324" spans="1:68">
+      <c r="A324" s="1">
+        <v>323</v>
+      </c>
+      <c r="B324">
+        <v>7479060</v>
+      </c>
+      <c r="C324" t="s">
+        <v>68</v>
+      </c>
+      <c r="D324" t="s">
+        <v>69</v>
+      </c>
+      <c r="E324" s="2">
+        <v>45676.375</v>
+      </c>
+      <c r="F324">
+        <v>27</v>
+      </c>
+      <c r="G324" t="s">
+        <v>76</v>
+      </c>
+      <c r="H324" t="s">
+        <v>80</v>
+      </c>
+      <c r="I324">
+        <v>1</v>
+      </c>
+      <c r="J324">
+        <v>0</v>
+      </c>
+      <c r="K324">
+        <v>1</v>
+      </c>
+      <c r="L324">
+        <v>3</v>
+      </c>
+      <c r="M324">
+        <v>0</v>
+      </c>
+      <c r="N324">
+        <v>3</v>
+      </c>
+      <c r="O324" t="s">
+        <v>301</v>
+      </c>
+      <c r="P324" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q324">
+        <v>1.83</v>
+      </c>
+      <c r="R324">
+        <v>2.4</v>
+      </c>
+      <c r="S324">
+        <v>8</v>
+      </c>
+      <c r="T324">
+        <v>1.36</v>
+      </c>
+      <c r="U324">
+        <v>3</v>
+      </c>
+      <c r="V324">
+        <v>2.63</v>
+      </c>
+      <c r="W324">
+        <v>1.44</v>
+      </c>
+      <c r="X324">
+        <v>7</v>
+      </c>
+      <c r="Y324">
+        <v>1.1</v>
+      </c>
+      <c r="Z324">
+        <v>1.35</v>
+      </c>
+      <c r="AA324">
+        <v>5</v>
+      </c>
+      <c r="AB324">
+        <v>8.75</v>
+      </c>
+      <c r="AC324">
+        <v>1.03</v>
+      </c>
+      <c r="AD324">
+        <v>13</v>
+      </c>
+      <c r="AE324">
+        <v>1.26</v>
+      </c>
+      <c r="AF324">
+        <v>4</v>
+      </c>
+      <c r="AG324">
+        <v>1.72</v>
+      </c>
+      <c r="AH324">
+        <v>2.05</v>
+      </c>
+      <c r="AI324">
+        <v>2.2</v>
+      </c>
+      <c r="AJ324">
+        <v>1.62</v>
+      </c>
+      <c r="AK324">
+        <v>1.07</v>
+      </c>
+      <c r="AL324">
+        <v>1.18</v>
+      </c>
+      <c r="AM324">
+        <v>3.1</v>
+      </c>
+      <c r="AN324">
+        <v>2.46</v>
+      </c>
+      <c r="AO324">
+        <v>1.42</v>
+      </c>
+      <c r="AP324">
+        <v>2.5</v>
+      </c>
+      <c r="AQ324">
+        <v>1.31</v>
+      </c>
+      <c r="AR324">
+        <v>1.89</v>
+      </c>
+      <c r="AS324">
+        <v>1.21</v>
+      </c>
+      <c r="AT324">
+        <v>3.1</v>
+      </c>
+      <c r="AU324">
+        <v>6</v>
+      </c>
+      <c r="AV324">
+        <v>4</v>
+      </c>
+      <c r="AW324">
+        <v>11</v>
+      </c>
+      <c r="AX324">
+        <v>3</v>
+      </c>
+      <c r="AY324">
+        <v>22</v>
+      </c>
+      <c r="AZ324">
+        <v>9</v>
+      </c>
+      <c r="BA324">
+        <v>9</v>
+      </c>
+      <c r="BB324">
+        <v>6</v>
+      </c>
+      <c r="BC324">
+        <v>15</v>
+      </c>
+      <c r="BD324">
+        <v>1.26</v>
+      </c>
+      <c r="BE324">
+        <v>8</v>
+      </c>
+      <c r="BF324">
+        <v>4.1</v>
+      </c>
+      <c r="BG324">
+        <v>1.15</v>
+      </c>
+      <c r="BH324">
+        <v>4.6</v>
+      </c>
+      <c r="BI324">
+        <v>1.28</v>
+      </c>
+      <c r="BJ324">
+        <v>3.3</v>
+      </c>
+      <c r="BK324">
+        <v>1.47</v>
+      </c>
+      <c r="BL324">
+        <v>2.48</v>
+      </c>
+      <c r="BM324">
+        <v>1.73</v>
+      </c>
+      <c r="BN324">
+        <v>1.96</v>
+      </c>
+      <c r="BO324">
+        <v>2.12</v>
+      </c>
+      <c r="BP324">
+        <v>1.62</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="413">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -922,6 +922,21 @@
     <t>['3', '88', '90+6']</t>
   </si>
   <si>
+    <t>['90']</t>
+  </si>
+  <si>
+    <t>['22', '59', '69']</t>
+  </si>
+  <si>
+    <t>['29', '83']</t>
+  </si>
+  <si>
+    <t>['84']</t>
+  </si>
+  <si>
+    <t>['2', '19']</t>
+  </si>
+  <si>
     <t>['67', '88']</t>
   </si>
   <si>
@@ -935,9 +950,6 @@
   </si>
   <si>
     <t>['23', '41', '90+2']</t>
-  </si>
-  <si>
-    <t>['84']</t>
   </si>
   <si>
     <t>['18', '89']</t>
@@ -1055,9 +1067,6 @@
   </si>
   <si>
     <t>['15', '37']</t>
-  </si>
-  <si>
-    <t>['90']</t>
   </si>
   <si>
     <t>['16', '45+3', '48']</t>
@@ -1226,6 +1235,24 @@
   </si>
   <si>
     <t>['4', '66']</t>
+  </si>
+  <si>
+    <t>['17', '56']</t>
+  </si>
+  <si>
+    <t>['11', '26']</t>
+  </si>
+  <si>
+    <t>['47', '68']</t>
+  </si>
+  <si>
+    <t>['41', '48']</t>
+  </si>
+  <si>
+    <t>['64', '70']</t>
+  </si>
+  <si>
+    <t>['45+1', '90+7']</t>
   </si>
 </sst>
 </file>
@@ -1587,7 +1614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP324"/>
+  <dimension ref="A1:BP332"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1843,7 +1870,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -1921,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ2">
         <v>0.5</v>
@@ -2049,7 +2076,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2130,7 +2157,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ3">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2255,7 +2282,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2336,7 +2363,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ4">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2539,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ5">
         <v>0.93</v>
@@ -2667,7 +2694,7 @@
         <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -2745,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ6">
         <v>0.86</v>
@@ -2954,7 +2981,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ7">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3079,7 +3106,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q8">
         <v>1.83</v>
@@ -3285,7 +3312,7 @@
         <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3363,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3491,7 +3518,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -3572,7 +3599,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ10">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3775,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -4109,7 +4136,7 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4315,7 +4342,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -4805,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ16">
         <v>1.38</v>
@@ -5014,7 +5041,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ17">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5139,7 +5166,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -5220,7 +5247,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ18">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5423,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ19">
         <v>0.77</v>
@@ -5629,10 +5656,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ20">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5757,7 +5784,7 @@
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5963,7 +5990,7 @@
         <v>111</v>
       </c>
       <c r="P22" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q22">
         <v>2.6</v>
@@ -6250,7 +6277,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ23">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6787,7 +6814,7 @@
         <v>95</v>
       </c>
       <c r="P26" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -7071,7 +7098,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ27">
         <v>0.83</v>
@@ -7486,7 +7513,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ29">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR29">
         <v>1.69</v>
@@ -7611,7 +7638,7 @@
         <v>117</v>
       </c>
       <c r="P30" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -7689,7 +7716,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ30">
         <v>0.5</v>
@@ -7895,7 +7922,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ31">
         <v>0.5</v>
@@ -8310,7 +8337,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ33">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR33">
         <v>0</v>
@@ -8513,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ34">
         <v>0.54</v>
@@ -8641,7 +8668,7 @@
         <v>122</v>
       </c>
       <c r="P35" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8722,7 +8749,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ35">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR35">
         <v>0.95</v>
@@ -8847,7 +8874,7 @@
         <v>123</v>
       </c>
       <c r="P36" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8928,7 +8955,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ36">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR36">
         <v>1.57</v>
@@ -9131,10 +9158,10 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ37">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR37">
         <v>1.5</v>
@@ -9259,7 +9286,7 @@
         <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q38">
         <v>2.4</v>
@@ -9340,7 +9367,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ38">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR38">
         <v>1.01</v>
@@ -9671,7 +9698,7 @@
         <v>95</v>
       </c>
       <c r="P40" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q40">
         <v>4.5</v>
@@ -9877,7 +9904,7 @@
         <v>95</v>
       </c>
       <c r="P41" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -10289,7 +10316,7 @@
         <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q43">
         <v>4.33</v>
@@ -10370,7 +10397,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ43">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR43">
         <v>1.59</v>
@@ -10779,7 +10806,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ45">
         <v>1.31</v>
@@ -11191,7 +11218,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ47">
         <v>1</v>
@@ -11397,10 +11424,10 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ48">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR48">
         <v>1.23</v>
@@ -11731,7 +11758,7 @@
         <v>95</v>
       </c>
       <c r="P50" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -11809,10 +11836,10 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ50">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR50">
         <v>1.4</v>
@@ -12221,10 +12248,10 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ52">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR52">
         <v>1.45</v>
@@ -12427,7 +12454,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ53">
         <v>0.77</v>
@@ -12633,10 +12660,10 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ54">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR54">
         <v>1.24</v>
@@ -12839,10 +12866,10 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ55">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR55">
         <v>1.71</v>
@@ -12967,7 +12994,7 @@
         <v>135</v>
       </c>
       <c r="P56" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q56">
         <v>4.5</v>
@@ -13048,7 +13075,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ56">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR56">
         <v>1.63</v>
@@ -13254,7 +13281,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ57">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR57">
         <v>1.82</v>
@@ -13457,7 +13484,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ58">
         <v>0.93</v>
@@ -13663,7 +13690,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13791,7 +13818,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13869,10 +13896,10 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ60">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR60">
         <v>1.85</v>
@@ -13997,7 +14024,7 @@
         <v>95</v>
       </c>
       <c r="P61" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q61">
         <v>4.33</v>
@@ -14078,7 +14105,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ61">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR61">
         <v>1.22</v>
@@ -14203,7 +14230,7 @@
         <v>139</v>
       </c>
       <c r="P62" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -15027,7 +15054,7 @@
         <v>95</v>
       </c>
       <c r="P66" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q66">
         <v>5.5</v>
@@ -15645,7 +15672,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q69">
         <v>2.05</v>
@@ -16057,7 +16084,7 @@
         <v>147</v>
       </c>
       <c r="P71" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -16675,7 +16702,7 @@
         <v>149</v>
       </c>
       <c r="P74" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q74">
         <v>3.9</v>
@@ -16756,7 +16783,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ74">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR74">
         <v>1.58</v>
@@ -16959,10 +16986,10 @@
         <v>1.67</v>
       </c>
       <c r="AP75">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ75">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR75">
         <v>1.35</v>
@@ -17087,7 +17114,7 @@
         <v>151</v>
       </c>
       <c r="P76" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17165,7 +17192,7 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ76">
         <v>0.93</v>
@@ -17293,7 +17320,7 @@
         <v>152</v>
       </c>
       <c r="P77" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q77">
         <v>3.75</v>
@@ -17374,7 +17401,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ77">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR77">
         <v>1.68</v>
@@ -17577,7 +17604,7 @@
         <v>2</v>
       </c>
       <c r="AP78">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ78">
         <v>2</v>
@@ -17705,7 +17732,7 @@
         <v>153</v>
       </c>
       <c r="P79" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17783,10 +17810,10 @@
         <v>2</v>
       </c>
       <c r="AP79">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ79">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR79">
         <v>1.74</v>
@@ -17989,7 +18016,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ80">
         <v>0.77</v>
@@ -18117,7 +18144,7 @@
         <v>155</v>
       </c>
       <c r="P81" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q81">
         <v>2.63</v>
@@ -18195,10 +18222,10 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ81">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR81">
         <v>1.39</v>
@@ -18401,10 +18428,10 @@
         <v>0.33</v>
       </c>
       <c r="AP82">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ82">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR82">
         <v>1.37</v>
@@ -18610,7 +18637,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ83">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR83">
         <v>1.1</v>
@@ -18816,7 +18843,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ84">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR84">
         <v>1.79</v>
@@ -19019,7 +19046,7 @@
         <v>0.33</v>
       </c>
       <c r="AP85">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ85">
         <v>1</v>
@@ -19765,7 +19792,7 @@
         <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q89">
         <v>2.1</v>
@@ -20383,7 +20410,7 @@
         <v>162</v>
       </c>
       <c r="P92" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q92">
         <v>2.85</v>
@@ -21619,7 +21646,7 @@
         <v>165</v>
       </c>
       <c r="P98" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -22318,7 +22345,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ101">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR101">
         <v>1.42</v>
@@ -22443,7 +22470,7 @@
         <v>119</v>
       </c>
       <c r="P102" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q102">
         <v>2.5</v>
@@ -22649,7 +22676,7 @@
         <v>168</v>
       </c>
       <c r="P103" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22936,7 +22963,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ104">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR104">
         <v>1.55</v>
@@ -23139,7 +23166,7 @@
         <v>0.75</v>
       </c>
       <c r="AP105">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ105">
         <v>0.77</v>
@@ -23345,7 +23372,7 @@
         <v>1.5</v>
       </c>
       <c r="AP106">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ106">
         <v>1.38</v>
@@ -23757,10 +23784,10 @@
         <v>1.25</v>
       </c>
       <c r="AP108">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ108">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR108">
         <v>1.27</v>
@@ -23966,7 +23993,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ109">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR109">
         <v>1.56</v>
@@ -24172,7 +24199,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ110">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR110">
         <v>1.76</v>
@@ -24790,7 +24817,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ113">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR113">
         <v>1.29</v>
@@ -24993,10 +25020,10 @@
         <v>2.25</v>
       </c>
       <c r="AP114">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ114">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR114">
         <v>1.12</v>
@@ -25121,7 +25148,7 @@
         <v>95</v>
       </c>
       <c r="P115" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q115">
         <v>3.4</v>
@@ -25327,7 +25354,7 @@
         <v>178</v>
       </c>
       <c r="P116" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25739,7 +25766,7 @@
         <v>95</v>
       </c>
       <c r="P118" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
@@ -25817,7 +25844,7 @@
         <v>0.5</v>
       </c>
       <c r="AP118">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ118">
         <v>1</v>
@@ -26023,7 +26050,7 @@
         <v>0.75</v>
       </c>
       <c r="AP119">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ119">
         <v>1</v>
@@ -26229,7 +26256,7 @@
         <v>0</v>
       </c>
       <c r="AP120">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ120">
         <v>0.5</v>
@@ -26435,10 +26462,10 @@
         <v>1.5</v>
       </c>
       <c r="AP121">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ121">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR121">
         <v>1.53</v>
@@ -26769,7 +26796,7 @@
         <v>182</v>
       </c>
       <c r="P123" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -26975,7 +27002,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q124">
         <v>3</v>
@@ -27671,7 +27698,7 @@
         <v>0.2</v>
       </c>
       <c r="AP127">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ127">
         <v>0.5</v>
@@ -27880,7 +27907,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ128">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR128">
         <v>1.8</v>
@@ -28083,7 +28110,7 @@
         <v>2</v>
       </c>
       <c r="AP129">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ129">
         <v>2</v>
@@ -28289,10 +28316,10 @@
         <v>2</v>
       </c>
       <c r="AP130">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ130">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR130">
         <v>1.41</v>
@@ -28417,7 +28444,7 @@
         <v>187</v>
       </c>
       <c r="P131" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28498,7 +28525,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ131">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR131">
         <v>1.3</v>
@@ -28701,7 +28728,7 @@
         <v>0.2</v>
       </c>
       <c r="AP132">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ132">
         <v>0.21</v>
@@ -28907,10 +28934,10 @@
         <v>1.6</v>
       </c>
       <c r="AP133">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ133">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR133">
         <v>1.89</v>
@@ -29035,7 +29062,7 @@
         <v>162</v>
       </c>
       <c r="P134" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29447,7 +29474,7 @@
         <v>190</v>
       </c>
       <c r="P136" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -29528,7 +29555,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ136">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR136">
         <v>1.84</v>
@@ -29731,7 +29758,7 @@
         <v>0.6</v>
       </c>
       <c r="AP137">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ137">
         <v>1.23</v>
@@ -29859,7 +29886,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>347</v>
+        <v>302</v>
       </c>
       <c r="Q138">
         <v>3.25</v>
@@ -29937,7 +29964,7 @@
         <v>0.6</v>
       </c>
       <c r="AP138">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ138">
         <v>0.83</v>
@@ -30146,7 +30173,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ139">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR139">
         <v>1.36</v>
@@ -30683,7 +30710,7 @@
         <v>194</v>
       </c>
       <c r="P142" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q142">
         <v>3.25</v>
@@ -30764,7 +30791,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ142">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR142">
         <v>1.64</v>
@@ -30967,7 +30994,7 @@
         <v>1.4</v>
       </c>
       <c r="AP143">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ143">
         <v>1.08</v>
@@ -31176,7 +31203,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ144">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR144">
         <v>1.29</v>
@@ -31301,7 +31328,7 @@
         <v>196</v>
       </c>
       <c r="P145" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q145">
         <v>3.2</v>
@@ -31507,7 +31534,7 @@
         <v>197</v>
       </c>
       <c r="P146" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31588,7 +31615,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ146">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR146">
         <v>1.37</v>
@@ -31713,7 +31740,7 @@
         <v>198</v>
       </c>
       <c r="P147" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q147">
         <v>3.4</v>
@@ -31791,7 +31818,7 @@
         <v>0.67</v>
       </c>
       <c r="AP147">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ147">
         <v>1</v>
@@ -31919,7 +31946,7 @@
         <v>199</v>
       </c>
       <c r="P148" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q148">
         <v>2.88</v>
@@ -32125,7 +32152,7 @@
         <v>95</v>
       </c>
       <c r="P149" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32203,10 +32230,10 @@
         <v>1.33</v>
       </c>
       <c r="AP149">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ149">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR149">
         <v>1.31</v>
@@ -32331,7 +32358,7 @@
         <v>200</v>
       </c>
       <c r="P150" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q150">
         <v>2.25</v>
@@ -32409,7 +32436,7 @@
         <v>0.83</v>
       </c>
       <c r="AP150">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ150">
         <v>0.5</v>
@@ -32743,7 +32770,7 @@
         <v>132</v>
       </c>
       <c r="P152" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33030,7 +33057,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ153">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR153">
         <v>1.73</v>
@@ -33155,7 +33182,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33567,7 +33594,7 @@
         <v>95</v>
       </c>
       <c r="P156" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q156">
         <v>2.25</v>
@@ -33645,10 +33672,10 @@
         <v>0.5</v>
       </c>
       <c r="AP156">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ156">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR156">
         <v>1.84</v>
@@ -33851,7 +33878,7 @@
         <v>1.83</v>
       </c>
       <c r="AP157">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ157">
         <v>2</v>
@@ -33979,7 +34006,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q158">
         <v>4.75</v>
@@ -34469,7 +34496,7 @@
         <v>1.33</v>
       </c>
       <c r="AP160">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ160">
         <v>1.08</v>
@@ -34597,7 +34624,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q161">
         <v>3.75</v>
@@ -34678,7 +34705,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ161">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR161">
         <v>1.36</v>
@@ -34881,7 +34908,7 @@
         <v>0.86</v>
       </c>
       <c r="AP162">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ162">
         <v>0.86</v>
@@ -35293,7 +35320,7 @@
         <v>1.67</v>
       </c>
       <c r="AP164">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ164">
         <v>1.62</v>
@@ -35421,7 +35448,7 @@
         <v>95</v>
       </c>
       <c r="P165" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -35499,7 +35526,7 @@
         <v>0.67</v>
       </c>
       <c r="AP165">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ165">
         <v>0.77</v>
@@ -35627,7 +35654,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q166">
         <v>2.5</v>
@@ -35914,7 +35941,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ167">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR167">
         <v>1.4</v>
@@ -36120,7 +36147,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ168">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR168">
         <v>1.18</v>
@@ -36529,7 +36556,7 @@
         <v>0.33</v>
       </c>
       <c r="AP170">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ170">
         <v>0.54</v>
@@ -36735,10 +36762,10 @@
         <v>0.67</v>
       </c>
       <c r="AP171">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ171">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR171">
         <v>1.68</v>
@@ -36863,7 +36890,7 @@
         <v>197</v>
       </c>
       <c r="P172" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37069,7 +37096,7 @@
         <v>172</v>
       </c>
       <c r="P173" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37356,7 +37383,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ174">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR174">
         <v>1.88</v>
@@ -37481,7 +37508,7 @@
         <v>214</v>
       </c>
       <c r="P175" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q175">
         <v>2.63</v>
@@ -37562,7 +37589,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ175">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR175">
         <v>1.34</v>
@@ -37768,7 +37795,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ176">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR176">
         <v>1.24</v>
@@ -37893,7 +37920,7 @@
         <v>216</v>
       </c>
       <c r="P177" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -37971,7 +37998,7 @@
         <v>0.14</v>
       </c>
       <c r="AP177">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ177">
         <v>0.21</v>
@@ -38511,7 +38538,7 @@
         <v>142</v>
       </c>
       <c r="P180" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q180">
         <v>3.75</v>
@@ -38589,10 +38616,10 @@
         <v>1.71</v>
       </c>
       <c r="AP180">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ180">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR180">
         <v>1.3</v>
@@ -38923,7 +38950,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q182">
         <v>3.4</v>
@@ -39335,7 +39362,7 @@
         <v>220</v>
       </c>
       <c r="P184" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q184">
         <v>3.2</v>
@@ -39416,7 +39443,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ184">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR184">
         <v>1.86</v>
@@ -39622,7 +39649,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ185">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR185">
         <v>1.45</v>
@@ -40031,10 +40058,10 @@
         <v>1.75</v>
       </c>
       <c r="AP187">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ187">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR187">
         <v>1.36</v>
@@ -40159,7 +40186,7 @@
         <v>223</v>
       </c>
       <c r="P188" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q188">
         <v>5.5</v>
@@ -40237,7 +40264,7 @@
         <v>1.43</v>
       </c>
       <c r="AP188">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ188">
         <v>1.38</v>
@@ -40777,7 +40804,7 @@
         <v>225</v>
       </c>
       <c r="P191" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -40983,7 +41010,7 @@
         <v>226</v>
       </c>
       <c r="P192" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q192">
         <v>5</v>
@@ -41061,7 +41088,7 @@
         <v>1.43</v>
       </c>
       <c r="AP192">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ192">
         <v>1.62</v>
@@ -41267,7 +41294,7 @@
         <v>1.5</v>
       </c>
       <c r="AP193">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ193">
         <v>1</v>
@@ -41476,7 +41503,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ194">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR194">
         <v>1.32</v>
@@ -41807,7 +41834,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q196">
         <v>3</v>
@@ -41885,7 +41912,7 @@
         <v>1</v>
       </c>
       <c r="AP196">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ196">
         <v>1.31</v>
@@ -42094,7 +42121,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ197">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR197">
         <v>1.46</v>
@@ -42506,7 +42533,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ199">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR199">
         <v>1.33</v>
@@ -42712,7 +42739,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ200">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR200">
         <v>1.86</v>
@@ -42837,7 +42864,7 @@
         <v>95</v>
       </c>
       <c r="P201" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q201">
         <v>2.6</v>
@@ -42918,7 +42945,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ201">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR201">
         <v>1.58</v>
@@ -43121,7 +43148,7 @@
         <v>0.86</v>
       </c>
       <c r="AP202">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ202">
         <v>1.23</v>
@@ -43327,7 +43354,7 @@
         <v>0.88</v>
       </c>
       <c r="AP203">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ203">
         <v>1</v>
@@ -43536,7 +43563,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ204">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR204">
         <v>1.53</v>
@@ -43739,10 +43766,10 @@
         <v>1.13</v>
       </c>
       <c r="AP205">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ205">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR205">
         <v>1.43</v>
@@ -43945,7 +43972,7 @@
         <v>1</v>
       </c>
       <c r="AP206">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ206">
         <v>0.83</v>
@@ -44073,7 +44100,7 @@
         <v>233</v>
       </c>
       <c r="P207" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q207">
         <v>2.05</v>
@@ -44151,7 +44178,7 @@
         <v>1</v>
       </c>
       <c r="AP207">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ207">
         <v>1.08</v>
@@ -44357,7 +44384,7 @@
         <v>1.63</v>
       </c>
       <c r="AP208">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ208">
         <v>1.62</v>
@@ -44566,7 +44593,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ209">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR209">
         <v>1.21</v>
@@ -44691,7 +44718,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44772,7 +44799,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ210">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR210">
         <v>1.48</v>
@@ -44897,7 +44924,7 @@
         <v>235</v>
       </c>
       <c r="P211" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q211">
         <v>2.38</v>
@@ -44978,7 +45005,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ211">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR211">
         <v>1.94</v>
@@ -45309,7 +45336,7 @@
         <v>237</v>
       </c>
       <c r="P213" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q213">
         <v>2.4</v>
@@ -45387,7 +45414,7 @@
         <v>0.75</v>
       </c>
       <c r="AP213">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ213">
         <v>0.5</v>
@@ -45515,7 +45542,7 @@
         <v>95</v>
       </c>
       <c r="P214" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45721,7 +45748,7 @@
         <v>178</v>
       </c>
       <c r="P215" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q215">
         <v>3.2</v>
@@ -45799,7 +45826,7 @@
         <v>1.25</v>
       </c>
       <c r="AP215">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ215">
         <v>1.31</v>
@@ -46420,7 +46447,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ218">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR218">
         <v>1.44</v>
@@ -46829,7 +46856,7 @@
         <v>1.13</v>
       </c>
       <c r="AP220">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ220">
         <v>1.23</v>
@@ -47035,10 +47062,10 @@
         <v>0.78</v>
       </c>
       <c r="AP221">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ221">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR221">
         <v>1.38</v>
@@ -47575,7 +47602,7 @@
         <v>244</v>
       </c>
       <c r="P224" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q224">
         <v>2.88</v>
@@ -47781,7 +47808,7 @@
         <v>245</v>
       </c>
       <c r="P225" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q225">
         <v>3.2</v>
@@ -47862,7 +47889,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ225">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR225">
         <v>1.38</v>
@@ -48193,7 +48220,7 @@
         <v>95</v>
       </c>
       <c r="P227" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q227">
         <v>3</v>
@@ -48605,7 +48632,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -49429,7 +49456,7 @@
         <v>95</v>
       </c>
       <c r="P233" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49507,10 +49534,10 @@
         <v>1.6</v>
       </c>
       <c r="AP233">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ233">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR233">
         <v>1.32</v>
@@ -49635,7 +49662,7 @@
         <v>95</v>
       </c>
       <c r="P234" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -49716,7 +49743,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ234">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR234">
         <v>1.65</v>
@@ -49919,7 +49946,7 @@
         <v>0.78</v>
       </c>
       <c r="AP235">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ235">
         <v>0.86</v>
@@ -50334,7 +50361,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ237">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR237">
         <v>1.38</v>
@@ -50537,7 +50564,7 @@
         <v>0.78</v>
       </c>
       <c r="AP238">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ238">
         <v>0.5</v>
@@ -50871,7 +50898,7 @@
         <v>252</v>
       </c>
       <c r="P240" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q240">
         <v>2.5</v>
@@ -51158,7 +51185,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ241">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR241">
         <v>1.43</v>
@@ -51361,7 +51388,7 @@
         <v>1</v>
       </c>
       <c r="AP242">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ242">
         <v>0.83</v>
@@ -51489,7 +51516,7 @@
         <v>253</v>
       </c>
       <c r="P243" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q243">
         <v>3.1</v>
@@ -51570,7 +51597,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ243">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR243">
         <v>1.27</v>
@@ -51695,7 +51722,7 @@
         <v>254</v>
       </c>
       <c r="P244" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -51773,10 +51800,10 @@
         <v>1.5</v>
       </c>
       <c r="AP244">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ244">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR244">
         <v>1.43</v>
@@ -52107,7 +52134,7 @@
         <v>244</v>
       </c>
       <c r="P246" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52185,7 +52212,7 @@
         <v>1.44</v>
       </c>
       <c r="AP246">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ246">
         <v>1.31</v>
@@ -52391,10 +52418,10 @@
         <v>0.44</v>
       </c>
       <c r="AP247">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ247">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR247">
         <v>1.31</v>
@@ -52597,10 +52624,10 @@
         <v>1.7</v>
       </c>
       <c r="AP248">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ248">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR248">
         <v>1.45</v>
@@ -52725,7 +52752,7 @@
         <v>131</v>
       </c>
       <c r="P249" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -53343,7 +53370,7 @@
         <v>260</v>
       </c>
       <c r="P252" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q252">
         <v>3.2</v>
@@ -53421,7 +53448,7 @@
         <v>1.27</v>
       </c>
       <c r="AP252">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ252">
         <v>1</v>
@@ -53630,7 +53657,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ253">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR253">
         <v>1.35</v>
@@ -53755,7 +53782,7 @@
         <v>262</v>
       </c>
       <c r="P254" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -54248,7 +54275,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ256">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR256">
         <v>1.63</v>
@@ -54657,7 +54684,7 @@
         <v>1.5</v>
       </c>
       <c r="AP258">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ258">
         <v>1.23</v>
@@ -54785,7 +54812,7 @@
         <v>266</v>
       </c>
       <c r="P259" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q259">
         <v>5.5</v>
@@ -54991,7 +55018,7 @@
         <v>267</v>
       </c>
       <c r="P260" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
@@ -55072,7 +55099,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ260">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR260">
         <v>1.65</v>
@@ -55403,7 +55430,7 @@
         <v>269</v>
       </c>
       <c r="P262" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q262">
         <v>3.5</v>
@@ -55481,10 +55508,10 @@
         <v>0.6</v>
       </c>
       <c r="AP262">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ262">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR262">
         <v>1.06</v>
@@ -56021,7 +56048,7 @@
         <v>95</v>
       </c>
       <c r="P265" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56227,7 +56254,7 @@
         <v>271</v>
       </c>
       <c r="P266" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q266">
         <v>2.25</v>
@@ -56305,7 +56332,7 @@
         <v>1.6</v>
       </c>
       <c r="AP266">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ266">
         <v>1.31</v>
@@ -56511,10 +56538,10 @@
         <v>1.1</v>
       </c>
       <c r="AP267">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ267">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR267">
         <v>1.39</v>
@@ -56720,7 +56747,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ268">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR268">
         <v>1.48</v>
@@ -56845,7 +56872,7 @@
         <v>274</v>
       </c>
       <c r="P269" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -56923,10 +56950,10 @@
         <v>1.64</v>
       </c>
       <c r="AP269">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ269">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR269">
         <v>1.31</v>
@@ -57129,7 +57156,7 @@
         <v>0.7</v>
       </c>
       <c r="AP270">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ270">
         <v>0.5</v>
@@ -57463,7 +57490,7 @@
         <v>277</v>
       </c>
       <c r="P272" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q272">
         <v>3.5</v>
@@ -57541,10 +57568,10 @@
         <v>1.55</v>
       </c>
       <c r="AP272">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ272">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR272">
         <v>1.43</v>
@@ -57669,7 +57696,7 @@
         <v>95</v>
       </c>
       <c r="P273" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Q273">
         <v>6</v>
@@ -57956,7 +57983,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ274">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR274">
         <v>1.41</v>
@@ -58081,7 +58108,7 @@
         <v>278</v>
       </c>
       <c r="P275" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q275">
         <v>3.2</v>
@@ -58287,7 +58314,7 @@
         <v>279</v>
       </c>
       <c r="P276" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q276">
         <v>2.5</v>
@@ -58368,7 +58395,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ276">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR276">
         <v>1.44</v>
@@ -58493,7 +58520,7 @@
         <v>280</v>
       </c>
       <c r="P277" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58571,10 +58598,10 @@
         <v>0.36</v>
       </c>
       <c r="AP277">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ277">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR277">
         <v>1.4</v>
@@ -58699,7 +58726,7 @@
         <v>281</v>
       </c>
       <c r="P278" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q278">
         <v>2.6</v>
@@ -58777,10 +58804,10 @@
         <v>0.55</v>
       </c>
       <c r="AP278">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ278">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR278">
         <v>1.47</v>
@@ -58986,7 +59013,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ279">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR279">
         <v>1.22</v>
@@ -59189,7 +59216,7 @@
         <v>0.17</v>
       </c>
       <c r="AP280">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ280">
         <v>0.21</v>
@@ -59395,7 +59422,7 @@
         <v>0.73</v>
       </c>
       <c r="AP281">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ281">
         <v>1.08</v>
@@ -60013,7 +60040,7 @@
         <v>1.55</v>
       </c>
       <c r="AP284">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ284">
         <v>1.62</v>
@@ -60219,7 +60246,7 @@
         <v>2</v>
       </c>
       <c r="AP285">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ285">
         <v>2</v>
@@ -60553,7 +60580,7 @@
         <v>285</v>
       </c>
       <c r="P287" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Q287">
         <v>3.75</v>
@@ -60837,7 +60864,7 @@
         <v>0.2</v>
       </c>
       <c r="AP288">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ288">
         <v>0.54</v>
@@ -60965,7 +60992,7 @@
         <v>286</v>
       </c>
       <c r="P289" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q289">
         <v>2.38</v>
@@ -61046,7 +61073,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ289">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR289">
         <v>1.34</v>
@@ -61171,7 +61198,7 @@
         <v>287</v>
       </c>
       <c r="P290" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61789,7 +61816,7 @@
         <v>198</v>
       </c>
       <c r="P293" t="s">
-        <v>347</v>
+        <v>302</v>
       </c>
       <c r="Q293">
         <v>1.95</v>
@@ -61995,7 +62022,7 @@
         <v>289</v>
       </c>
       <c r="P294" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q294">
         <v>3.4</v>
@@ -62076,7 +62103,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ294">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR294">
         <v>1.58</v>
@@ -62485,7 +62512,7 @@
         <v>1.36</v>
       </c>
       <c r="AP296">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ296">
         <v>1.38</v>
@@ -62613,7 +62640,7 @@
         <v>290</v>
       </c>
       <c r="P297" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -62694,7 +62721,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ297">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR297">
         <v>1.55</v>
@@ -63103,10 +63130,10 @@
         <v>1.38</v>
       </c>
       <c r="AP299">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ299">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR299">
         <v>1.49</v>
@@ -63309,7 +63336,7 @@
         <v>1.92</v>
       </c>
       <c r="AP300">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ300">
         <v>2</v>
@@ -63437,7 +63464,7 @@
         <v>291</v>
       </c>
       <c r="P301" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="Q301">
         <v>3</v>
@@ -63643,7 +63670,7 @@
         <v>204</v>
       </c>
       <c r="P302" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -63930,7 +63957,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ303">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR303">
         <v>1.45</v>
@@ -64055,7 +64082,7 @@
         <v>293</v>
       </c>
       <c r="P304" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="Q304">
         <v>3.75</v>
@@ -64133,10 +64160,10 @@
         <v>1.69</v>
       </c>
       <c r="AP304">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ304">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR304">
         <v>1.45</v>
@@ -64261,7 +64288,7 @@
         <v>294</v>
       </c>
       <c r="P305" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q305">
         <v>6.5</v>
@@ -64339,7 +64366,7 @@
         <v>1.67</v>
       </c>
       <c r="AP305">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ305">
         <v>1.62</v>
@@ -64673,7 +64700,7 @@
         <v>200</v>
       </c>
       <c r="P307" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q307">
         <v>2.2</v>
@@ -64751,10 +64778,10 @@
         <v>0.75</v>
       </c>
       <c r="AP307">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ307">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR307">
         <v>1.51</v>
@@ -65166,7 +65193,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ309">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR309">
         <v>1.61</v>
@@ -65291,7 +65318,7 @@
         <v>231</v>
       </c>
       <c r="P310" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
@@ -65781,7 +65808,7 @@
         <v>0.54</v>
       </c>
       <c r="AP312">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ312">
         <v>0.5</v>
@@ -65990,7 +66017,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ313">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR313">
         <v>1.47</v>
@@ -66402,7 +66429,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ315">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR315">
         <v>1.45</v>
@@ -66605,7 +66632,7 @@
         <v>0.92</v>
       </c>
       <c r="AP316">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ316">
         <v>1.08</v>
@@ -67017,7 +67044,7 @@
         <v>1.33</v>
       </c>
       <c r="AP318">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ318">
         <v>1.23</v>
@@ -67351,7 +67378,7 @@
         <v>95</v>
       </c>
       <c r="P320" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="Q320">
         <v>3.1</v>
@@ -67429,7 +67456,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP320">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ320">
         <v>0.86</v>
@@ -67844,7 +67871,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ322">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR322">
         <v>1.41</v>
@@ -68332,6 +68359,1654 @@
       </c>
       <c r="BP324">
         <v>1.62</v>
+      </c>
+    </row>
+    <row r="325" spans="1:68">
+      <c r="A325" s="1">
+        <v>324</v>
+      </c>
+      <c r="B325">
+        <v>7479075</v>
+      </c>
+      <c r="C325" t="s">
+        <v>68</v>
+      </c>
+      <c r="D325" t="s">
+        <v>69</v>
+      </c>
+      <c r="E325" s="2">
+        <v>45678.69791666666</v>
+      </c>
+      <c r="F325">
+        <v>28</v>
+      </c>
+      <c r="G325" t="s">
+        <v>87</v>
+      </c>
+      <c r="H325" t="s">
+        <v>71</v>
+      </c>
+      <c r="I325">
+        <v>0</v>
+      </c>
+      <c r="J325">
+        <v>1</v>
+      </c>
+      <c r="K325">
+        <v>1</v>
+      </c>
+      <c r="L325">
+        <v>1</v>
+      </c>
+      <c r="M325">
+        <v>2</v>
+      </c>
+      <c r="N325">
+        <v>3</v>
+      </c>
+      <c r="O325" t="s">
+        <v>302</v>
+      </c>
+      <c r="P325" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q325">
+        <v>2.5</v>
+      </c>
+      <c r="R325">
+        <v>2.3</v>
+      </c>
+      <c r="S325">
+        <v>4.33</v>
+      </c>
+      <c r="T325">
+        <v>1.33</v>
+      </c>
+      <c r="U325">
+        <v>3.25</v>
+      </c>
+      <c r="V325">
+        <v>2.63</v>
+      </c>
+      <c r="W325">
+        <v>1.44</v>
+      </c>
+      <c r="X325">
+        <v>6.5</v>
+      </c>
+      <c r="Y325">
+        <v>1.11</v>
+      </c>
+      <c r="Z325">
+        <v>2.05</v>
+      </c>
+      <c r="AA325">
+        <v>3.4</v>
+      </c>
+      <c r="AB325">
+        <v>3.5</v>
+      </c>
+      <c r="AC325">
+        <v>1.07</v>
+      </c>
+      <c r="AD325">
+        <v>10</v>
+      </c>
+      <c r="AE325">
+        <v>1.33</v>
+      </c>
+      <c r="AF325">
+        <v>3.3</v>
+      </c>
+      <c r="AG325">
+        <v>2</v>
+      </c>
+      <c r="AH325">
+        <v>1.73</v>
+      </c>
+      <c r="AI325">
+        <v>1.62</v>
+      </c>
+      <c r="AJ325">
+        <v>2.2</v>
+      </c>
+      <c r="AK325">
+        <v>1.28</v>
+      </c>
+      <c r="AL325">
+        <v>1.28</v>
+      </c>
+      <c r="AM325">
+        <v>1.78</v>
+      </c>
+      <c r="AN325">
+        <v>2.23</v>
+      </c>
+      <c r="AO325">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP325">
+        <v>2.07</v>
+      </c>
+      <c r="AQ325">
+        <v>0.86</v>
+      </c>
+      <c r="AR325">
+        <v>1.43</v>
+      </c>
+      <c r="AS325">
+        <v>1.05</v>
+      </c>
+      <c r="AT325">
+        <v>2.48</v>
+      </c>
+      <c r="AU325">
+        <v>5</v>
+      </c>
+      <c r="AV325">
+        <v>8</v>
+      </c>
+      <c r="AW325">
+        <v>6</v>
+      </c>
+      <c r="AX325">
+        <v>7</v>
+      </c>
+      <c r="AY325">
+        <v>14</v>
+      </c>
+      <c r="AZ325">
+        <v>18</v>
+      </c>
+      <c r="BA325">
+        <v>4</v>
+      </c>
+      <c r="BB325">
+        <v>2</v>
+      </c>
+      <c r="BC325">
+        <v>6</v>
+      </c>
+      <c r="BD325">
+        <v>1.57</v>
+      </c>
+      <c r="BE325">
+        <v>6.75</v>
+      </c>
+      <c r="BF325">
+        <v>2.65</v>
+      </c>
+      <c r="BG325">
+        <v>1.29</v>
+      </c>
+      <c r="BH325">
+        <v>3.2</v>
+      </c>
+      <c r="BI325">
+        <v>1.49</v>
+      </c>
+      <c r="BJ325">
+        <v>2.4</v>
+      </c>
+      <c r="BK325">
+        <v>1.81</v>
+      </c>
+      <c r="BL325">
+        <v>1.88</v>
+      </c>
+      <c r="BM325">
+        <v>2.25</v>
+      </c>
+      <c r="BN325">
+        <v>1.55</v>
+      </c>
+      <c r="BO325">
+        <v>2.9</v>
+      </c>
+      <c r="BP325">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="326" spans="1:68">
+      <c r="A326" s="1">
+        <v>325</v>
+      </c>
+      <c r="B326">
+        <v>7479073</v>
+      </c>
+      <c r="C326" t="s">
+        <v>68</v>
+      </c>
+      <c r="D326" t="s">
+        <v>69</v>
+      </c>
+      <c r="E326" s="2">
+        <v>45678.69791666666</v>
+      </c>
+      <c r="F326">
+        <v>28</v>
+      </c>
+      <c r="G326" t="s">
+        <v>73</v>
+      </c>
+      <c r="H326" t="s">
+        <v>81</v>
+      </c>
+      <c r="I326">
+        <v>1</v>
+      </c>
+      <c r="J326">
+        <v>2</v>
+      </c>
+      <c r="K326">
+        <v>3</v>
+      </c>
+      <c r="L326">
+        <v>3</v>
+      </c>
+      <c r="M326">
+        <v>2</v>
+      </c>
+      <c r="N326">
+        <v>5</v>
+      </c>
+      <c r="O326" t="s">
+        <v>303</v>
+      </c>
+      <c r="P326" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q326">
+        <v>3</v>
+      </c>
+      <c r="R326">
+        <v>2.2</v>
+      </c>
+      <c r="S326">
+        <v>3.5</v>
+      </c>
+      <c r="T326">
+        <v>1.4</v>
+      </c>
+      <c r="U326">
+        <v>2.75</v>
+      </c>
+      <c r="V326">
+        <v>2.75</v>
+      </c>
+      <c r="W326">
+        <v>1.4</v>
+      </c>
+      <c r="X326">
+        <v>8</v>
+      </c>
+      <c r="Y326">
+        <v>1.08</v>
+      </c>
+      <c r="Z326">
+        <v>2.6</v>
+      </c>
+      <c r="AA326">
+        <v>3.4</v>
+      </c>
+      <c r="AB326">
+        <v>2.62</v>
+      </c>
+      <c r="AC326">
+        <v>1.07</v>
+      </c>
+      <c r="AD326">
+        <v>9.5</v>
+      </c>
+      <c r="AE326">
+        <v>1.35</v>
+      </c>
+      <c r="AF326">
+        <v>3.25</v>
+      </c>
+      <c r="AG326">
+        <v>2.1</v>
+      </c>
+      <c r="AH326">
+        <v>1.67</v>
+      </c>
+      <c r="AI326">
+        <v>1.67</v>
+      </c>
+      <c r="AJ326">
+        <v>2.1</v>
+      </c>
+      <c r="AK326">
+        <v>1.52</v>
+      </c>
+      <c r="AL326">
+        <v>1.3</v>
+      </c>
+      <c r="AM326">
+        <v>1.45</v>
+      </c>
+      <c r="AN326">
+        <v>1.79</v>
+      </c>
+      <c r="AO326">
+        <v>0.31</v>
+      </c>
+      <c r="AP326">
+        <v>1.87</v>
+      </c>
+      <c r="AQ326">
+        <v>0.29</v>
+      </c>
+      <c r="AR326">
+        <v>1.16</v>
+      </c>
+      <c r="AS326">
+        <v>1.13</v>
+      </c>
+      <c r="AT326">
+        <v>2.29</v>
+      </c>
+      <c r="AU326">
+        <v>7</v>
+      </c>
+      <c r="AV326">
+        <v>4</v>
+      </c>
+      <c r="AW326">
+        <v>8</v>
+      </c>
+      <c r="AX326">
+        <v>4</v>
+      </c>
+      <c r="AY326">
+        <v>20</v>
+      </c>
+      <c r="AZ326">
+        <v>11</v>
+      </c>
+      <c r="BA326">
+        <v>6</v>
+      </c>
+      <c r="BB326">
+        <v>5</v>
+      </c>
+      <c r="BC326">
+        <v>11</v>
+      </c>
+      <c r="BD326">
+        <v>2.2</v>
+      </c>
+      <c r="BE326">
+        <v>6.75</v>
+      </c>
+      <c r="BF326">
+        <v>1.79</v>
+      </c>
+      <c r="BG326">
+        <v>1.19</v>
+      </c>
+      <c r="BH326">
+        <v>4.1</v>
+      </c>
+      <c r="BI326">
+        <v>1.34</v>
+      </c>
+      <c r="BJ326">
+        <v>2.9</v>
+      </c>
+      <c r="BK326">
+        <v>1.56</v>
+      </c>
+      <c r="BL326">
+        <v>2.23</v>
+      </c>
+      <c r="BM326">
+        <v>1.9</v>
+      </c>
+      <c r="BN326">
+        <v>1.79</v>
+      </c>
+      <c r="BO326">
+        <v>2.38</v>
+      </c>
+      <c r="BP326">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="327" spans="1:68">
+      <c r="A327" s="1">
+        <v>326</v>
+      </c>
+      <c r="B327">
+        <v>7479071</v>
+      </c>
+      <c r="C327" t="s">
+        <v>68</v>
+      </c>
+      <c r="D327" t="s">
+        <v>69</v>
+      </c>
+      <c r="E327" s="2">
+        <v>45678.69791666666</v>
+      </c>
+      <c r="F327">
+        <v>28</v>
+      </c>
+      <c r="G327" t="s">
+        <v>79</v>
+      </c>
+      <c r="H327" t="s">
+        <v>83</v>
+      </c>
+      <c r="I327">
+        <v>1</v>
+      </c>
+      <c r="J327">
+        <v>0</v>
+      </c>
+      <c r="K327">
+        <v>1</v>
+      </c>
+      <c r="L327">
+        <v>2</v>
+      </c>
+      <c r="M327">
+        <v>0</v>
+      </c>
+      <c r="N327">
+        <v>2</v>
+      </c>
+      <c r="O327" t="s">
+        <v>304</v>
+      </c>
+      <c r="P327" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q327">
+        <v>2.6</v>
+      </c>
+      <c r="R327">
+        <v>2.2</v>
+      </c>
+      <c r="S327">
+        <v>4.5</v>
+      </c>
+      <c r="T327">
+        <v>1.4</v>
+      </c>
+      <c r="U327">
+        <v>2.75</v>
+      </c>
+      <c r="V327">
+        <v>3</v>
+      </c>
+      <c r="W327">
+        <v>1.36</v>
+      </c>
+      <c r="X327">
+        <v>8</v>
+      </c>
+      <c r="Y327">
+        <v>1.08</v>
+      </c>
+      <c r="Z327">
+        <v>1.95</v>
+      </c>
+      <c r="AA327">
+        <v>3.5</v>
+      </c>
+      <c r="AB327">
+        <v>3.8</v>
+      </c>
+      <c r="AC327">
+        <v>1.05</v>
+      </c>
+      <c r="AD327">
+        <v>9</v>
+      </c>
+      <c r="AE327">
+        <v>1.33</v>
+      </c>
+      <c r="AF327">
+        <v>3.3</v>
+      </c>
+      <c r="AG327">
+        <v>1.95</v>
+      </c>
+      <c r="AH327">
+        <v>1.8</v>
+      </c>
+      <c r="AI327">
+        <v>1.8</v>
+      </c>
+      <c r="AJ327">
+        <v>1.91</v>
+      </c>
+      <c r="AK327">
+        <v>1.25</v>
+      </c>
+      <c r="AL327">
+        <v>1.25</v>
+      </c>
+      <c r="AM327">
+        <v>1.8</v>
+      </c>
+      <c r="AN327">
+        <v>1.64</v>
+      </c>
+      <c r="AO327">
+        <v>1.36</v>
+      </c>
+      <c r="AP327">
+        <v>1.73</v>
+      </c>
+      <c r="AQ327">
+        <v>1.27</v>
+      </c>
+      <c r="AR327">
+        <v>1.48</v>
+      </c>
+      <c r="AS327">
+        <v>1.15</v>
+      </c>
+      <c r="AT327">
+        <v>2.63</v>
+      </c>
+      <c r="AU327">
+        <v>5</v>
+      </c>
+      <c r="AV327">
+        <v>2</v>
+      </c>
+      <c r="AW327">
+        <v>10</v>
+      </c>
+      <c r="AX327">
+        <v>13</v>
+      </c>
+      <c r="AY327">
+        <v>22</v>
+      </c>
+      <c r="AZ327">
+        <v>18</v>
+      </c>
+      <c r="BA327">
+        <v>5</v>
+      </c>
+      <c r="BB327">
+        <v>5</v>
+      </c>
+      <c r="BC327">
+        <v>10</v>
+      </c>
+      <c r="BD327">
+        <v>1.49</v>
+      </c>
+      <c r="BE327">
+        <v>7</v>
+      </c>
+      <c r="BF327">
+        <v>2.9</v>
+      </c>
+      <c r="BG327">
+        <v>1.17</v>
+      </c>
+      <c r="BH327">
+        <v>4.3</v>
+      </c>
+      <c r="BI327">
+        <v>1.3</v>
+      </c>
+      <c r="BJ327">
+        <v>3.15</v>
+      </c>
+      <c r="BK327">
+        <v>1.5</v>
+      </c>
+      <c r="BL327">
+        <v>2.35</v>
+      </c>
+      <c r="BM327">
+        <v>1.81</v>
+      </c>
+      <c r="BN327">
+        <v>1.88</v>
+      </c>
+      <c r="BO327">
+        <v>2.23</v>
+      </c>
+      <c r="BP327">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="328" spans="1:68">
+      <c r="A328" s="1">
+        <v>327</v>
+      </c>
+      <c r="B328">
+        <v>7479074</v>
+      </c>
+      <c r="C328" t="s">
+        <v>68</v>
+      </c>
+      <c r="D328" t="s">
+        <v>69</v>
+      </c>
+      <c r="E328" s="2">
+        <v>45678.69791666666</v>
+      </c>
+      <c r="F328">
+        <v>28</v>
+      </c>
+      <c r="G328" t="s">
+        <v>88</v>
+      </c>
+      <c r="H328" t="s">
+        <v>86</v>
+      </c>
+      <c r="I328">
+        <v>1</v>
+      </c>
+      <c r="J328">
+        <v>0</v>
+      </c>
+      <c r="K328">
+        <v>1</v>
+      </c>
+      <c r="L328">
+        <v>1</v>
+      </c>
+      <c r="M328">
+        <v>2</v>
+      </c>
+      <c r="N328">
+        <v>3</v>
+      </c>
+      <c r="O328" t="s">
+        <v>296</v>
+      </c>
+      <c r="P328" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q328">
+        <v>3.5</v>
+      </c>
+      <c r="R328">
+        <v>2.1</v>
+      </c>
+      <c r="S328">
+        <v>3.1</v>
+      </c>
+      <c r="T328">
+        <v>1.4</v>
+      </c>
+      <c r="U328">
+        <v>2.75</v>
+      </c>
+      <c r="V328">
+        <v>3</v>
+      </c>
+      <c r="W328">
+        <v>1.36</v>
+      </c>
+      <c r="X328">
+        <v>8</v>
+      </c>
+      <c r="Y328">
+        <v>1.08</v>
+      </c>
+      <c r="Z328">
+        <v>2.62</v>
+      </c>
+      <c r="AA328">
+        <v>3.3</v>
+      </c>
+      <c r="AB328">
+        <v>2.62</v>
+      </c>
+      <c r="AC328">
+        <v>1.06</v>
+      </c>
+      <c r="AD328">
+        <v>10</v>
+      </c>
+      <c r="AE328">
+        <v>1.35</v>
+      </c>
+      <c r="AF328">
+        <v>3.25</v>
+      </c>
+      <c r="AG328">
+        <v>1.95</v>
+      </c>
+      <c r="AH328">
+        <v>1.8</v>
+      </c>
+      <c r="AI328">
+        <v>1.73</v>
+      </c>
+      <c r="AJ328">
+        <v>2</v>
+      </c>
+      <c r="AK328">
+        <v>1.48</v>
+      </c>
+      <c r="AL328">
+        <v>1.28</v>
+      </c>
+      <c r="AM328">
+        <v>1.5</v>
+      </c>
+      <c r="AN328">
+        <v>1.54</v>
+      </c>
+      <c r="AO328">
+        <v>1.79</v>
+      </c>
+      <c r="AP328">
+        <v>1.43</v>
+      </c>
+      <c r="AQ328">
+        <v>1.87</v>
+      </c>
+      <c r="AR328">
+        <v>1.45</v>
+      </c>
+      <c r="AS328">
+        <v>1.25</v>
+      </c>
+      <c r="AT328">
+        <v>2.7</v>
+      </c>
+      <c r="AU328">
+        <v>5</v>
+      </c>
+      <c r="AV328">
+        <v>8</v>
+      </c>
+      <c r="AW328">
+        <v>3</v>
+      </c>
+      <c r="AX328">
+        <v>7</v>
+      </c>
+      <c r="AY328">
+        <v>9</v>
+      </c>
+      <c r="AZ328">
+        <v>18</v>
+      </c>
+      <c r="BA328">
+        <v>1</v>
+      </c>
+      <c r="BB328">
+        <v>2</v>
+      </c>
+      <c r="BC328">
+        <v>3</v>
+      </c>
+      <c r="BD328">
+        <v>1.75</v>
+      </c>
+      <c r="BE328">
+        <v>6.75</v>
+      </c>
+      <c r="BF328">
+        <v>2.25</v>
+      </c>
+      <c r="BG328">
+        <v>1.19</v>
+      </c>
+      <c r="BH328">
+        <v>4.1</v>
+      </c>
+      <c r="BI328">
+        <v>1.33</v>
+      </c>
+      <c r="BJ328">
+        <v>2.95</v>
+      </c>
+      <c r="BK328">
+        <v>1.54</v>
+      </c>
+      <c r="BL328">
+        <v>2.3</v>
+      </c>
+      <c r="BM328">
+        <v>1.85</v>
+      </c>
+      <c r="BN328">
+        <v>1.83</v>
+      </c>
+      <c r="BO328">
+        <v>2.3</v>
+      </c>
+      <c r="BP328">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="329" spans="1:68">
+      <c r="A329" s="1">
+        <v>328</v>
+      </c>
+      <c r="B329">
+        <v>7479069</v>
+      </c>
+      <c r="C329" t="s">
+        <v>68</v>
+      </c>
+      <c r="D329" t="s">
+        <v>69</v>
+      </c>
+      <c r="E329" s="2">
+        <v>45678.69791666666</v>
+      </c>
+      <c r="F329">
+        <v>28</v>
+      </c>
+      <c r="G329" t="s">
+        <v>84</v>
+      </c>
+      <c r="H329" t="s">
+        <v>93</v>
+      </c>
+      <c r="I329">
+        <v>0</v>
+      </c>
+      <c r="J329">
+        <v>1</v>
+      </c>
+      <c r="K329">
+        <v>1</v>
+      </c>
+      <c r="L329">
+        <v>0</v>
+      </c>
+      <c r="M329">
+        <v>1</v>
+      </c>
+      <c r="N329">
+        <v>1</v>
+      </c>
+      <c r="O329" t="s">
+        <v>95</v>
+      </c>
+      <c r="P329" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q329">
+        <v>4</v>
+      </c>
+      <c r="R329">
+        <v>2.1</v>
+      </c>
+      <c r="S329">
+        <v>2.75</v>
+      </c>
+      <c r="T329">
+        <v>1.44</v>
+      </c>
+      <c r="U329">
+        <v>2.63</v>
+      </c>
+      <c r="V329">
+        <v>3.25</v>
+      </c>
+      <c r="W329">
+        <v>1.33</v>
+      </c>
+      <c r="X329">
+        <v>9</v>
+      </c>
+      <c r="Y329">
+        <v>1.07</v>
+      </c>
+      <c r="Z329">
+        <v>3.4</v>
+      </c>
+      <c r="AA329">
+        <v>3.3</v>
+      </c>
+      <c r="AB329">
+        <v>2.15</v>
+      </c>
+      <c r="AC329">
+        <v>1.06</v>
+      </c>
+      <c r="AD329">
+        <v>8.5</v>
+      </c>
+      <c r="AE329">
+        <v>1.36</v>
+      </c>
+      <c r="AF329">
+        <v>3.1</v>
+      </c>
+      <c r="AG329">
+        <v>2.1</v>
+      </c>
+      <c r="AH329">
+        <v>1.65</v>
+      </c>
+      <c r="AI329">
+        <v>1.83</v>
+      </c>
+      <c r="AJ329">
+        <v>1.83</v>
+      </c>
+      <c r="AK329">
+        <v>1.6</v>
+      </c>
+      <c r="AL329">
+        <v>1.28</v>
+      </c>
+      <c r="AM329">
+        <v>1.35</v>
+      </c>
+      <c r="AN329">
+        <v>1.54</v>
+      </c>
+      <c r="AO329">
+        <v>1.43</v>
+      </c>
+      <c r="AP329">
+        <v>1.43</v>
+      </c>
+      <c r="AQ329">
+        <v>1.53</v>
+      </c>
+      <c r="AR329">
+        <v>1.39</v>
+      </c>
+      <c r="AS329">
+        <v>1.35</v>
+      </c>
+      <c r="AT329">
+        <v>2.74</v>
+      </c>
+      <c r="AU329">
+        <v>4</v>
+      </c>
+      <c r="AV329">
+        <v>5</v>
+      </c>
+      <c r="AW329">
+        <v>6</v>
+      </c>
+      <c r="AX329">
+        <v>4</v>
+      </c>
+      <c r="AY329">
+        <v>12</v>
+      </c>
+      <c r="AZ329">
+        <v>10</v>
+      </c>
+      <c r="BA329">
+        <v>8</v>
+      </c>
+      <c r="BB329">
+        <v>4</v>
+      </c>
+      <c r="BC329">
+        <v>12</v>
+      </c>
+      <c r="BD329">
+        <v>2.02</v>
+      </c>
+      <c r="BE329">
+        <v>6.75</v>
+      </c>
+      <c r="BF329">
+        <v>1.95</v>
+      </c>
+      <c r="BG329">
+        <v>1.21</v>
+      </c>
+      <c r="BH329">
+        <v>3.8</v>
+      </c>
+      <c r="BI329">
+        <v>1.38</v>
+      </c>
+      <c r="BJ329">
+        <v>2.7</v>
+      </c>
+      <c r="BK329">
+        <v>1.64</v>
+      </c>
+      <c r="BL329">
+        <v>2.1</v>
+      </c>
+      <c r="BM329">
+        <v>1.98</v>
+      </c>
+      <c r="BN329">
+        <v>1.72</v>
+      </c>
+      <c r="BO329">
+        <v>2.5</v>
+      </c>
+      <c r="BP329">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="330" spans="1:68">
+      <c r="A330" s="1">
+        <v>329</v>
+      </c>
+      <c r="B330">
+        <v>7479068</v>
+      </c>
+      <c r="C330" t="s">
+        <v>68</v>
+      </c>
+      <c r="D330" t="s">
+        <v>69</v>
+      </c>
+      <c r="E330" s="2">
+        <v>45678.69791666666</v>
+      </c>
+      <c r="F330">
+        <v>28</v>
+      </c>
+      <c r="G330" t="s">
+        <v>70</v>
+      </c>
+      <c r="H330" t="s">
+        <v>82</v>
+      </c>
+      <c r="I330">
+        <v>0</v>
+      </c>
+      <c r="J330">
+        <v>1</v>
+      </c>
+      <c r="K330">
+        <v>1</v>
+      </c>
+      <c r="L330">
+        <v>0</v>
+      </c>
+      <c r="M330">
+        <v>2</v>
+      </c>
+      <c r="N330">
+        <v>2</v>
+      </c>
+      <c r="O330" t="s">
+        <v>95</v>
+      </c>
+      <c r="P330" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q330">
+        <v>3.4</v>
+      </c>
+      <c r="R330">
+        <v>2.2</v>
+      </c>
+      <c r="S330">
+        <v>3.1</v>
+      </c>
+      <c r="T330">
+        <v>1.4</v>
+      </c>
+      <c r="U330">
+        <v>2.75</v>
+      </c>
+      <c r="V330">
+        <v>2.75</v>
+      </c>
+      <c r="W330">
+        <v>1.4</v>
+      </c>
+      <c r="X330">
+        <v>8</v>
+      </c>
+      <c r="Y330">
+        <v>1.08</v>
+      </c>
+      <c r="Z330">
+        <v>2.62</v>
+      </c>
+      <c r="AA330">
+        <v>3.3</v>
+      </c>
+      <c r="AB330">
+        <v>2.7</v>
+      </c>
+      <c r="AC330">
+        <v>1.05</v>
+      </c>
+      <c r="AD330">
+        <v>9</v>
+      </c>
+      <c r="AE330">
+        <v>1.3</v>
+      </c>
+      <c r="AF330">
+        <v>3.45</v>
+      </c>
+      <c r="AG330">
+        <v>2.05</v>
+      </c>
+      <c r="AH330">
+        <v>1.7</v>
+      </c>
+      <c r="AI330">
+        <v>1.67</v>
+      </c>
+      <c r="AJ330">
+        <v>2.1</v>
+      </c>
+      <c r="AK330">
+        <v>1.45</v>
+      </c>
+      <c r="AL330">
+        <v>1.25</v>
+      </c>
+      <c r="AM330">
+        <v>1.5</v>
+      </c>
+      <c r="AN330">
+        <v>1.86</v>
+      </c>
+      <c r="AO330">
+        <v>0.79</v>
+      </c>
+      <c r="AP330">
+        <v>1.73</v>
+      </c>
+      <c r="AQ330">
+        <v>0.93</v>
+      </c>
+      <c r="AR330">
+        <v>1.26</v>
+      </c>
+      <c r="AS330">
+        <v>1.09</v>
+      </c>
+      <c r="AT330">
+        <v>2.35</v>
+      </c>
+      <c r="AU330">
+        <v>6</v>
+      </c>
+      <c r="AV330">
+        <v>4</v>
+      </c>
+      <c r="AW330">
+        <v>9</v>
+      </c>
+      <c r="AX330">
+        <v>4</v>
+      </c>
+      <c r="AY330">
+        <v>18</v>
+      </c>
+      <c r="AZ330">
+        <v>10</v>
+      </c>
+      <c r="BA330">
+        <v>4</v>
+      </c>
+      <c r="BB330">
+        <v>4</v>
+      </c>
+      <c r="BC330">
+        <v>8</v>
+      </c>
+      <c r="BD330">
+        <v>2.07</v>
+      </c>
+      <c r="BE330">
+        <v>6.75</v>
+      </c>
+      <c r="BF330">
+        <v>1.91</v>
+      </c>
+      <c r="BG330">
+        <v>1.2</v>
+      </c>
+      <c r="BH330">
+        <v>3.9</v>
+      </c>
+      <c r="BI330">
+        <v>1.37</v>
+      </c>
+      <c r="BJ330">
+        <v>2.8</v>
+      </c>
+      <c r="BK330">
+        <v>1.62</v>
+      </c>
+      <c r="BL330">
+        <v>2.12</v>
+      </c>
+      <c r="BM330">
+        <v>1.97</v>
+      </c>
+      <c r="BN330">
+        <v>1.72</v>
+      </c>
+      <c r="BO330">
+        <v>2.48</v>
+      </c>
+      <c r="BP330">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="331" spans="1:68">
+      <c r="A331" s="1">
+        <v>330</v>
+      </c>
+      <c r="B331">
+        <v>7479070</v>
+      </c>
+      <c r="C331" t="s">
+        <v>68</v>
+      </c>
+      <c r="D331" t="s">
+        <v>69</v>
+      </c>
+      <c r="E331" s="2">
+        <v>45678.69791666666</v>
+      </c>
+      <c r="F331">
+        <v>28</v>
+      </c>
+      <c r="G331" t="s">
+        <v>77</v>
+      </c>
+      <c r="H331" t="s">
+        <v>72</v>
+      </c>
+      <c r="I331">
+        <v>0</v>
+      </c>
+      <c r="J331">
+        <v>0</v>
+      </c>
+      <c r="K331">
+        <v>0</v>
+      </c>
+      <c r="L331">
+        <v>1</v>
+      </c>
+      <c r="M331">
+        <v>2</v>
+      </c>
+      <c r="N331">
+        <v>3</v>
+      </c>
+      <c r="O331" t="s">
+        <v>305</v>
+      </c>
+      <c r="P331" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q331">
+        <v>2.88</v>
+      </c>
+      <c r="R331">
+        <v>2</v>
+      </c>
+      <c r="S331">
+        <v>4</v>
+      </c>
+      <c r="T331">
+        <v>1.5</v>
+      </c>
+      <c r="U331">
+        <v>2.5</v>
+      </c>
+      <c r="V331">
+        <v>3.4</v>
+      </c>
+      <c r="W331">
+        <v>1.3</v>
+      </c>
+      <c r="X331">
+        <v>10</v>
+      </c>
+      <c r="Y331">
+        <v>1.06</v>
+      </c>
+      <c r="Z331">
+        <v>2.2</v>
+      </c>
+      <c r="AA331">
+        <v>3.25</v>
+      </c>
+      <c r="AB331">
+        <v>3.4</v>
+      </c>
+      <c r="AC331">
+        <v>1.08</v>
+      </c>
+      <c r="AD331">
+        <v>7.5</v>
+      </c>
+      <c r="AE331">
+        <v>1.4</v>
+      </c>
+      <c r="AF331">
+        <v>2.88</v>
+      </c>
+      <c r="AG331">
+        <v>2.15</v>
+      </c>
+      <c r="AH331">
+        <v>1.65</v>
+      </c>
+      <c r="AI331">
+        <v>1.91</v>
+      </c>
+      <c r="AJ331">
+        <v>1.8</v>
+      </c>
+      <c r="AK331">
+        <v>1.3</v>
+      </c>
+      <c r="AL331">
+        <v>1.3</v>
+      </c>
+      <c r="AM331">
+        <v>1.62</v>
+      </c>
+      <c r="AN331">
+        <v>0.86</v>
+      </c>
+      <c r="AO331">
+        <v>1.15</v>
+      </c>
+      <c r="AP331">
+        <v>0.8</v>
+      </c>
+      <c r="AQ331">
+        <v>1.29</v>
+      </c>
+      <c r="AR331">
+        <v>1.31</v>
+      </c>
+      <c r="AS331">
+        <v>0.84</v>
+      </c>
+      <c r="AT331">
+        <v>2.15</v>
+      </c>
+      <c r="AU331">
+        <v>4</v>
+      </c>
+      <c r="AV331">
+        <v>4</v>
+      </c>
+      <c r="AW331">
+        <v>8</v>
+      </c>
+      <c r="AX331">
+        <v>4</v>
+      </c>
+      <c r="AY331">
+        <v>15</v>
+      </c>
+      <c r="AZ331">
+        <v>10</v>
+      </c>
+      <c r="BA331">
+        <v>4</v>
+      </c>
+      <c r="BB331">
+        <v>3</v>
+      </c>
+      <c r="BC331">
+        <v>7</v>
+      </c>
+      <c r="BD331">
+        <v>1.46</v>
+      </c>
+      <c r="BE331">
+        <v>7</v>
+      </c>
+      <c r="BF331">
+        <v>3</v>
+      </c>
+      <c r="BG331">
+        <v>1.15</v>
+      </c>
+      <c r="BH331">
+        <v>4.6</v>
+      </c>
+      <c r="BI331">
+        <v>1.27</v>
+      </c>
+      <c r="BJ331">
+        <v>3.3</v>
+      </c>
+      <c r="BK331">
+        <v>1.46</v>
+      </c>
+      <c r="BL331">
+        <v>2.5</v>
+      </c>
+      <c r="BM331">
+        <v>1.72</v>
+      </c>
+      <c r="BN331">
+        <v>1.98</v>
+      </c>
+      <c r="BO331">
+        <v>2.08</v>
+      </c>
+      <c r="BP331">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="332" spans="1:68">
+      <c r="A332" s="1">
+        <v>331</v>
+      </c>
+      <c r="B332">
+        <v>7479072</v>
+      </c>
+      <c r="C332" t="s">
+        <v>68</v>
+      </c>
+      <c r="D332" t="s">
+        <v>69</v>
+      </c>
+      <c r="E332" s="2">
+        <v>45678.70833333334</v>
+      </c>
+      <c r="F332">
+        <v>28</v>
+      </c>
+      <c r="G332" t="s">
+        <v>74</v>
+      </c>
+      <c r="H332" t="s">
+        <v>78</v>
+      </c>
+      <c r="I332">
+        <v>2</v>
+      </c>
+      <c r="J332">
+        <v>1</v>
+      </c>
+      <c r="K332">
+        <v>3</v>
+      </c>
+      <c r="L332">
+        <v>2</v>
+      </c>
+      <c r="M332">
+        <v>2</v>
+      </c>
+      <c r="N332">
+        <v>4</v>
+      </c>
+      <c r="O332" t="s">
+        <v>306</v>
+      </c>
+      <c r="P332" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q332">
+        <v>2.63</v>
+      </c>
+      <c r="R332">
+        <v>2.05</v>
+      </c>
+      <c r="S332">
+        <v>4.75</v>
+      </c>
+      <c r="T332">
+        <v>1.5</v>
+      </c>
+      <c r="U332">
+        <v>2.5</v>
+      </c>
+      <c r="V332">
+        <v>3.4</v>
+      </c>
+      <c r="W332">
+        <v>1.3</v>
+      </c>
+      <c r="X332">
+        <v>10</v>
+      </c>
+      <c r="Y332">
+        <v>1.06</v>
+      </c>
+      <c r="Z332">
+        <v>2.1</v>
+      </c>
+      <c r="AA332">
+        <v>3.1</v>
+      </c>
+      <c r="AB332">
+        <v>3.75</v>
+      </c>
+      <c r="AC332">
+        <v>1.1</v>
+      </c>
+      <c r="AD332">
+        <v>6.5</v>
+      </c>
+      <c r="AE332">
+        <v>1.5</v>
+      </c>
+      <c r="AF332">
+        <v>2.4</v>
+      </c>
+      <c r="AG332">
+        <v>2.37</v>
+      </c>
+      <c r="AH332">
+        <v>1.53</v>
+      </c>
+      <c r="AI332">
+        <v>2</v>
+      </c>
+      <c r="AJ332">
+        <v>1.73</v>
+      </c>
+      <c r="AK332">
+        <v>1.25</v>
+      </c>
+      <c r="AL332">
+        <v>1.3</v>
+      </c>
+      <c r="AM332">
+        <v>1.7</v>
+      </c>
+      <c r="AN332">
+        <v>1.43</v>
+      </c>
+      <c r="AO332">
+        <v>0.77</v>
+      </c>
+      <c r="AP332">
+        <v>1.4</v>
+      </c>
+      <c r="AQ332">
+        <v>0.79</v>
+      </c>
+      <c r="AR332">
+        <v>1.34</v>
+      </c>
+      <c r="AS332">
+        <v>1.1</v>
+      </c>
+      <c r="AT332">
+        <v>2.44</v>
+      </c>
+      <c r="AU332">
+        <v>4</v>
+      </c>
+      <c r="AV332">
+        <v>6</v>
+      </c>
+      <c r="AW332">
+        <v>4</v>
+      </c>
+      <c r="AX332">
+        <v>8</v>
+      </c>
+      <c r="AY332">
+        <v>10</v>
+      </c>
+      <c r="AZ332">
+        <v>17</v>
+      </c>
+      <c r="BA332">
+        <v>4</v>
+      </c>
+      <c r="BB332">
+        <v>2</v>
+      </c>
+      <c r="BC332">
+        <v>6</v>
+      </c>
+      <c r="BD332">
+        <v>1.7</v>
+      </c>
+      <c r="BE332">
+        <v>6.75</v>
+      </c>
+      <c r="BF332">
+        <v>2.4</v>
+      </c>
+      <c r="BG332">
+        <v>1.24</v>
+      </c>
+      <c r="BH332">
+        <v>3.55</v>
+      </c>
+      <c r="BI332">
+        <v>1.43</v>
+      </c>
+      <c r="BJ332">
+        <v>2.6</v>
+      </c>
+      <c r="BK332">
+        <v>1.68</v>
+      </c>
+      <c r="BL332">
+        <v>2.02</v>
+      </c>
+      <c r="BM332">
+        <v>2.08</v>
+      </c>
+      <c r="BN332">
+        <v>1.65</v>
+      </c>
+      <c r="BO332">
+        <v>2.65</v>
+      </c>
+      <c r="BP332">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="420">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -937,6 +937,15 @@
     <t>['2', '19']</t>
   </si>
   <si>
+    <t>['1', '65']</t>
+  </si>
+  <si>
+    <t>['5', '9', '49']</t>
+  </si>
+  <si>
+    <t>['16', '53']</t>
+  </si>
+  <si>
     <t>['67', '88']</t>
   </si>
   <si>
@@ -1253,6 +1262,18 @@
   </si>
   <si>
     <t>['45+1', '90+7']</t>
+  </si>
+  <si>
+    <t>['27']</t>
+  </si>
+  <si>
+    <t>['51', '86']</t>
+  </si>
+  <si>
+    <t>['11', '31', '34', '45', '45+2']</t>
+  </si>
+  <si>
+    <t>['6', '63', '88']</t>
   </si>
 </sst>
 </file>
@@ -1614,7 +1635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP332"/>
+  <dimension ref="A1:BP337"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1870,7 +1891,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -2076,7 +2097,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2282,7 +2303,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2569,7 +2590,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ5">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2694,7 +2715,7 @@
         <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -3106,7 +3127,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q8">
         <v>1.83</v>
@@ -3184,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ8">
         <v>0.5</v>
@@ -3518,7 +3539,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -4008,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ12">
         <v>0.21</v>
@@ -4136,7 +4157,7 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4217,7 +4238,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ13">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4342,7 +4363,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -5038,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ17">
         <v>0.29</v>
@@ -5166,7 +5187,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -5244,7 +5265,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AQ18">
         <v>1.29</v>
@@ -5453,7 +5474,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ19">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5784,7 +5805,7 @@
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5990,7 +6011,7 @@
         <v>111</v>
       </c>
       <c r="P22" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q22">
         <v>2.6</v>
@@ -6480,10 +6501,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ24">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6814,7 +6835,7 @@
         <v>95</v>
       </c>
       <c r="P26" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6892,7 +6913,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ26">
         <v>1.62</v>
@@ -7638,7 +7659,7 @@
         <v>117</v>
       </c>
       <c r="P30" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -8131,7 +8152,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ32">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR32">
         <v>1.46</v>
@@ -8668,7 +8689,7 @@
         <v>122</v>
       </c>
       <c r="P35" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8874,7 +8895,7 @@
         <v>123</v>
       </c>
       <c r="P36" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -9286,7 +9307,7 @@
         <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q38">
         <v>2.4</v>
@@ -9698,7 +9719,7 @@
         <v>95</v>
       </c>
       <c r="P40" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q40">
         <v>4.5</v>
@@ -9904,7 +9925,7 @@
         <v>95</v>
       </c>
       <c r="P41" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9985,7 +10006,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ41">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR41">
         <v>2.58</v>
@@ -10316,7 +10337,7 @@
         <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q43">
         <v>4.33</v>
@@ -10394,7 +10415,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ43">
         <v>1.53</v>
@@ -10600,10 +10621,10 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ44">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR44">
         <v>1.62</v>
@@ -11012,10 +11033,10 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ46">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR46">
         <v>2.31</v>
@@ -11630,7 +11651,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AQ49">
         <v>0.86</v>
@@ -11758,7 +11779,7 @@
         <v>95</v>
       </c>
       <c r="P50" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -12042,10 +12063,10 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ51">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR51">
         <v>1.83</v>
@@ -12457,7 +12478,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ53">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR53">
         <v>1.18</v>
@@ -12994,7 +13015,7 @@
         <v>135</v>
       </c>
       <c r="P56" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q56">
         <v>4.5</v>
@@ -13072,7 +13093,7 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ56">
         <v>1.53</v>
@@ -13278,7 +13299,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ57">
         <v>1.29</v>
@@ -13487,7 +13508,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ58">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR58">
         <v>1.35</v>
@@ -13818,7 +13839,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -14024,7 +14045,7 @@
         <v>95</v>
       </c>
       <c r="P61" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q61">
         <v>4.33</v>
@@ -14102,7 +14123,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ61">
         <v>1.27</v>
@@ -14230,7 +14251,7 @@
         <v>139</v>
       </c>
       <c r="P62" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14311,7 +14332,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ62">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR62">
         <v>0.99</v>
@@ -15054,7 +15075,7 @@
         <v>95</v>
       </c>
       <c r="P66" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q66">
         <v>5.5</v>
@@ -15672,7 +15693,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q69">
         <v>2.05</v>
@@ -16084,7 +16105,7 @@
         <v>147</v>
       </c>
       <c r="P71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -16368,7 +16389,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AQ72">
         <v>0.5</v>
@@ -16702,7 +16723,7 @@
         <v>149</v>
       </c>
       <c r="P74" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q74">
         <v>3.9</v>
@@ -16780,7 +16801,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ74">
         <v>0.29</v>
@@ -17114,7 +17135,7 @@
         <v>151</v>
       </c>
       <c r="P76" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17195,7 +17216,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ76">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR76">
         <v>1.2</v>
@@ -17320,7 +17341,7 @@
         <v>152</v>
       </c>
       <c r="P77" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q77">
         <v>3.75</v>
@@ -17398,7 +17419,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ77">
         <v>1.27</v>
@@ -17607,7 +17628,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ78">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR78">
         <v>1.32</v>
@@ -17732,7 +17753,7 @@
         <v>153</v>
       </c>
       <c r="P79" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -18019,7 +18040,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ80">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR80">
         <v>1.8</v>
@@ -18144,7 +18165,7 @@
         <v>155</v>
       </c>
       <c r="P81" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q81">
         <v>2.63</v>
@@ -18634,7 +18655,7 @@
         <v>2.33</v>
       </c>
       <c r="AP83">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ83">
         <v>1.87</v>
@@ -18840,7 +18861,7 @@
         <v>0.67</v>
       </c>
       <c r="AP84">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ84">
         <v>0.93</v>
@@ -19792,7 +19813,7 @@
         <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q89">
         <v>2.1</v>
@@ -20410,7 +20431,7 @@
         <v>162</v>
       </c>
       <c r="P92" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q92">
         <v>2.85</v>
@@ -20491,7 +20512,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ92">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR92">
         <v>1.63</v>
@@ -20900,7 +20921,7 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -21646,7 +21667,7 @@
         <v>165</v>
       </c>
       <c r="P98" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21930,7 +21951,7 @@
         <v>0.25</v>
       </c>
       <c r="AP99">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ99">
         <v>0.54</v>
@@ -22139,7 +22160,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ100">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR100">
         <v>1.37</v>
@@ -22470,7 +22491,7 @@
         <v>119</v>
       </c>
       <c r="P102" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q102">
         <v>2.5</v>
@@ -22676,7 +22697,7 @@
         <v>168</v>
       </c>
       <c r="P103" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22754,7 +22775,7 @@
         <v>0.75</v>
       </c>
       <c r="AP103">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ103">
         <v>1.23</v>
@@ -22960,7 +22981,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AQ104">
         <v>0.29</v>
@@ -23169,7 +23190,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ105">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR105">
         <v>1.25</v>
@@ -24196,7 +24217,7 @@
         <v>2</v>
       </c>
       <c r="AP110">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ110">
         <v>1.87</v>
@@ -25148,7 +25169,7 @@
         <v>95</v>
       </c>
       <c r="P115" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q115">
         <v>3.4</v>
@@ -25226,10 +25247,10 @@
         <v>1.75</v>
       </c>
       <c r="AP115">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ115">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR115">
         <v>1.6</v>
@@ -25354,7 +25375,7 @@
         <v>178</v>
       </c>
       <c r="P116" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25641,7 +25662,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ117">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR117">
         <v>1.44</v>
@@ -25766,7 +25787,7 @@
         <v>95</v>
       </c>
       <c r="P118" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
@@ -26668,7 +26689,7 @@
         <v>0.6</v>
       </c>
       <c r="AP122">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ122">
         <v>1</v>
@@ -26796,7 +26817,7 @@
         <v>182</v>
       </c>
       <c r="P123" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -26877,7 +26898,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ123">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -27002,7 +27023,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q124">
         <v>3</v>
@@ -27286,7 +27307,7 @@
         <v>0.6</v>
       </c>
       <c r="AP125">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ125">
         <v>0.86</v>
@@ -28113,7 +28134,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ129">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR129">
         <v>1.4</v>
@@ -28444,7 +28465,7 @@
         <v>187</v>
       </c>
       <c r="P131" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -29062,7 +29083,7 @@
         <v>162</v>
       </c>
       <c r="P134" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29140,7 +29161,7 @@
         <v>0.8</v>
       </c>
       <c r="AP134">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ134">
         <v>1.31</v>
@@ -29474,7 +29495,7 @@
         <v>190</v>
       </c>
       <c r="P136" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -30582,10 +30603,10 @@
         <v>0.8</v>
       </c>
       <c r="AP141">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AQ141">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR141">
         <v>1.59</v>
@@ -30710,7 +30731,7 @@
         <v>194</v>
       </c>
       <c r="P142" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q142">
         <v>3.25</v>
@@ -30788,7 +30809,7 @@
         <v>0.4</v>
       </c>
       <c r="AP142">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ142">
         <v>0.86</v>
@@ -30997,7 +31018,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ143">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR143">
         <v>1.28</v>
@@ -31328,7 +31349,7 @@
         <v>196</v>
       </c>
       <c r="P145" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q145">
         <v>3.2</v>
@@ -31534,7 +31555,7 @@
         <v>197</v>
       </c>
       <c r="P146" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31740,7 +31761,7 @@
         <v>198</v>
       </c>
       <c r="P147" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q147">
         <v>3.4</v>
@@ -31946,7 +31967,7 @@
         <v>199</v>
       </c>
       <c r="P148" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q148">
         <v>2.88</v>
@@ -32152,7 +32173,7 @@
         <v>95</v>
       </c>
       <c r="P149" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32358,7 +32379,7 @@
         <v>200</v>
       </c>
       <c r="P150" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q150">
         <v>2.25</v>
@@ -32645,7 +32666,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ151">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR151">
         <v>1.54</v>
@@ -32770,7 +32791,7 @@
         <v>132</v>
       </c>
       <c r="P152" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33182,7 +33203,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33260,7 +33281,7 @@
         <v>0.5</v>
       </c>
       <c r="AP154">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ154">
         <v>0.86</v>
@@ -33466,7 +33487,7 @@
         <v>0.17</v>
       </c>
       <c r="AP155">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ155">
         <v>0.21</v>
@@ -33594,7 +33615,7 @@
         <v>95</v>
       </c>
       <c r="P156" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q156">
         <v>2.25</v>
@@ -33881,7 +33902,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ157">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR157">
         <v>1.46</v>
@@ -34006,7 +34027,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q158">
         <v>4.75</v>
@@ -34290,10 +34311,10 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ159">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR159">
         <v>1.46</v>
@@ -34499,7 +34520,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ160">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR160">
         <v>1.05</v>
@@ -34624,7 +34645,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q161">
         <v>3.75</v>
@@ -35114,7 +35135,7 @@
         <v>0.86</v>
       </c>
       <c r="AP163">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ163">
         <v>0.5</v>
@@ -35448,7 +35469,7 @@
         <v>95</v>
       </c>
       <c r="P165" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -35529,7 +35550,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ165">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR165">
         <v>1.23</v>
@@ -35654,7 +35675,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q166">
         <v>2.5</v>
@@ -36353,7 +36374,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ169">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR169">
         <v>1.4</v>
@@ -36890,7 +36911,7 @@
         <v>197</v>
       </c>
       <c r="P172" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37096,7 +37117,7 @@
         <v>172</v>
       </c>
       <c r="P173" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37380,7 +37401,7 @@
         <v>1</v>
       </c>
       <c r="AP174">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ174">
         <v>1.29</v>
@@ -37508,7 +37529,7 @@
         <v>214</v>
       </c>
       <c r="P175" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q175">
         <v>2.63</v>
@@ -37792,7 +37813,7 @@
         <v>0.5</v>
       </c>
       <c r="AP176">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ176">
         <v>0.86</v>
@@ -37920,7 +37941,7 @@
         <v>216</v>
       </c>
       <c r="P177" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38410,7 +38431,7 @@
         <v>1.17</v>
       </c>
       <c r="AP179">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AQ179">
         <v>1.31</v>
@@ -38538,7 +38559,7 @@
         <v>142</v>
       </c>
       <c r="P180" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q180">
         <v>3.75</v>
@@ -38950,7 +38971,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q182">
         <v>3.4</v>
@@ -39028,7 +39049,7 @@
         <v>0.75</v>
       </c>
       <c r="AP182">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ182">
         <v>0.86</v>
@@ -39237,7 +39258,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ183">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR183">
         <v>1.3</v>
@@ -39362,7 +39383,7 @@
         <v>220</v>
       </c>
       <c r="P184" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q184">
         <v>3.2</v>
@@ -39646,7 +39667,7 @@
         <v>0.43</v>
       </c>
       <c r="AP185">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ185">
         <v>0.79</v>
@@ -39855,7 +39876,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ186">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR186">
         <v>1.39</v>
@@ -40186,7 +40207,7 @@
         <v>223</v>
       </c>
       <c r="P188" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q188">
         <v>5.5</v>
@@ -40679,7 +40700,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ190">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR190">
         <v>1.68</v>
@@ -40804,7 +40825,7 @@
         <v>225</v>
       </c>
       <c r="P191" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -40885,7 +40906,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ191">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR191">
         <v>1.32</v>
@@ -41010,7 +41031,7 @@
         <v>226</v>
       </c>
       <c r="P192" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q192">
         <v>5</v>
@@ -41706,7 +41727,7 @@
         <v>0.29</v>
       </c>
       <c r="AP195">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AQ195">
         <v>0.54</v>
@@ -41834,7 +41855,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q196">
         <v>3</v>
@@ -42736,7 +42757,7 @@
         <v>0.57</v>
       </c>
       <c r="AP200">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ200">
         <v>0.29</v>
@@ -42864,7 +42885,7 @@
         <v>95</v>
       </c>
       <c r="P201" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q201">
         <v>2.6</v>
@@ -43560,7 +43581,7 @@
         <v>1.67</v>
       </c>
       <c r="AP204">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AQ204">
         <v>1.53</v>
@@ -44100,7 +44121,7 @@
         <v>233</v>
       </c>
       <c r="P207" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q207">
         <v>2.05</v>
@@ -44181,7 +44202,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ207">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR207">
         <v>1.61</v>
@@ -44718,7 +44739,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44924,7 +44945,7 @@
         <v>235</v>
       </c>
       <c r="P211" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q211">
         <v>2.38</v>
@@ -45336,7 +45357,7 @@
         <v>237</v>
       </c>
       <c r="P213" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q213">
         <v>2.4</v>
@@ -45542,7 +45563,7 @@
         <v>95</v>
       </c>
       <c r="P214" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45623,7 +45644,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ214">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR214">
         <v>1.26</v>
@@ -45748,7 +45769,7 @@
         <v>178</v>
       </c>
       <c r="P215" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q215">
         <v>3.2</v>
@@ -46238,7 +46259,7 @@
         <v>0.67</v>
       </c>
       <c r="AP217">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ217">
         <v>0.5</v>
@@ -46444,7 +46465,7 @@
         <v>0.5</v>
       </c>
       <c r="AP218">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ218">
         <v>0.86</v>
@@ -46653,7 +46674,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ219">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR219">
         <v>1.4</v>
@@ -47268,7 +47289,7 @@
         <v>1.33</v>
       </c>
       <c r="AP222">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ222">
         <v>1</v>
@@ -47477,7 +47498,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ223">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR223">
         <v>1.71</v>
@@ -47602,7 +47623,7 @@
         <v>244</v>
       </c>
       <c r="P224" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q224">
         <v>2.88</v>
@@ -47808,7 +47829,7 @@
         <v>245</v>
       </c>
       <c r="P225" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q225">
         <v>3.2</v>
@@ -48220,7 +48241,7 @@
         <v>95</v>
       </c>
       <c r="P227" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q227">
         <v>3</v>
@@ -48298,7 +48319,7 @@
         <v>1.33</v>
       </c>
       <c r="AP227">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ227">
         <v>1.23</v>
@@ -48504,10 +48525,10 @@
         <v>0.9</v>
       </c>
       <c r="AP228">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ228">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR228">
         <v>1.37</v>
@@ -48632,7 +48653,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48710,7 +48731,7 @@
         <v>1.1</v>
       </c>
       <c r="AP229">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ229">
         <v>1</v>
@@ -48919,7 +48940,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ230">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR230">
         <v>1.35</v>
@@ -49328,7 +49349,7 @@
         <v>1.56</v>
       </c>
       <c r="AP232">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ232">
         <v>1.38</v>
@@ -49456,7 +49477,7 @@
         <v>95</v>
       </c>
       <c r="P233" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49662,7 +49683,7 @@
         <v>95</v>
       </c>
       <c r="P234" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -50898,7 +50919,7 @@
         <v>252</v>
       </c>
       <c r="P240" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q240">
         <v>2.5</v>
@@ -50979,7 +51000,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ240">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR240">
         <v>1.9</v>
@@ -51516,7 +51537,7 @@
         <v>253</v>
       </c>
       <c r="P243" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q243">
         <v>3.1</v>
@@ -51722,7 +51743,7 @@
         <v>254</v>
       </c>
       <c r="P244" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -52006,7 +52027,7 @@
         <v>0.2</v>
       </c>
       <c r="AP245">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AQ245">
         <v>0.21</v>
@@ -52134,7 +52155,7 @@
         <v>244</v>
       </c>
       <c r="P246" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52752,7 +52773,7 @@
         <v>131</v>
       </c>
       <c r="P249" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -52833,7 +52854,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ249">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR249">
         <v>1.47</v>
@@ -53242,10 +53263,10 @@
         <v>0.8</v>
       </c>
       <c r="AP251">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ251">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR251">
         <v>1.45</v>
@@ -53370,7 +53391,7 @@
         <v>260</v>
       </c>
       <c r="P252" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q252">
         <v>3.2</v>
@@ -53654,7 +53675,7 @@
         <v>0.91</v>
       </c>
       <c r="AP253">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ253">
         <v>0.93</v>
@@ -53782,7 +53803,7 @@
         <v>262</v>
       </c>
       <c r="P254" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -53863,7 +53884,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ254">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR254">
         <v>1.59</v>
@@ -54478,7 +54499,7 @@
         <v>0.22</v>
       </c>
       <c r="AP257">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ257">
         <v>0.54</v>
@@ -54812,7 +54833,7 @@
         <v>266</v>
       </c>
       <c r="P259" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q259">
         <v>5.5</v>
@@ -54890,7 +54911,7 @@
         <v>1.4</v>
       </c>
       <c r="AP259">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ259">
         <v>1.38</v>
@@ -55018,7 +55039,7 @@
         <v>267</v>
       </c>
       <c r="P260" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
@@ -55430,7 +55451,7 @@
         <v>269</v>
       </c>
       <c r="P262" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q262">
         <v>3.5</v>
@@ -55717,7 +55738,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ263">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR263">
         <v>1.21</v>
@@ -56048,7 +56069,7 @@
         <v>95</v>
       </c>
       <c r="P265" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56126,10 +56147,10 @@
         <v>1.91</v>
       </c>
       <c r="AP265">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AQ265">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR265">
         <v>1.46</v>
@@ -56254,7 +56275,7 @@
         <v>271</v>
       </c>
       <c r="P266" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Q266">
         <v>2.25</v>
@@ -56872,7 +56893,7 @@
         <v>274</v>
       </c>
       <c r="P269" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57490,7 +57511,7 @@
         <v>277</v>
       </c>
       <c r="P272" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q272">
         <v>3.5</v>
@@ -57696,7 +57717,7 @@
         <v>95</v>
       </c>
       <c r="P273" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q273">
         <v>6</v>
@@ -57980,7 +58001,7 @@
         <v>1.42</v>
       </c>
       <c r="AP274">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AQ274">
         <v>1.27</v>
@@ -58108,7 +58129,7 @@
         <v>278</v>
       </c>
       <c r="P275" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Q275">
         <v>3.2</v>
@@ -58314,7 +58335,7 @@
         <v>279</v>
       </c>
       <c r="P276" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q276">
         <v>2.5</v>
@@ -58520,7 +58541,7 @@
         <v>280</v>
       </c>
       <c r="P277" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58726,7 +58747,7 @@
         <v>281</v>
       </c>
       <c r="P278" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q278">
         <v>2.6</v>
@@ -59425,7 +59446,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ281">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR281">
         <v>1.28</v>
@@ -60249,7 +60270,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ285">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR285">
         <v>1.55</v>
@@ -60580,7 +60601,7 @@
         <v>285</v>
       </c>
       <c r="P287" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="Q287">
         <v>3.75</v>
@@ -60658,7 +60679,7 @@
         <v>1.08</v>
       </c>
       <c r="AP287">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ287">
         <v>1</v>
@@ -60992,7 +61013,7 @@
         <v>286</v>
       </c>
       <c r="P289" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q289">
         <v>2.38</v>
@@ -61198,7 +61219,7 @@
         <v>287</v>
       </c>
       <c r="P290" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61276,7 +61297,7 @@
         <v>0.58</v>
       </c>
       <c r="AP290">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ290">
         <v>0.5</v>
@@ -61482,7 +61503,7 @@
         <v>1.17</v>
       </c>
       <c r="AP291">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ291">
         <v>1</v>
@@ -61691,7 +61712,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ292">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR292">
         <v>1.41</v>
@@ -61894,7 +61915,7 @@
         <v>1.36</v>
       </c>
       <c r="AP293">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ293">
         <v>1.23</v>
@@ -62022,7 +62043,7 @@
         <v>289</v>
       </c>
       <c r="P294" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q294">
         <v>3.4</v>
@@ -62309,7 +62330,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ295">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR295">
         <v>1.45</v>
@@ -62640,7 +62661,7 @@
         <v>290</v>
       </c>
       <c r="P297" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -63339,7 +63360,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ300">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR300">
         <v>1.28</v>
@@ -63464,7 +63485,7 @@
         <v>291</v>
       </c>
       <c r="P301" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="Q301">
         <v>3</v>
@@ -63542,7 +63563,7 @@
         <v>0.82</v>
       </c>
       <c r="AP301">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ301">
         <v>0.83</v>
@@ -63670,7 +63691,7 @@
         <v>204</v>
       </c>
       <c r="P302" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -64082,7 +64103,7 @@
         <v>293</v>
       </c>
       <c r="P304" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="Q304">
         <v>3.75</v>
@@ -64288,7 +64309,7 @@
         <v>294</v>
       </c>
       <c r="P305" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="Q305">
         <v>6.5</v>
@@ -64700,7 +64721,7 @@
         <v>200</v>
       </c>
       <c r="P307" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q307">
         <v>2.2</v>
@@ -65318,7 +65339,7 @@
         <v>231</v>
       </c>
       <c r="P310" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
@@ -65602,7 +65623,7 @@
         <v>0.5</v>
       </c>
       <c r="AP311">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ311">
         <v>0.54</v>
@@ -66426,7 +66447,7 @@
         <v>1</v>
       </c>
       <c r="AP315">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ315">
         <v>1.29</v>
@@ -66635,7 +66656,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ316">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR316">
         <v>1.34</v>
@@ -66841,7 +66862,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ317">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR317">
         <v>1.35</v>
@@ -67250,10 +67271,10 @@
         <v>1</v>
       </c>
       <c r="AP319">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AQ319">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR319">
         <v>1.41</v>
@@ -67378,7 +67399,7 @@
         <v>95</v>
       </c>
       <c r="P320" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="Q320">
         <v>3.1</v>
@@ -68074,7 +68095,7 @@
         <v>1.5</v>
       </c>
       <c r="AP323">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ323">
         <v>1.38</v>
@@ -68280,7 +68301,7 @@
         <v>1.42</v>
       </c>
       <c r="AP324">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ324">
         <v>1.31</v>
@@ -68408,7 +68429,7 @@
         <v>302</v>
       </c>
       <c r="P325" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="Q325">
         <v>2.5</v>
@@ -68614,7 +68635,7 @@
         <v>303</v>
       </c>
       <c r="P326" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="Q326">
         <v>3</v>
@@ -69026,7 +69047,7 @@
         <v>296</v>
       </c>
       <c r="P328" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="Q328">
         <v>3.5</v>
@@ -69438,7 +69459,7 @@
         <v>95</v>
       </c>
       <c r="P330" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="Q330">
         <v>3.4</v>
@@ -69644,7 +69665,7 @@
         <v>305</v>
       </c>
       <c r="P331" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="Q331">
         <v>2.88</v>
@@ -69850,7 +69871,7 @@
         <v>306</v>
       </c>
       <c r="P332" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="Q332">
         <v>2.63</v>
@@ -70007,6 +70028,1036 @@
       </c>
       <c r="BP332">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="333" spans="1:68">
+      <c r="A333" s="1">
+        <v>332</v>
+      </c>
+      <c r="B333">
+        <v>7479076</v>
+      </c>
+      <c r="C333" t="s">
+        <v>68</v>
+      </c>
+      <c r="D333" t="s">
+        <v>69</v>
+      </c>
+      <c r="E333" s="2">
+        <v>45679.69791666666</v>
+      </c>
+      <c r="F333">
+        <v>28</v>
+      </c>
+      <c r="G333" t="s">
+        <v>76</v>
+      </c>
+      <c r="H333" t="s">
+        <v>90</v>
+      </c>
+      <c r="I333">
+        <v>1</v>
+      </c>
+      <c r="J333">
+        <v>0</v>
+      </c>
+      <c r="K333">
+        <v>1</v>
+      </c>
+      <c r="L333">
+        <v>2</v>
+      </c>
+      <c r="M333">
+        <v>0</v>
+      </c>
+      <c r="N333">
+        <v>2</v>
+      </c>
+      <c r="O333" t="s">
+        <v>307</v>
+      </c>
+      <c r="P333" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q333">
+        <v>1.95</v>
+      </c>
+      <c r="R333">
+        <v>2.4</v>
+      </c>
+      <c r="S333">
+        <v>6.5</v>
+      </c>
+      <c r="T333">
+        <v>1.33</v>
+      </c>
+      <c r="U333">
+        <v>3.25</v>
+      </c>
+      <c r="V333">
+        <v>2.5</v>
+      </c>
+      <c r="W333">
+        <v>1.5</v>
+      </c>
+      <c r="X333">
+        <v>6.5</v>
+      </c>
+      <c r="Y333">
+        <v>1.11</v>
+      </c>
+      <c r="Z333">
+        <v>1.47</v>
+      </c>
+      <c r="AA333">
+        <v>4.7</v>
+      </c>
+      <c r="AB333">
+        <v>6.8</v>
+      </c>
+      <c r="AC333">
+        <v>1.04</v>
+      </c>
+      <c r="AD333">
+        <v>10</v>
+      </c>
+      <c r="AE333">
+        <v>1.22</v>
+      </c>
+      <c r="AF333">
+        <v>4.2</v>
+      </c>
+      <c r="AG333">
+        <v>1.65</v>
+      </c>
+      <c r="AH333">
+        <v>2.1</v>
+      </c>
+      <c r="AI333">
+        <v>1.83</v>
+      </c>
+      <c r="AJ333">
+        <v>1.83</v>
+      </c>
+      <c r="AK333">
+        <v>1.1</v>
+      </c>
+      <c r="AL333">
+        <v>1.15</v>
+      </c>
+      <c r="AM333">
+        <v>2.65</v>
+      </c>
+      <c r="AN333">
+        <v>2.5</v>
+      </c>
+      <c r="AO333">
+        <v>0.93</v>
+      </c>
+      <c r="AP333">
+        <v>2.53</v>
+      </c>
+      <c r="AQ333">
+        <v>0.87</v>
+      </c>
+      <c r="AR333">
+        <v>1.89</v>
+      </c>
+      <c r="AS333">
+        <v>1.02</v>
+      </c>
+      <c r="AT333">
+        <v>2.91</v>
+      </c>
+      <c r="AU333">
+        <v>8</v>
+      </c>
+      <c r="AV333">
+        <v>0</v>
+      </c>
+      <c r="AW333">
+        <v>7</v>
+      </c>
+      <c r="AX333">
+        <v>3</v>
+      </c>
+      <c r="AY333">
+        <v>17</v>
+      </c>
+      <c r="AZ333">
+        <v>5</v>
+      </c>
+      <c r="BA333">
+        <v>8</v>
+      </c>
+      <c r="BB333">
+        <v>4</v>
+      </c>
+      <c r="BC333">
+        <v>12</v>
+      </c>
+      <c r="BD333">
+        <v>1.24</v>
+      </c>
+      <c r="BE333">
+        <v>8.5</v>
+      </c>
+      <c r="BF333">
+        <v>4.4</v>
+      </c>
+      <c r="BG333">
+        <v>1.21</v>
+      </c>
+      <c r="BH333">
+        <v>3.8</v>
+      </c>
+      <c r="BI333">
+        <v>1.38</v>
+      </c>
+      <c r="BJ333">
+        <v>2.7</v>
+      </c>
+      <c r="BK333">
+        <v>1.63</v>
+      </c>
+      <c r="BL333">
+        <v>2.1</v>
+      </c>
+      <c r="BM333">
+        <v>1.98</v>
+      </c>
+      <c r="BN333">
+        <v>1.72</v>
+      </c>
+      <c r="BO333">
+        <v>2.48</v>
+      </c>
+      <c r="BP333">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="334" spans="1:68">
+      <c r="A334" s="1">
+        <v>333</v>
+      </c>
+      <c r="B334">
+        <v>7479078</v>
+      </c>
+      <c r="C334" t="s">
+        <v>68</v>
+      </c>
+      <c r="D334" t="s">
+        <v>69</v>
+      </c>
+      <c r="E334" s="2">
+        <v>45679.69791666666</v>
+      </c>
+      <c r="F334">
+        <v>28</v>
+      </c>
+      <c r="G334" t="s">
+        <v>85</v>
+      </c>
+      <c r="H334" t="s">
+        <v>75</v>
+      </c>
+      <c r="I334">
+        <v>2</v>
+      </c>
+      <c r="J334">
+        <v>1</v>
+      </c>
+      <c r="K334">
+        <v>3</v>
+      </c>
+      <c r="L334">
+        <v>3</v>
+      </c>
+      <c r="M334">
+        <v>1</v>
+      </c>
+      <c r="N334">
+        <v>4</v>
+      </c>
+      <c r="O334" t="s">
+        <v>308</v>
+      </c>
+      <c r="P334" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q334">
+        <v>3.1</v>
+      </c>
+      <c r="R334">
+        <v>2.2</v>
+      </c>
+      <c r="S334">
+        <v>3.4</v>
+      </c>
+      <c r="T334">
+        <v>1.4</v>
+      </c>
+      <c r="U334">
+        <v>2.75</v>
+      </c>
+      <c r="V334">
+        <v>2.75</v>
+      </c>
+      <c r="W334">
+        <v>1.4</v>
+      </c>
+      <c r="X334">
+        <v>8</v>
+      </c>
+      <c r="Y334">
+        <v>1.08</v>
+      </c>
+      <c r="Z334">
+        <v>2.4</v>
+      </c>
+      <c r="AA334">
+        <v>3.6</v>
+      </c>
+      <c r="AB334">
+        <v>2.9</v>
+      </c>
+      <c r="AC334">
+        <v>1.06</v>
+      </c>
+      <c r="AD334">
+        <v>11</v>
+      </c>
+      <c r="AE334">
+        <v>1.3</v>
+      </c>
+      <c r="AF334">
+        <v>3.6</v>
+      </c>
+      <c r="AG334">
+        <v>1.89</v>
+      </c>
+      <c r="AH334">
+        <v>1.96</v>
+      </c>
+      <c r="AI334">
+        <v>1.67</v>
+      </c>
+      <c r="AJ334">
+        <v>2.1</v>
+      </c>
+      <c r="AK334">
+        <v>1.4</v>
+      </c>
+      <c r="AL334">
+        <v>1.3</v>
+      </c>
+      <c r="AM334">
+        <v>1.6</v>
+      </c>
+      <c r="AN334">
+        <v>1.58</v>
+      </c>
+      <c r="AO334">
+        <v>0.77</v>
+      </c>
+      <c r="AP334">
+        <v>1.69</v>
+      </c>
+      <c r="AQ334">
+        <v>0.71</v>
+      </c>
+      <c r="AR334">
+        <v>1.42</v>
+      </c>
+      <c r="AS334">
+        <v>1.13</v>
+      </c>
+      <c r="AT334">
+        <v>2.55</v>
+      </c>
+      <c r="AU334">
+        <v>8</v>
+      </c>
+      <c r="AV334">
+        <v>3</v>
+      </c>
+      <c r="AW334">
+        <v>10</v>
+      </c>
+      <c r="AX334">
+        <v>6</v>
+      </c>
+      <c r="AY334">
+        <v>20</v>
+      </c>
+      <c r="AZ334">
+        <v>9</v>
+      </c>
+      <c r="BA334">
+        <v>7</v>
+      </c>
+      <c r="BB334">
+        <v>1</v>
+      </c>
+      <c r="BC334">
+        <v>8</v>
+      </c>
+      <c r="BD334">
+        <v>1.59</v>
+      </c>
+      <c r="BE334">
+        <v>7.3</v>
+      </c>
+      <c r="BF334">
+        <v>3.06</v>
+      </c>
+      <c r="BG334">
+        <v>1.1</v>
+      </c>
+      <c r="BH334">
+        <v>5.05</v>
+      </c>
+      <c r="BI334">
+        <v>1.24</v>
+      </c>
+      <c r="BJ334">
+        <v>3.34</v>
+      </c>
+      <c r="BK334">
+        <v>1.45</v>
+      </c>
+      <c r="BL334">
+        <v>2.48</v>
+      </c>
+      <c r="BM334">
+        <v>1.8</v>
+      </c>
+      <c r="BN334">
+        <v>1.91</v>
+      </c>
+      <c r="BO334">
+        <v>2.23</v>
+      </c>
+      <c r="BP334">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="335" spans="1:68">
+      <c r="A335" s="1">
+        <v>334</v>
+      </c>
+      <c r="B335">
+        <v>7479079</v>
+      </c>
+      <c r="C335" t="s">
+        <v>68</v>
+      </c>
+      <c r="D335" t="s">
+        <v>69</v>
+      </c>
+      <c r="E335" s="2">
+        <v>45679.69791666666</v>
+      </c>
+      <c r="F335">
+        <v>28</v>
+      </c>
+      <c r="G335" t="s">
+        <v>80</v>
+      </c>
+      <c r="H335" t="s">
+        <v>89</v>
+      </c>
+      <c r="I335">
+        <v>1</v>
+      </c>
+      <c r="J335">
+        <v>0</v>
+      </c>
+      <c r="K335">
+        <v>1</v>
+      </c>
+      <c r="L335">
+        <v>2</v>
+      </c>
+      <c r="M335">
+        <v>2</v>
+      </c>
+      <c r="N335">
+        <v>4</v>
+      </c>
+      <c r="O335" t="s">
+        <v>309</v>
+      </c>
+      <c r="P335" t="s">
+        <v>417</v>
+      </c>
+      <c r="Q335">
+        <v>3</v>
+      </c>
+      <c r="R335">
+        <v>2.1</v>
+      </c>
+      <c r="S335">
+        <v>3.6</v>
+      </c>
+      <c r="T335">
+        <v>1.44</v>
+      </c>
+      <c r="U335">
+        <v>2.63</v>
+      </c>
+      <c r="V335">
+        <v>3.25</v>
+      </c>
+      <c r="W335">
+        <v>1.33</v>
+      </c>
+      <c r="X335">
+        <v>9</v>
+      </c>
+      <c r="Y335">
+        <v>1.07</v>
+      </c>
+      <c r="Z335">
+        <v>2.34</v>
+      </c>
+      <c r="AA335">
+        <v>3.45</v>
+      </c>
+      <c r="AB335">
+        <v>3.1</v>
+      </c>
+      <c r="AC335">
+        <v>1.07</v>
+      </c>
+      <c r="AD335">
+        <v>8</v>
+      </c>
+      <c r="AE335">
+        <v>1.36</v>
+      </c>
+      <c r="AF335">
+        <v>3.1</v>
+      </c>
+      <c r="AG335">
+        <v>2</v>
+      </c>
+      <c r="AH335">
+        <v>1.75</v>
+      </c>
+      <c r="AI335">
+        <v>1.8</v>
+      </c>
+      <c r="AJ335">
+        <v>1.91</v>
+      </c>
+      <c r="AK335">
+        <v>1.4</v>
+      </c>
+      <c r="AL335">
+        <v>1.32</v>
+      </c>
+      <c r="AM335">
+        <v>1.53</v>
+      </c>
+      <c r="AN335">
+        <v>1.43</v>
+      </c>
+      <c r="AO335">
+        <v>1</v>
+      </c>
+      <c r="AP335">
+        <v>1.4</v>
+      </c>
+      <c r="AQ335">
+        <v>1</v>
+      </c>
+      <c r="AR335">
+        <v>1.4</v>
+      </c>
+      <c r="AS335">
+        <v>1.25</v>
+      </c>
+      <c r="AT335">
+        <v>2.65</v>
+      </c>
+      <c r="AU335">
+        <v>6</v>
+      </c>
+      <c r="AV335">
+        <v>4</v>
+      </c>
+      <c r="AW335">
+        <v>7</v>
+      </c>
+      <c r="AX335">
+        <v>10</v>
+      </c>
+      <c r="AY335">
+        <v>16</v>
+      </c>
+      <c r="AZ335">
+        <v>16</v>
+      </c>
+      <c r="BA335">
+        <v>7</v>
+      </c>
+      <c r="BB335">
+        <v>4</v>
+      </c>
+      <c r="BC335">
+        <v>11</v>
+      </c>
+      <c r="BD335">
+        <v>1.76</v>
+      </c>
+      <c r="BE335">
+        <v>6.75</v>
+      </c>
+      <c r="BF335">
+        <v>2.65</v>
+      </c>
+      <c r="BG335">
+        <v>1.14</v>
+      </c>
+      <c r="BH335">
+        <v>4.4</v>
+      </c>
+      <c r="BI335">
+        <v>1.3</v>
+      </c>
+      <c r="BJ335">
+        <v>2.97</v>
+      </c>
+      <c r="BK335">
+        <v>1.56</v>
+      </c>
+      <c r="BL335">
+        <v>2.21</v>
+      </c>
+      <c r="BM335">
+        <v>1.9</v>
+      </c>
+      <c r="BN335">
+        <v>1.8</v>
+      </c>
+      <c r="BO335">
+        <v>2.51</v>
+      </c>
+      <c r="BP335">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="336" spans="1:68">
+      <c r="A336" s="1">
+        <v>335</v>
+      </c>
+      <c r="B336">
+        <v>7479077</v>
+      </c>
+      <c r="C336" t="s">
+        <v>68</v>
+      </c>
+      <c r="D336" t="s">
+        <v>69</v>
+      </c>
+      <c r="E336" s="2">
+        <v>45679.70833333334</v>
+      </c>
+      <c r="F336">
+        <v>28</v>
+      </c>
+      <c r="G336" t="s">
+        <v>92</v>
+      </c>
+      <c r="H336" t="s">
+        <v>91</v>
+      </c>
+      <c r="I336">
+        <v>0</v>
+      </c>
+      <c r="J336">
+        <v>5</v>
+      </c>
+      <c r="K336">
+        <v>5</v>
+      </c>
+      <c r="L336">
+        <v>0</v>
+      </c>
+      <c r="M336">
+        <v>5</v>
+      </c>
+      <c r="N336">
+        <v>5</v>
+      </c>
+      <c r="O336" t="s">
+        <v>95</v>
+      </c>
+      <c r="P336" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q336">
+        <v>5.5</v>
+      </c>
+      <c r="R336">
+        <v>2.1</v>
+      </c>
+      <c r="S336">
+        <v>2.3</v>
+      </c>
+      <c r="T336">
+        <v>1.44</v>
+      </c>
+      <c r="U336">
+        <v>2.63</v>
+      </c>
+      <c r="V336">
+        <v>3.25</v>
+      </c>
+      <c r="W336">
+        <v>1.33</v>
+      </c>
+      <c r="X336">
+        <v>9</v>
+      </c>
+      <c r="Y336">
+        <v>1.07</v>
+      </c>
+      <c r="Z336">
+        <v>6.2</v>
+      </c>
+      <c r="AA336">
+        <v>4.3</v>
+      </c>
+      <c r="AB336">
+        <v>1.54</v>
+      </c>
+      <c r="AC336">
+        <v>1.06</v>
+      </c>
+      <c r="AD336">
+        <v>10</v>
+      </c>
+      <c r="AE336">
+        <v>1.36</v>
+      </c>
+      <c r="AF336">
+        <v>3.2</v>
+      </c>
+      <c r="AG336">
+        <v>1.89</v>
+      </c>
+      <c r="AH336">
+        <v>1.96</v>
+      </c>
+      <c r="AI336">
+        <v>2</v>
+      </c>
+      <c r="AJ336">
+        <v>1.73</v>
+      </c>
+      <c r="AK336">
+        <v>2.15</v>
+      </c>
+      <c r="AL336">
+        <v>1.27</v>
+      </c>
+      <c r="AM336">
+        <v>1.16</v>
+      </c>
+      <c r="AN336">
+        <v>1.38</v>
+      </c>
+      <c r="AO336">
+        <v>2</v>
+      </c>
+      <c r="AP336">
+        <v>1.29</v>
+      </c>
+      <c r="AQ336">
+        <v>2.07</v>
+      </c>
+      <c r="AR336">
+        <v>1.39</v>
+      </c>
+      <c r="AS336">
+        <v>1.18</v>
+      </c>
+      <c r="AT336">
+        <v>2.57</v>
+      </c>
+      <c r="AU336">
+        <v>2</v>
+      </c>
+      <c r="AV336">
+        <v>10</v>
+      </c>
+      <c r="AW336">
+        <v>3</v>
+      </c>
+      <c r="AX336">
+        <v>8</v>
+      </c>
+      <c r="AY336">
+        <v>6</v>
+      </c>
+      <c r="AZ336">
+        <v>21</v>
+      </c>
+      <c r="BA336">
+        <v>1</v>
+      </c>
+      <c r="BB336">
+        <v>5</v>
+      </c>
+      <c r="BC336">
+        <v>6</v>
+      </c>
+      <c r="BD336">
+        <v>4.75</v>
+      </c>
+      <c r="BE336">
+        <v>8.4</v>
+      </c>
+      <c r="BF336">
+        <v>1.31</v>
+      </c>
+      <c r="BG336">
+        <v>1.12</v>
+      </c>
+      <c r="BH336">
+        <v>4.65</v>
+      </c>
+      <c r="BI336">
+        <v>1.27</v>
+      </c>
+      <c r="BJ336">
+        <v>3.14</v>
+      </c>
+      <c r="BK336">
+        <v>1.51</v>
+      </c>
+      <c r="BL336">
+        <v>2.32</v>
+      </c>
+      <c r="BM336">
+        <v>1.85</v>
+      </c>
+      <c r="BN336">
+        <v>1.85</v>
+      </c>
+      <c r="BO336">
+        <v>2.38</v>
+      </c>
+      <c r="BP336">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="337" spans="1:68">
+      <c r="A337" s="1">
+        <v>336</v>
+      </c>
+      <c r="B337">
+        <v>7479088</v>
+      </c>
+      <c r="C337" t="s">
+        <v>68</v>
+      </c>
+      <c r="D337" t="s">
+        <v>69</v>
+      </c>
+      <c r="E337" s="2">
+        <v>45681.70833333334</v>
+      </c>
+      <c r="F337">
+        <v>29</v>
+      </c>
+      <c r="G337" t="s">
+        <v>86</v>
+      </c>
+      <c r="H337" t="s">
+        <v>77</v>
+      </c>
+      <c r="I337">
+        <v>0</v>
+      </c>
+      <c r="J337">
+        <v>1</v>
+      </c>
+      <c r="K337">
+        <v>1</v>
+      </c>
+      <c r="L337">
+        <v>0</v>
+      </c>
+      <c r="M337">
+        <v>3</v>
+      </c>
+      <c r="N337">
+        <v>3</v>
+      </c>
+      <c r="O337" t="s">
+        <v>95</v>
+      </c>
+      <c r="P337" t="s">
+        <v>419</v>
+      </c>
+      <c r="Q337">
+        <v>2.2</v>
+      </c>
+      <c r="R337">
+        <v>2.2</v>
+      </c>
+      <c r="S337">
+        <v>6</v>
+      </c>
+      <c r="T337">
+        <v>1.4</v>
+      </c>
+      <c r="U337">
+        <v>2.75</v>
+      </c>
+      <c r="V337">
+        <v>3</v>
+      </c>
+      <c r="W337">
+        <v>1.36</v>
+      </c>
+      <c r="X337">
+        <v>9</v>
+      </c>
+      <c r="Y337">
+        <v>1.07</v>
+      </c>
+      <c r="Z337">
+        <v>1.6</v>
+      </c>
+      <c r="AA337">
+        <v>3.8</v>
+      </c>
+      <c r="AB337">
+        <v>5.75</v>
+      </c>
+      <c r="AC337">
+        <v>1.06</v>
+      </c>
+      <c r="AD337">
+        <v>8.5</v>
+      </c>
+      <c r="AE337">
+        <v>1.33</v>
+      </c>
+      <c r="AF337">
+        <v>3.25</v>
+      </c>
+      <c r="AG337">
+        <v>2</v>
+      </c>
+      <c r="AH337">
+        <v>1.8</v>
+      </c>
+      <c r="AI337">
+        <v>2</v>
+      </c>
+      <c r="AJ337">
+        <v>1.73</v>
+      </c>
+      <c r="AK337">
+        <v>1.14</v>
+      </c>
+      <c r="AL337">
+        <v>1.25</v>
+      </c>
+      <c r="AM337">
+        <v>2.25</v>
+      </c>
+      <c r="AN337">
+        <v>2.46</v>
+      </c>
+      <c r="AO337">
+        <v>1.08</v>
+      </c>
+      <c r="AP337">
+        <v>2.29</v>
+      </c>
+      <c r="AQ337">
+        <v>1.21</v>
+      </c>
+      <c r="AR337">
+        <v>1.48</v>
+      </c>
+      <c r="AS337">
+        <v>1.27</v>
+      </c>
+      <c r="AT337">
+        <v>2.75</v>
+      </c>
+      <c r="AU337">
+        <v>3</v>
+      </c>
+      <c r="AV337">
+        <v>6</v>
+      </c>
+      <c r="AW337">
+        <v>14</v>
+      </c>
+      <c r="AX337">
+        <v>3</v>
+      </c>
+      <c r="AY337">
+        <v>22</v>
+      </c>
+      <c r="AZ337">
+        <v>11</v>
+      </c>
+      <c r="BA337">
+        <v>11</v>
+      </c>
+      <c r="BB337">
+        <v>1</v>
+      </c>
+      <c r="BC337">
+        <v>12</v>
+      </c>
+      <c r="BD337">
+        <v>1.6</v>
+      </c>
+      <c r="BE337">
+        <v>6.75</v>
+      </c>
+      <c r="BF337">
+        <v>2.55</v>
+      </c>
+      <c r="BG337">
+        <v>1.15</v>
+      </c>
+      <c r="BH337">
+        <v>4.4</v>
+      </c>
+      <c r="BI337">
+        <v>1.29</v>
+      </c>
+      <c r="BJ337">
+        <v>3.15</v>
+      </c>
+      <c r="BK337">
+        <v>1.49</v>
+      </c>
+      <c r="BL337">
+        <v>2.4</v>
+      </c>
+      <c r="BM337">
+        <v>1.77</v>
+      </c>
+      <c r="BN337">
+        <v>1.92</v>
+      </c>
+      <c r="BO337">
+        <v>2.18</v>
+      </c>
+      <c r="BP337">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>
